--- a/Übungen/02_Netzplan_Firmennetzwerk.xlsx
+++ b/Übungen/02_Netzplan_Firmennetzwerk.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -224,7 +224,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="13">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -316,41 +316,6 @@
       <bottom style="hair"/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thick"/>
-      <top style="thick"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thick"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thick"/>
-      <right/>
-      <top style="thick"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thick"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thick"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -380,7 +345,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -529,40 +494,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -687,7 +624,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AL51"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="2" width="3.83"/>
@@ -1138,19 +1075,19 @@
       <c r="C11" s="32"/>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="32"/>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
       <c r="N11" s="0"/>
       <c r="O11" s="0"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="32"/>
+      <c r="P11" s="0"/>
+      <c r="Q11" s="0"/>
+      <c r="R11" s="0"/>
       <c r="S11" s="0"/>
       <c r="T11" s="0"/>
       <c r="U11" s="0"/>
@@ -1180,25 +1117,19 @@
       <c r="C12" s="33"/>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
-      <c r="P12" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
+      <c r="P12" s="0"/>
+      <c r="Q12" s="0"/>
+      <c r="R12" s="0"/>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
       <c r="U12" s="0"/>
@@ -1226,27 +1157,21 @@
       </c>
       <c r="B13" s="35"/>
       <c r="C13" s="36"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="35"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="35"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="36"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
+      <c r="G13" s="0"/>
+      <c r="H13" s="0"/>
+      <c r="I13" s="0"/>
+      <c r="J13" s="0"/>
+      <c r="K13" s="0"/>
+      <c r="L13" s="0"/>
+      <c r="M13" s="0"/>
+      <c r="N13" s="0"/>
+      <c r="O13" s="0"/>
+      <c r="P13" s="0"/>
+      <c r="Q13" s="0"/>
+      <c r="R13" s="0"/>
       <c r="S13" s="0"/>
       <c r="T13" s="0"/>
       <c r="U13" s="0"/>
@@ -1269,26 +1194,26 @@
       <c r="AL13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="40" t="n">
+      <c r="A14" s="37" t="n">
         <v>0</v>
       </c>
       <c r="B14" s="28"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="42"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="0"/>
       <c r="E14" s="0"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="41"/>
+      <c r="F14" s="0"/>
+      <c r="G14" s="0"/>
+      <c r="H14" s="0"/>
       <c r="I14" s="0"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="41"/>
+      <c r="J14" s="0"/>
+      <c r="K14" s="0"/>
+      <c r="L14" s="0"/>
+      <c r="M14" s="0"/>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="41"/>
+      <c r="P14" s="0"/>
+      <c r="Q14" s="0"/>
+      <c r="R14" s="0"/>
       <c r="S14" s="0"/>
       <c r="T14" s="0"/>
       <c r="U14" s="0"/>
@@ -1311,13 +1236,13 @@
       <c r="AL14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="42"/>
+      <c r="D15" s="0"/>
       <c r="E15" s="0"/>
       <c r="F15" s="0"/>
       <c r="G15" s="0"/>
       <c r="H15" s="0"/>
       <c r="I15" s="0"/>
-      <c r="J15" s="43"/>
+      <c r="J15" s="0"/>
       <c r="K15" s="0"/>
       <c r="L15" s="0"/>
       <c r="M15" s="0"/>
@@ -1348,13 +1273,13 @@
       <c r="AL15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="42"/>
+      <c r="D16" s="0"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0"/>
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
-      <c r="J16" s="43"/>
+      <c r="J16" s="0"/>
       <c r="K16" s="0"/>
       <c r="L16" s="0"/>
       <c r="M16" s="0"/>
@@ -1385,13 +1310,13 @@
       <c r="AL16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="42"/>
+      <c r="D17" s="0"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="32"/>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
       <c r="I17" s="0"/>
-      <c r="J17" s="43"/>
+      <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0"/>
       <c r="M17" s="0"/>
@@ -1422,13 +1347,22 @@
       <c r="AL17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="44"/>
-      <c r="F18" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="J18" s="45"/>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
+      <c r="I18" s="0"/>
+      <c r="J18" s="0"/>
+      <c r="K18" s="0"/>
+      <c r="L18" s="0"/>
+      <c r="M18" s="0"/>
+      <c r="N18" s="0"/>
+      <c r="O18" s="0"/>
+      <c r="P18" s="0"/>
+      <c r="Q18" s="0"/>
+      <c r="R18" s="0"/>
+      <c r="S18" s="0"/>
       <c r="W18" s="0"/>
       <c r="X18" s="0"/>
       <c r="Y18" s="0"/>
@@ -1447,15 +1381,22 @@
       <c r="AL18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="44"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="34" t="n">
-        <v>6</v>
-      </c>
-      <c r="G19" s="35"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="45"/>
+      <c r="D19" s="0"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0"/>
+      <c r="G19" s="0"/>
+      <c r="H19" s="0"/>
+      <c r="I19" s="0"/>
+      <c r="J19" s="0"/>
+      <c r="K19" s="0"/>
+      <c r="L19" s="0"/>
+      <c r="M19" s="0"/>
+      <c r="N19" s="0"/>
+      <c r="O19" s="0"/>
+      <c r="P19" s="0"/>
+      <c r="Q19" s="0"/>
+      <c r="R19" s="0"/>
+      <c r="S19" s="0"/>
       <c r="W19" s="0"/>
       <c r="X19" s="0"/>
       <c r="Y19" s="0"/>
@@ -1474,11 +1415,22 @@
       <c r="AL19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="44"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="41"/>
-      <c r="J20" s="45"/>
+      <c r="D20" s="0"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0"/>
+      <c r="G20" s="0"/>
+      <c r="H20" s="0"/>
+      <c r="I20" s="0"/>
+      <c r="J20" s="0"/>
+      <c r="K20" s="0"/>
+      <c r="L20" s="0"/>
+      <c r="M20" s="0"/>
+      <c r="N20" s="0"/>
+      <c r="O20" s="0"/>
+      <c r="P20" s="0"/>
+      <c r="Q20" s="0"/>
+      <c r="R20" s="0"/>
+      <c r="S20" s="0"/>
       <c r="W20" s="0"/>
       <c r="X20" s="0"/>
       <c r="Y20" s="0"/>
@@ -1498,8 +1450,22 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
-      <c r="D21" s="44"/>
-      <c r="J21" s="45"/>
+      <c r="D21" s="0"/>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0"/>
+      <c r="G21" s="0"/>
+      <c r="H21" s="0"/>
+      <c r="I21" s="0"/>
+      <c r="J21" s="0"/>
+      <c r="K21" s="0"/>
+      <c r="L21" s="0"/>
+      <c r="M21" s="0"/>
+      <c r="N21" s="0"/>
+      <c r="O21" s="0"/>
+      <c r="P21" s="0"/>
+      <c r="Q21" s="0"/>
+      <c r="R21" s="0"/>
+      <c r="S21" s="0"/>
       <c r="W21" s="0"/>
       <c r="X21" s="0"/>
       <c r="Y21" s="0"/>
@@ -1519,11 +1485,22 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="D22" s="44"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="32"/>
-      <c r="J22" s="45"/>
+      <c r="D22" s="0"/>
+      <c r="E22" s="0"/>
+      <c r="F22" s="0"/>
+      <c r="G22" s="0"/>
+      <c r="H22" s="0"/>
+      <c r="I22" s="0"/>
+      <c r="J22" s="0"/>
+      <c r="K22" s="0"/>
+      <c r="L22" s="0"/>
+      <c r="M22" s="0"/>
+      <c r="N22" s="0"/>
+      <c r="O22" s="0"/>
+      <c r="P22" s="0"/>
+      <c r="Q22" s="0"/>
+      <c r="R22" s="0"/>
+      <c r="S22" s="0"/>
       <c r="W22" s="0"/>
       <c r="X22" s="0"/>
       <c r="Y22" s="0"/>
@@ -1543,31 +1520,43 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="D23" s="44"/>
-      <c r="F23" s="33" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" s="33"/>
-      <c r="H23" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="J23" s="45"/>
+      <c r="D23" s="0"/>
+      <c r="E23" s="0"/>
+      <c r="F23" s="0"/>
+      <c r="G23" s="0"/>
+      <c r="H23" s="0"/>
+      <c r="I23" s="0"/>
+      <c r="J23" s="0"/>
+      <c r="K23" s="0"/>
+      <c r="L23" s="0"/>
+      <c r="M23" s="0"/>
+      <c r="N23" s="0"/>
+      <c r="O23" s="0"/>
+      <c r="P23" s="0"/>
+      <c r="Q23" s="0"/>
+      <c r="R23" s="0"/>
+      <c r="S23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0"/>
       <c r="B24" s="0"/>
       <c r="C24" s="0"/>
       <c r="D24" s="0"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="35"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="38"/>
+      <c r="E24" s="0"/>
+      <c r="F24" s="0"/>
+      <c r="G24" s="0"/>
+      <c r="H24" s="0"/>
+      <c r="I24" s="0"/>
       <c r="J24" s="0"/>
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
+      <c r="M24" s="0"/>
+      <c r="N24" s="0"/>
+      <c r="O24" s="0"/>
+      <c r="P24" s="0"/>
+      <c r="Q24" s="0"/>
+      <c r="R24" s="0"/>
+      <c r="S24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0"/>
@@ -1575,15 +1564,20 @@
       <c r="C25" s="0"/>
       <c r="D25" s="0"/>
       <c r="E25" s="0"/>
-      <c r="F25" s="40" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" s="28"/>
-      <c r="H25" s="41"/>
+      <c r="F25" s="0"/>
+      <c r="G25" s="0"/>
+      <c r="H25" s="0"/>
       <c r="I25" s="0"/>
       <c r="J25" s="0"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
+      <c r="M25" s="0"/>
+      <c r="N25" s="0"/>
+      <c r="O25" s="0"/>
+      <c r="P25" s="0"/>
+      <c r="Q25" s="0"/>
+      <c r="R25" s="0"/>
+      <c r="S25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0"/>
@@ -1754,75 +1748,75 @@
       <c r="L37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="46"/>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="47"/>
-      <c r="I38" s="47"/>
-      <c r="J38" s="47"/>
-      <c r="K38" s="47"/>
-      <c r="L38" s="47"/>
+      <c r="A38" s="39"/>
+      <c r="B38" s="40"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="40"/>
+      <c r="L38" s="40"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="46"/>
+      <c r="A39" s="39"/>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="47"/>
+      <c r="L39" s="40"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="46"/>
-      <c r="B40" s="48" t="s">
+      <c r="A40" s="39"/>
+      <c r="B40" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="F40" s="49" t="s">
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="F40" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="49"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="L40" s="47"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="L40" s="40"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="46"/>
-      <c r="B41" s="50" t="s">
+      <c r="A41" s="39"/>
+      <c r="B41" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="51" t="s">
+      <c r="C41" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="50" t="s">
+      <c r="D41" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="L41" s="47"/>
+      <c r="L41" s="40"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="46"/>
+      <c r="A42" s="39"/>
       <c r="B42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L42" s="47"/>
+      <c r="L42" s="40"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="46"/>
-      <c r="L43" s="47"/>
+      <c r="A43" s="39"/>
+      <c r="L43" s="40"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="46"/>
-      <c r="B44" s="52" t="s">
+      <c r="A44" s="39"/>
+      <c r="B44" s="45" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="28" t="s">
@@ -1836,11 +1830,11 @@
       <c r="I44" s="28"/>
       <c r="J44" s="28"/>
       <c r="K44" s="28"/>
-      <c r="L44" s="47"/>
+      <c r="L44" s="40"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="46"/>
-      <c r="B45" s="52" t="s">
+      <c r="A45" s="39"/>
+      <c r="B45" s="45" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="28" t="s">
@@ -1854,11 +1848,11 @@
       <c r="I45" s="28"/>
       <c r="J45" s="28"/>
       <c r="K45" s="28"/>
-      <c r="L45" s="47"/>
+      <c r="L45" s="40"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="46"/>
-      <c r="B46" s="52" t="s">
+      <c r="A46" s="39"/>
+      <c r="B46" s="45" t="s">
         <v>17</v>
       </c>
       <c r="C46" s="28" t="s">
@@ -1872,11 +1866,11 @@
       <c r="I46" s="28"/>
       <c r="J46" s="28"/>
       <c r="K46" s="28"/>
-      <c r="L46" s="47"/>
+      <c r="L46" s="40"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="46"/>
-      <c r="B47" s="52" t="s">
+      <c r="A47" s="39"/>
+      <c r="B47" s="45" t="s">
         <v>22</v>
       </c>
       <c r="C47" s="28" t="s">
@@ -1890,11 +1884,11 @@
       <c r="I47" s="28"/>
       <c r="J47" s="28"/>
       <c r="K47" s="28"/>
-      <c r="L47" s="47"/>
+      <c r="L47" s="40"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="46"/>
-      <c r="B48" s="50" t="s">
+      <c r="A48" s="39"/>
+      <c r="B48" s="43" t="s">
         <v>4</v>
       </c>
       <c r="C48" s="28" t="s">
@@ -1908,11 +1902,11 @@
       <c r="I48" s="28"/>
       <c r="J48" s="28"/>
       <c r="K48" s="28"/>
-      <c r="L48" s="47"/>
+      <c r="L48" s="40"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="46"/>
-      <c r="B49" s="51" t="s">
+      <c r="A49" s="39"/>
+      <c r="B49" s="44" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="28" t="s">
@@ -1926,42 +1920,42 @@
       <c r="I49" s="28"/>
       <c r="J49" s="28"/>
       <c r="K49" s="28"/>
-      <c r="L49" s="47"/>
+      <c r="L49" s="40"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="46"/>
-      <c r="B50" s="53" t="s">
+      <c r="A50" s="39"/>
+      <c r="B50" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="47" t="s">
+      <c r="C50" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="47"/>
-      <c r="I50" s="47"/>
-      <c r="J50" s="47"/>
-      <c r="K50" s="47"/>
-      <c r="L50" s="47"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="40"/>
+      <c r="L50" s="40"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="46"/>
-      <c r="B51" s="47"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="47"/>
-      <c r="I51" s="47"/>
-      <c r="J51" s="47"/>
-      <c r="K51" s="47"/>
-      <c r="L51" s="47"/>
+      <c r="A51" s="39"/>
+      <c r="B51" s="40"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="18">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:P1"/>
@@ -1972,11 +1966,6 @@
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F23:H23"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="F40:J40"/>
     <mergeCell ref="C44:K44"/>
@@ -1986,7 +1975,7 @@
     <mergeCell ref="C48:K48"/>
     <mergeCell ref="C49:K49"/>
   </mergeCells>
-  <conditionalFormatting sqref="B13 G13 G19 G24 L13 Q13">
+  <conditionalFormatting sqref="B13">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/Übungen/02_Netzplan_Firmennetzwerk.xlsx
+++ b/Übungen/02_Netzplan_Firmennetzwerk.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -224,7 +224,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="18">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -316,6 +316,41 @@
       <bottom style="hair"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -345,7 +380,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="52">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -494,12 +529,32 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -624,7 +679,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AL51"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="2" width="3.83"/>
@@ -1072,22 +1127,36 @@
         <v>0</v>
       </c>
       <c r="B11" s="31"/>
-      <c r="C11" s="32"/>
+      <c r="C11" s="32" t="n">
+        <v>7</v>
+      </c>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
+      <c r="F11" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32" t="n">
+        <v>10</v>
+      </c>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
-      <c r="K11" s="0"/>
-      <c r="L11" s="0"/>
-      <c r="M11" s="0"/>
+      <c r="K11" s="30" t="n">
+        <v>13</v>
+      </c>
+      <c r="L11" s="31"/>
+      <c r="M11" s="32" t="n">
+        <v>14</v>
+      </c>
       <c r="N11" s="0"/>
       <c r="O11" s="0"/>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="0"/>
-      <c r="R11" s="0"/>
+      <c r="P11" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="32" t="n">
+        <v>15</v>
+      </c>
       <c r="S11" s="0"/>
       <c r="T11" s="0"/>
       <c r="U11" s="0"/>
@@ -1117,19 +1186,25 @@
       <c r="C12" s="33"/>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
+      <c r="F12" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="0"/>
-      <c r="L12" s="0"/>
-      <c r="M12" s="0"/>
+      <c r="K12" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
-      <c r="P12" s="0"/>
-      <c r="Q12" s="0"/>
-      <c r="R12" s="0"/>
+      <c r="P12" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
       <c r="U12" s="0"/>
@@ -1151,27 +1226,50 @@
       <c r="AK12" s="0"/>
       <c r="AL12" s="0"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0"/>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0"/>
-      <c r="K13" s="0"/>
-      <c r="L13" s="0"/>
-      <c r="M13" s="0"/>
-      <c r="N13" s="0"/>
-      <c r="O13" s="0"/>
-      <c r="P13" s="0"/>
-      <c r="Q13" s="0"/>
-      <c r="R13" s="0"/>
+      <c r="B13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="37"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="34" t="n">
+        <f aca="false">Q3</f>
+        <v>3</v>
+      </c>
+      <c r="G13" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="38"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="34" t="n">
+        <f aca="false">Q6</f>
+        <v>1</v>
+      </c>
+      <c r="L13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="34" t="n">
+        <f aca="false">Q7</f>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="36"/>
       <c r="S13" s="0"/>
       <c r="T13" s="0"/>
       <c r="U13" s="0"/>
@@ -1194,26 +1292,40 @@
       <c r="AL13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
+      <c r="A14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="B14" s="28"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="0"/>
+      <c r="C14" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="42"/>
       <c r="E14" s="0"/>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
+      <c r="F14" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="28"/>
+      <c r="H14" s="41" t="n">
+        <v>13</v>
+      </c>
       <c r="I14" s="0"/>
-      <c r="J14" s="0"/>
-      <c r="K14" s="0"/>
-      <c r="L14" s="0"/>
-      <c r="M14" s="0"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="L14" s="28"/>
+      <c r="M14" s="41" t="n">
+        <v>14</v>
+      </c>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
-      <c r="P14" s="0"/>
-      <c r="Q14" s="0"/>
-      <c r="R14" s="0"/>
+      <c r="P14" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="41" t="n">
+        <v>15</v>
+      </c>
       <c r="S14" s="0"/>
       <c r="T14" s="0"/>
       <c r="U14" s="0"/>
@@ -1236,13 +1348,13 @@
       <c r="AL14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="0"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="0"/>
       <c r="F15" s="0"/>
       <c r="G15" s="0"/>
       <c r="H15" s="0"/>
       <c r="I15" s="0"/>
-      <c r="J15" s="0"/>
+      <c r="J15" s="43"/>
       <c r="K15" s="0"/>
       <c r="L15" s="0"/>
       <c r="M15" s="0"/>
@@ -1273,13 +1385,13 @@
       <c r="AL15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="0"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0"/>
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
-      <c r="J16" s="0"/>
+      <c r="J16" s="43"/>
       <c r="K16" s="0"/>
       <c r="L16" s="0"/>
       <c r="M16" s="0"/>
@@ -1310,13 +1422,17 @@
       <c r="AL16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="0"/>
+      <c r="D17" s="42"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="0"/>
-      <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
+      <c r="F17" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="31"/>
+      <c r="H17" s="32" t="n">
+        <v>13</v>
+      </c>
       <c r="I17" s="0"/>
-      <c r="J17" s="0"/>
+      <c r="J17" s="43"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0"/>
       <c r="M17" s="0"/>
@@ -1347,13 +1463,15 @@
       <c r="AL17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="0"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="0"/>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
+      <c r="F18" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="0"/>
-      <c r="J18" s="0"/>
+      <c r="J18" s="43"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
       <c r="M18" s="0"/>
@@ -1380,14 +1498,21 @@
       <c r="AK18" s="0"/>
       <c r="AL18" s="0"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0"/>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-      <c r="I19" s="0"/>
-      <c r="J19" s="0"/>
+    <row r="19" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="42"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="34" t="n">
+        <f aca="false">Q4</f>
+        <v>6</v>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="38"/>
+      <c r="J19" s="43"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0"/>
       <c r="M19" s="0"/>
@@ -1415,13 +1540,17 @@
       <c r="AL19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="0"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="0"/>
-      <c r="F20" s="0"/>
-      <c r="G20" s="0"/>
-      <c r="H20" s="0"/>
+      <c r="F20" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="28"/>
+      <c r="H20" s="41" t="n">
+        <v>13</v>
+      </c>
       <c r="I20" s="0"/>
-      <c r="J20" s="0"/>
+      <c r="J20" s="43"/>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
       <c r="M20" s="0"/>
@@ -1450,13 +1579,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
-      <c r="D21" s="0"/>
+      <c r="D21" s="42"/>
       <c r="E21" s="0"/>
       <c r="F21" s="0"/>
       <c r="G21" s="0"/>
       <c r="H21" s="0"/>
       <c r="I21" s="0"/>
-      <c r="J21" s="0"/>
+      <c r="J21" s="43"/>
       <c r="K21" s="0"/>
       <c r="L21" s="0"/>
       <c r="M21" s="0"/>
@@ -1485,13 +1614,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="D22" s="0"/>
+      <c r="D22" s="42"/>
       <c r="E22" s="0"/>
       <c r="F22" s="0"/>
       <c r="G22" s="0"/>
       <c r="H22" s="0"/>
       <c r="I22" s="0"/>
-      <c r="J22" s="0"/>
+      <c r="J22" s="43"/>
       <c r="K22" s="0"/>
       <c r="L22" s="0"/>
       <c r="M22" s="0"/>
@@ -1520,13 +1649,17 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="D23" s="0"/>
+      <c r="D23" s="42"/>
       <c r="E23" s="0"/>
-      <c r="F23" s="0"/>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
+      <c r="F23" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="31"/>
+      <c r="H23" s="32" t="n">
+        <v>10</v>
+      </c>
       <c r="I23" s="0"/>
-      <c r="J23" s="0"/>
+      <c r="J23" s="43"/>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
       <c r="M23" s="0"/>
@@ -1541,13 +1674,15 @@
       <c r="A24" s="0"/>
       <c r="B24" s="0"/>
       <c r="C24" s="0"/>
-      <c r="D24" s="0"/>
+      <c r="D24" s="42"/>
       <c r="E24" s="0"/>
-      <c r="F24" s="0"/>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
+      <c r="F24" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
       <c r="I24" s="0"/>
-      <c r="J24" s="0"/>
+      <c r="J24" s="43"/>
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
       <c r="M24" s="0"/>
@@ -1558,16 +1693,23 @@
       <c r="R24" s="0"/>
       <c r="S24" s="0"/>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0"/>
       <c r="B25" s="0"/>
       <c r="C25" s="0"/>
       <c r="D25" s="0"/>
-      <c r="E25" s="0"/>
-      <c r="F25" s="0"/>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-      <c r="I25" s="0"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="34" t="n">
+        <f aca="false">Q5</f>
+        <v>3</v>
+      </c>
+      <c r="G25" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="38"/>
       <c r="J25" s="0"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
@@ -1585,9 +1727,13 @@
       <c r="C26" s="0"/>
       <c r="D26" s="0"/>
       <c r="E26" s="0"/>
-      <c r="F26" s="0"/>
-      <c r="G26" s="0"/>
-      <c r="H26" s="0"/>
+      <c r="F26" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" s="28"/>
+      <c r="H26" s="41" t="n">
+        <v>13</v>
+      </c>
       <c r="I26" s="0"/>
       <c r="J26" s="0"/>
       <c r="K26" s="0"/>
@@ -1748,75 +1894,75 @@
       <c r="L37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="39"/>
-      <c r="B38" s="40"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
+      <c r="A38" s="44"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="45"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="45"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="39"/>
+      <c r="A39" s="44"/>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="40"/>
+      <c r="L39" s="45"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="39"/>
-      <c r="B40" s="41" t="s">
+      <c r="A40" s="44"/>
+      <c r="B40" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="F40" s="42" t="s">
+      <c r="C40" s="46"/>
+      <c r="D40" s="46"/>
+      <c r="F40" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
-      <c r="L40" s="40"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="47"/>
+      <c r="I40" s="47"/>
+      <c r="J40" s="47"/>
+      <c r="L40" s="45"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="39"/>
-      <c r="B41" s="43" t="s">
+      <c r="A41" s="44"/>
+      <c r="B41" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="44" t="s">
+      <c r="C41" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="43" t="s">
+      <c r="D41" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="L41" s="40"/>
+      <c r="L41" s="45"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="39"/>
+      <c r="A42" s="44"/>
       <c r="B42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L42" s="40"/>
+      <c r="L42" s="45"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="39"/>
-      <c r="L43" s="40"/>
+      <c r="A43" s="44"/>
+      <c r="L43" s="45"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="39"/>
-      <c r="B44" s="45" t="s">
+      <c r="A44" s="44"/>
+      <c r="B44" s="50" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="28" t="s">
@@ -1830,11 +1976,11 @@
       <c r="I44" s="28"/>
       <c r="J44" s="28"/>
       <c r="K44" s="28"/>
-      <c r="L44" s="40"/>
+      <c r="L44" s="45"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="39"/>
-      <c r="B45" s="45" t="s">
+      <c r="A45" s="44"/>
+      <c r="B45" s="50" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="28" t="s">
@@ -1848,11 +1994,11 @@
       <c r="I45" s="28"/>
       <c r="J45" s="28"/>
       <c r="K45" s="28"/>
-      <c r="L45" s="40"/>
+      <c r="L45" s="45"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="39"/>
-      <c r="B46" s="45" t="s">
+      <c r="A46" s="44"/>
+      <c r="B46" s="50" t="s">
         <v>17</v>
       </c>
       <c r="C46" s="28" t="s">
@@ -1866,11 +2012,11 @@
       <c r="I46" s="28"/>
       <c r="J46" s="28"/>
       <c r="K46" s="28"/>
-      <c r="L46" s="40"/>
+      <c r="L46" s="45"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="39"/>
-      <c r="B47" s="45" t="s">
+      <c r="A47" s="44"/>
+      <c r="B47" s="50" t="s">
         <v>22</v>
       </c>
       <c r="C47" s="28" t="s">
@@ -1884,11 +2030,11 @@
       <c r="I47" s="28"/>
       <c r="J47" s="28"/>
       <c r="K47" s="28"/>
-      <c r="L47" s="40"/>
+      <c r="L47" s="45"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="39"/>
-      <c r="B48" s="43" t="s">
+      <c r="A48" s="44"/>
+      <c r="B48" s="48" t="s">
         <v>4</v>
       </c>
       <c r="C48" s="28" t="s">
@@ -1902,11 +2048,11 @@
       <c r="I48" s="28"/>
       <c r="J48" s="28"/>
       <c r="K48" s="28"/>
-      <c r="L48" s="40"/>
+      <c r="L48" s="45"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="39"/>
-      <c r="B49" s="44" t="s">
+      <c r="A49" s="44"/>
+      <c r="B49" s="49" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="28" t="s">
@@ -1920,42 +2066,42 @@
       <c r="I49" s="28"/>
       <c r="J49" s="28"/>
       <c r="K49" s="28"/>
-      <c r="L49" s="40"/>
+      <c r="L49" s="45"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="39"/>
-      <c r="B50" s="46" t="s">
+      <c r="A50" s="44"/>
+      <c r="B50" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="40" t="s">
+      <c r="C50" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="40"/>
-      <c r="L50" s="40"/>
+      <c r="D50" s="45"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="45"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="39"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="40"/>
-      <c r="L51" s="40"/>
+      <c r="A51" s="44"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="45"/>
+      <c r="D51" s="45"/>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="45"/>
+      <c r="H51" s="45"/>
+      <c r="I51" s="45"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="45"/>
+      <c r="L51" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="23">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:P1"/>
@@ -1966,6 +2112,11 @@
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="F40:J40"/>
     <mergeCell ref="C44:K44"/>
@@ -1975,7 +2126,7 @@
     <mergeCell ref="C48:K48"/>
     <mergeCell ref="C49:K49"/>
   </mergeCells>
-  <conditionalFormatting sqref="B13">
+  <conditionalFormatting sqref="B13 G13 G19 G25 L13 Q13">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/Übungen/02_Netzplan_Firmennetzwerk.xlsx
+++ b/Übungen/02_Netzplan_Firmennetzwerk.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -119,8 +119,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -186,7 +188,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,6 +199,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFAADCF7"/>
         <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF729FCF"/>
+        <bgColor rgb="FF999999"/>
       </patternFill>
     </fill>
     <fill>
@@ -224,7 +232,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="18">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -316,6 +324,41 @@
       <bottom style="hair"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -345,7 +388,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -378,6 +421,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -386,15 +437,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -410,6 +461,18 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -446,16 +509,28 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -466,51 +541,71 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -518,19 +613,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -573,7 +668,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB2B2B2"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF729FCF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
@@ -623,19 +718,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AL51"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BN51"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="2" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="3" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="4.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="3.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="20" style="4" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="36" style="2" width="3.83"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="42.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -663,225 +758,470 @@
       <c r="Q1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R1" s="0"/>
-      <c r="T1" s="2"/>
-      <c r="W1" s="0"/>
-      <c r="X1" s="0"/>
-      <c r="Y1" s="0"/>
-      <c r="Z1" s="0"/>
-      <c r="AA1" s="0"/>
-      <c r="AB1" s="0"/>
-      <c r="AC1" s="0"/>
-      <c r="AD1" s="0"/>
-      <c r="AE1" s="0"/>
-      <c r="AF1" s="0"/>
-      <c r="AG1" s="0"/>
-      <c r="AH1" s="0"/>
-      <c r="AI1" s="0"/>
-      <c r="AJ1" s="0"/>
-      <c r="AK1" s="0"/>
-      <c r="AL1" s="0"/>
+      <c r="R1" s="8" t="n">
+        <v>44606</v>
+      </c>
+      <c r="S1" s="8" t="n">
+        <v>44607</v>
+      </c>
+      <c r="T1" s="8" t="n">
+        <v>44608</v>
+      </c>
+      <c r="U1" s="8" t="n">
+        <v>44609</v>
+      </c>
+      <c r="V1" s="8" t="n">
+        <v>44610</v>
+      </c>
+      <c r="W1" s="8" t="n">
+        <v>44611</v>
+      </c>
+      <c r="X1" s="8" t="n">
+        <v>44612</v>
+      </c>
+      <c r="Y1" s="8" t="n">
+        <v>44613</v>
+      </c>
+      <c r="Z1" s="8" t="n">
+        <v>44614</v>
+      </c>
+      <c r="AA1" s="8" t="n">
+        <v>44615</v>
+      </c>
+      <c r="AB1" s="8" t="n">
+        <v>44616</v>
+      </c>
+      <c r="AC1" s="8" t="n">
+        <v>44617</v>
+      </c>
+      <c r="AD1" s="8" t="n">
+        <v>44618</v>
+      </c>
+      <c r="AE1" s="8" t="n">
+        <v>44619</v>
+      </c>
+      <c r="AF1" s="8" t="n">
+        <v>44620</v>
+      </c>
+      <c r="AG1" s="8" t="n">
+        <v>44621</v>
+      </c>
+      <c r="AH1" s="8" t="n">
+        <v>44622</v>
+      </c>
+      <c r="AI1" s="8" t="n">
+        <v>44623</v>
+      </c>
+      <c r="AJ1" s="8" t="n">
+        <v>44624</v>
+      </c>
+      <c r="AK1" s="8" t="n">
+        <v>44625</v>
+      </c>
+      <c r="AL1" s="8" t="n">
+        <v>44626</v>
+      </c>
+      <c r="AM1" s="8" t="n">
+        <v>44627</v>
+      </c>
+      <c r="AN1" s="8" t="n">
+        <v>44628</v>
+      </c>
+      <c r="AO1" s="8" t="n">
+        <v>44629</v>
+      </c>
+      <c r="AP1" s="8" t="n">
+        <v>44630</v>
+      </c>
+      <c r="AQ1" s="8" t="n">
+        <v>44631</v>
+      </c>
+      <c r="AR1" s="8" t="n">
+        <v>44632</v>
+      </c>
+      <c r="AS1" s="8" t="n">
+        <v>44633</v>
+      </c>
+      <c r="AT1" s="8" t="n">
+        <v>44634</v>
+      </c>
+      <c r="AU1" s="8" t="n">
+        <v>44635</v>
+      </c>
+      <c r="AV1" s="8" t="n">
+        <v>44636</v>
+      </c>
+      <c r="AW1" s="8" t="n">
+        <v>44637</v>
+      </c>
+      <c r="AX1" s="8" t="n">
+        <v>44638</v>
+      </c>
+      <c r="AY1" s="8" t="n">
+        <v>44639</v>
+      </c>
+      <c r="AZ1" s="8" t="n">
+        <v>44640</v>
+      </c>
+      <c r="BA1" s="8" t="n">
+        <v>44641</v>
+      </c>
+      <c r="BB1" s="8" t="n">
+        <v>44642</v>
+      </c>
+      <c r="BC1" s="8" t="n">
+        <v>44643</v>
+      </c>
+      <c r="BD1" s="8" t="n">
+        <v>44644</v>
+      </c>
+      <c r="BE1" s="8" t="n">
+        <v>44645</v>
+      </c>
+      <c r="BF1" s="8" t="n">
+        <v>44646</v>
+      </c>
+      <c r="BG1" s="8" t="n">
+        <v>44647</v>
+      </c>
+      <c r="BH1" s="8" t="n">
+        <v>44648</v>
+      </c>
+      <c r="BI1" s="8" t="n">
+        <v>44649</v>
+      </c>
+      <c r="BJ1" s="8" t="n">
+        <v>44650</v>
+      </c>
+      <c r="BK1" s="8" t="n">
+        <v>44651</v>
+      </c>
+      <c r="BL1" s="8" t="n">
+        <v>44652</v>
+      </c>
+      <c r="BM1" s="9"/>
+      <c r="BN1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="13" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15" t="n">
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="R2" s="0"/>
-      <c r="W2" s="0"/>
-      <c r="X2" s="0"/>
-      <c r="Y2" s="0"/>
-      <c r="Z2" s="0"/>
-      <c r="AA2" s="0"/>
-      <c r="AB2" s="0"/>
-      <c r="AC2" s="0"/>
-      <c r="AD2" s="0"/>
-      <c r="AE2" s="0"/>
-      <c r="AF2" s="0"/>
-      <c r="AG2" s="0"/>
-      <c r="AH2" s="0"/>
-      <c r="AI2" s="0"/>
-      <c r="AJ2" s="0"/>
-      <c r="AK2" s="0"/>
-      <c r="AL2" s="0"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="18"/>
+      <c r="Y2" s="18"/>
+      <c r="Z2" s="18"/>
+      <c r="AA2" s="18"/>
+      <c r="AB2" s="18"/>
+      <c r="AC2" s="18"/>
+      <c r="AD2" s="18"/>
+      <c r="AE2" s="18"/>
+      <c r="AF2" s="18"/>
+      <c r="AG2" s="18"/>
+      <c r="AH2" s="18"/>
+      <c r="AI2" s="18"/>
+      <c r="AJ2" s="18"/>
+      <c r="AK2" s="18"/>
+      <c r="AL2" s="18"/>
+      <c r="AM2" s="19"/>
+      <c r="AN2" s="19"/>
+      <c r="AO2" s="19"/>
+      <c r="AP2" s="19"/>
+      <c r="AQ2" s="19"/>
+      <c r="AR2" s="19"/>
+      <c r="AS2" s="19"/>
+      <c r="AT2" s="19"/>
+      <c r="AU2" s="19"/>
+      <c r="AV2" s="19"/>
+      <c r="AW2" s="19"/>
+      <c r="AX2" s="19"/>
+      <c r="AY2" s="19"/>
+      <c r="AZ2" s="19"/>
+      <c r="BA2" s="19"/>
+      <c r="BB2" s="19"/>
+      <c r="BC2" s="19"/>
+      <c r="BD2" s="19"/>
+      <c r="BE2" s="19"/>
+      <c r="BF2" s="19"/>
+      <c r="BG2" s="19"/>
+      <c r="BH2" s="19"/>
+      <c r="BI2" s="19"/>
+      <c r="BJ2" s="19"/>
+      <c r="BK2" s="19"/>
+      <c r="BL2" s="19"/>
     </row>
     <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18" t="s">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="23" t="s">
         <v>5</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="18" t="s">
+      <c r="L3" s="24"/>
+      <c r="M3" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19" t="n">
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="R3" s="0"/>
-      <c r="W3" s="0"/>
-      <c r="X3" s="0"/>
-      <c r="Y3" s="0"/>
-      <c r="Z3" s="0"/>
-      <c r="AA3" s="0"/>
-      <c r="AB3" s="0"/>
-      <c r="AC3" s="0"/>
-      <c r="AD3" s="0"/>
-      <c r="AE3" s="0"/>
-      <c r="AF3" s="0"/>
-      <c r="AG3" s="0"/>
-      <c r="AH3" s="0"/>
-      <c r="AI3" s="0"/>
-      <c r="AJ3" s="0"/>
-      <c r="AK3" s="0"/>
-      <c r="AL3" s="0"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="18"/>
+      <c r="Y3" s="18"/>
+      <c r="Z3" s="18"/>
+      <c r="AA3" s="18"/>
+      <c r="AB3" s="18"/>
+      <c r="AC3" s="18"/>
+      <c r="AD3" s="18"/>
+      <c r="AE3" s="18"/>
+      <c r="AF3" s="18"/>
+      <c r="AG3" s="18"/>
+      <c r="AH3" s="18"/>
+      <c r="AI3" s="18"/>
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="18"/>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="19"/>
+      <c r="AO3" s="19"/>
+      <c r="AP3" s="19"/>
+      <c r="AQ3" s="19"/>
+      <c r="AR3" s="19"/>
+      <c r="AS3" s="19"/>
+      <c r="AT3" s="19"/>
+      <c r="AU3" s="19"/>
+      <c r="AV3" s="19"/>
+      <c r="AW3" s="19"/>
+      <c r="AX3" s="19"/>
+      <c r="AY3" s="19"/>
+      <c r="AZ3" s="19"/>
+      <c r="BA3" s="19"/>
+      <c r="BB3" s="19"/>
+      <c r="BC3" s="19"/>
+      <c r="BD3" s="19"/>
+      <c r="BE3" s="19"/>
+      <c r="BF3" s="19"/>
+      <c r="BG3" s="19"/>
+      <c r="BH3" s="19"/>
+      <c r="BI3" s="19"/>
+      <c r="BJ3" s="19"/>
+      <c r="BK3" s="19"/>
+      <c r="BL3" s="19"/>
     </row>
     <row r="4" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="23" t="s">
         <v>5</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="18" t="s">
+      <c r="L4" s="24"/>
+      <c r="M4" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19" t="n">
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="0"/>
-      <c r="W4" s="0"/>
-      <c r="X4" s="0"/>
-      <c r="Y4" s="0"/>
-      <c r="Z4" s="0"/>
-      <c r="AA4" s="0"/>
-      <c r="AB4" s="0"/>
-      <c r="AC4" s="0"/>
-      <c r="AD4" s="0"/>
-      <c r="AE4" s="0"/>
-      <c r="AF4" s="0"/>
-      <c r="AG4" s="0"/>
-      <c r="AH4" s="0"/>
-      <c r="AI4" s="0"/>
-      <c r="AJ4" s="0"/>
-      <c r="AK4" s="0"/>
-      <c r="AL4" s="0"/>
+      <c r="R4" s="18"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="18"/>
+      <c r="X4" s="18"/>
+      <c r="Y4" s="18"/>
+      <c r="Z4" s="18"/>
+      <c r="AA4" s="18"/>
+      <c r="AB4" s="18"/>
+      <c r="AC4" s="18"/>
+      <c r="AD4" s="18"/>
+      <c r="AE4" s="18"/>
+      <c r="AF4" s="18"/>
+      <c r="AG4" s="18"/>
+      <c r="AH4" s="18"/>
+      <c r="AI4" s="18"/>
+      <c r="AJ4" s="18"/>
+      <c r="AK4" s="18"/>
+      <c r="AL4" s="18"/>
+      <c r="AM4" s="19"/>
+      <c r="AN4" s="19"/>
+      <c r="AO4" s="19"/>
+      <c r="AP4" s="19"/>
+      <c r="AQ4" s="19"/>
+      <c r="AR4" s="19"/>
+      <c r="AS4" s="19"/>
+      <c r="AT4" s="19"/>
+      <c r="AU4" s="19"/>
+      <c r="AV4" s="19"/>
+      <c r="AW4" s="19"/>
+      <c r="AX4" s="19"/>
+      <c r="AY4" s="19"/>
+      <c r="AZ4" s="19"/>
+      <c r="BA4" s="19"/>
+      <c r="BB4" s="19"/>
+      <c r="BC4" s="19"/>
+      <c r="BD4" s="19"/>
+      <c r="BE4" s="19"/>
+      <c r="BF4" s="19"/>
+      <c r="BG4" s="19"/>
+      <c r="BH4" s="19"/>
+      <c r="BI4" s="19"/>
+      <c r="BJ4" s="19"/>
+      <c r="BK4" s="19"/>
+      <c r="BL4" s="19"/>
     </row>
     <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18" t="s">
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="23" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="18" t="s">
+      <c r="L5" s="24"/>
+      <c r="M5" s="23" t="s">
         <v>10</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19" t="n">
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="R5" s="0"/>
-      <c r="W5" s="0"/>
-      <c r="X5" s="0"/>
-      <c r="Y5" s="0"/>
-      <c r="Z5" s="0"/>
-      <c r="AA5" s="0"/>
-      <c r="AB5" s="0"/>
-      <c r="AC5" s="0"/>
-      <c r="AD5" s="0"/>
-      <c r="AE5" s="0"/>
-      <c r="AF5" s="0"/>
-      <c r="AG5" s="0"/>
-      <c r="AH5" s="0"/>
-      <c r="AI5" s="0"/>
-      <c r="AJ5" s="0"/>
-      <c r="AK5" s="0"/>
-      <c r="AL5" s="0"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="18"/>
+      <c r="Y5" s="18"/>
+      <c r="Z5" s="18"/>
+      <c r="AA5" s="18"/>
+      <c r="AB5" s="18"/>
+      <c r="AC5" s="18"/>
+      <c r="AD5" s="18"/>
+      <c r="AE5" s="18"/>
+      <c r="AF5" s="18"/>
+      <c r="AG5" s="18"/>
+      <c r="AH5" s="18"/>
+      <c r="AI5" s="18"/>
+      <c r="AJ5" s="18"/>
+      <c r="AK5" s="18"/>
+      <c r="AL5" s="18"/>
+      <c r="AM5" s="19"/>
+      <c r="AN5" s="19"/>
+      <c r="AO5" s="19"/>
+      <c r="AP5" s="19"/>
+      <c r="AQ5" s="19"/>
+      <c r="AR5" s="19"/>
+      <c r="AS5" s="19"/>
+      <c r="AT5" s="19"/>
+      <c r="AU5" s="19"/>
+      <c r="AV5" s="19"/>
+      <c r="AW5" s="19"/>
+      <c r="AX5" s="19"/>
+      <c r="AY5" s="19"/>
+      <c r="AZ5" s="19"/>
+      <c r="BA5" s="19"/>
+      <c r="BB5" s="19"/>
+      <c r="BC5" s="19"/>
+      <c r="BD5" s="19"/>
+      <c r="BE5" s="19"/>
+      <c r="BF5" s="19"/>
+      <c r="BG5" s="19"/>
+      <c r="BH5" s="19"/>
+      <c r="BI5" s="19"/>
+      <c r="BJ5" s="19"/>
+      <c r="BK5" s="19"/>
+      <c r="BL5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="18" t="s">
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="23" t="s">
         <v>7</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -890,90 +1230,150 @@
       <c r="K6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="19"/>
-      <c r="M6" s="18" t="s">
+      <c r="L6" s="24"/>
+      <c r="M6" s="23" t="s">
         <v>14</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19" t="n">
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="R6" s="0"/>
-      <c r="W6" s="0"/>
-      <c r="X6" s="0"/>
-      <c r="Y6" s="0"/>
-      <c r="Z6" s="0"/>
-      <c r="AA6" s="0"/>
-      <c r="AB6" s="0"/>
-      <c r="AC6" s="0"/>
-      <c r="AD6" s="0"/>
-      <c r="AE6" s="0"/>
-      <c r="AF6" s="0"/>
-      <c r="AG6" s="0"/>
-      <c r="AH6" s="0"/>
-      <c r="AI6" s="0"/>
-      <c r="AJ6" s="0"/>
-      <c r="AK6" s="0"/>
-      <c r="AL6" s="0"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="18"/>
+      <c r="X6" s="18"/>
+      <c r="Y6" s="18"/>
+      <c r="Z6" s="18"/>
+      <c r="AA6" s="18"/>
+      <c r="AB6" s="18"/>
+      <c r="AC6" s="18"/>
+      <c r="AD6" s="18"/>
+      <c r="AE6" s="18"/>
+      <c r="AF6" s="18"/>
+      <c r="AG6" s="18"/>
+      <c r="AH6" s="18"/>
+      <c r="AI6" s="18"/>
+      <c r="AJ6" s="18"/>
+      <c r="AK6" s="18"/>
+      <c r="AL6" s="18"/>
+      <c r="AM6" s="19"/>
+      <c r="AN6" s="19"/>
+      <c r="AO6" s="19"/>
+      <c r="AP6" s="19"/>
+      <c r="AQ6" s="19"/>
+      <c r="AR6" s="19"/>
+      <c r="AS6" s="19"/>
+      <c r="AT6" s="19"/>
+      <c r="AU6" s="19"/>
+      <c r="AV6" s="19"/>
+      <c r="AW6" s="19"/>
+      <c r="AX6" s="19"/>
+      <c r="AY6" s="19"/>
+      <c r="AZ6" s="19"/>
+      <c r="BA6" s="19"/>
+      <c r="BB6" s="19"/>
+      <c r="BC6" s="19"/>
+      <c r="BD6" s="19"/>
+      <c r="BE6" s="19"/>
+      <c r="BF6" s="19"/>
+      <c r="BG6" s="19"/>
+      <c r="BH6" s="19"/>
+      <c r="BI6" s="19"/>
+      <c r="BJ6" s="19"/>
+      <c r="BK6" s="19"/>
+      <c r="BL6" s="19"/>
     </row>
     <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="22" t="s">
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="24" t="n">
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="0"/>
-      <c r="W7" s="0"/>
-      <c r="X7" s="0"/>
-      <c r="Y7" s="0"/>
-      <c r="Z7" s="0"/>
-      <c r="AA7" s="0"/>
-      <c r="AB7" s="0"/>
-      <c r="AC7" s="0"/>
-      <c r="AD7" s="0"/>
-      <c r="AE7" s="0"/>
-      <c r="AF7" s="0"/>
-      <c r="AG7" s="0"/>
-      <c r="AH7" s="0"/>
-      <c r="AI7" s="0"/>
-      <c r="AJ7" s="0"/>
-      <c r="AK7" s="0"/>
-      <c r="AL7" s="0"/>
+      <c r="R7" s="33"/>
+      <c r="S7" s="34"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="33"/>
+      <c r="X7" s="33"/>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="33"/>
+      <c r="AA7" s="33"/>
+      <c r="AB7" s="33"/>
+      <c r="AC7" s="33"/>
+      <c r="AD7" s="33"/>
+      <c r="AE7" s="33"/>
+      <c r="AF7" s="33"/>
+      <c r="AG7" s="33"/>
+      <c r="AH7" s="33"/>
+      <c r="AI7" s="33"/>
+      <c r="AJ7" s="33"/>
+      <c r="AK7" s="33"/>
+      <c r="AL7" s="33"/>
+      <c r="AM7" s="34"/>
+      <c r="AN7" s="34"/>
+      <c r="AO7" s="34"/>
+      <c r="AP7" s="34"/>
+      <c r="AQ7" s="34"/>
+      <c r="AR7" s="34"/>
+      <c r="AS7" s="34"/>
+      <c r="AT7" s="34"/>
+      <c r="AU7" s="34"/>
+      <c r="AV7" s="34"/>
+      <c r="AW7" s="34"/>
+      <c r="AX7" s="34"/>
+      <c r="AY7" s="34"/>
+      <c r="AZ7" s="34"/>
+      <c r="BA7" s="34"/>
+      <c r="BB7" s="34"/>
+      <c r="BC7" s="34"/>
+      <c r="BD7" s="34"/>
+      <c r="BE7" s="34"/>
+      <c r="BF7" s="34"/>
+      <c r="BG7" s="34"/>
+      <c r="BH7" s="34"/>
+      <c r="BI7" s="34"/>
+      <c r="BJ7" s="34"/>
+      <c r="BK7" s="34"/>
+      <c r="BL7" s="34"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="29"/>
+      <c r="B8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="37"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
       <c r="T8" s="2"/>
       <c r="W8" s="0"/>
       <c r="X8" s="0"/>
@@ -993,7 +1393,7 @@
       <c r="AL8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="28"/>
+      <c r="B9" s="36"/>
       <c r="D9" s="0"/>
       <c r="E9" s="0"/>
       <c r="F9" s="0"/>
@@ -1068,26 +1468,47 @@
       <c r="AL10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="32"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40" t="n">
+        <f aca="false">A11+A13</f>
+        <v>7</v>
+      </c>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
+      <c r="F11" s="38" t="n">
+        <f aca="false">C11</f>
+        <v>7</v>
+      </c>
+      <c r="G11" s="39"/>
+      <c r="H11" s="40" t="n">
+        <f aca="false">F11+F13</f>
+        <v>10</v>
+      </c>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
-      <c r="K11" s="0"/>
-      <c r="L11" s="0"/>
-      <c r="M11" s="0"/>
+      <c r="K11" s="38" t="n">
+        <f aca="false">MAX(H11,H17,H23)</f>
+        <v>13</v>
+      </c>
+      <c r="L11" s="39"/>
+      <c r="M11" s="40" t="n">
+        <f aca="false">K11+K13</f>
+        <v>14</v>
+      </c>
       <c r="N11" s="0"/>
       <c r="O11" s="0"/>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="0"/>
-      <c r="R11" s="0"/>
+      <c r="P11" s="38" t="n">
+        <f aca="false">M11</f>
+        <v>14</v>
+      </c>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="40" t="n">
+        <f aca="false">P11+P13</f>
+        <v>15</v>
+      </c>
       <c r="S11" s="0"/>
       <c r="T11" s="0"/>
       <c r="U11" s="0"/>
@@ -1110,26 +1531,32 @@
       <c r="AL11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
+      <c r="F12" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="0"/>
-      <c r="L12" s="0"/>
-      <c r="M12" s="0"/>
+      <c r="K12" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
-      <c r="P12" s="0"/>
-      <c r="Q12" s="0"/>
-      <c r="R12" s="0"/>
+      <c r="P12" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41"/>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
       <c r="U12" s="0"/>
@@ -1151,27 +1578,48 @@
       <c r="AK12" s="0"/>
       <c r="AL12" s="0"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="n">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0"/>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0"/>
-      <c r="K13" s="0"/>
-      <c r="L13" s="0"/>
-      <c r="M13" s="0"/>
-      <c r="N13" s="0"/>
-      <c r="O13" s="0"/>
-      <c r="P13" s="0"/>
-      <c r="Q13" s="0"/>
-      <c r="R13" s="0"/>
+      <c r="B13" s="43" t="n">
+        <f aca="false">C14-C11</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="44"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="42" t="n">
+        <f aca="false">Q3</f>
+        <v>3</v>
+      </c>
+      <c r="G13" s="43" t="n">
+        <f aca="false">H14-H11</f>
+        <v>3</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="42" t="n">
+        <f aca="false">Q6</f>
+        <v>1</v>
+      </c>
+      <c r="L13" s="43" t="n">
+        <f aca="false">M14-M11</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="44"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="42" t="n">
+        <f aca="false">Q7</f>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="43" t="n">
+        <f aca="false">R14-R11</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="44"/>
       <c r="S13" s="0"/>
       <c r="T13" s="0"/>
       <c r="U13" s="0"/>
@@ -1194,26 +1642,48 @@
       <c r="AL13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
+      <c r="A14" s="48" t="n">
+        <f aca="false">C14-A13</f>
         <v>0</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="0"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="49" t="n">
+        <f aca="false">MIN(F26,F20,F14)</f>
+        <v>7</v>
+      </c>
+      <c r="D14" s="50"/>
       <c r="E14" s="0"/>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
+      <c r="F14" s="48" t="n">
+        <f aca="false">H14-F13</f>
+        <v>10</v>
+      </c>
+      <c r="G14" s="36"/>
+      <c r="H14" s="49" t="n">
+        <f aca="false">K14</f>
+        <v>13</v>
+      </c>
       <c r="I14" s="0"/>
-      <c r="J14" s="0"/>
-      <c r="K14" s="0"/>
-      <c r="L14" s="0"/>
-      <c r="M14" s="0"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="48" t="n">
+        <f aca="false">M14-K13</f>
+        <v>13</v>
+      </c>
+      <c r="L14" s="36"/>
+      <c r="M14" s="49" t="n">
+        <f aca="false">P14</f>
+        <v>14</v>
+      </c>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
-      <c r="P14" s="0"/>
-      <c r="Q14" s="0"/>
-      <c r="R14" s="0"/>
+      <c r="P14" s="48" t="n">
+        <f aca="false">R14-P13</f>
+        <v>14</v>
+      </c>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="49" t="n">
+        <f aca="false">R11</f>
+        <v>15</v>
+      </c>
       <c r="S14" s="0"/>
       <c r="T14" s="0"/>
       <c r="U14" s="0"/>
@@ -1236,13 +1706,13 @@
       <c r="AL14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="0"/>
+      <c r="D15" s="50"/>
       <c r="E15" s="0"/>
       <c r="F15" s="0"/>
       <c r="G15" s="0"/>
       <c r="H15" s="0"/>
       <c r="I15" s="0"/>
-      <c r="J15" s="0"/>
+      <c r="J15" s="51"/>
       <c r="K15" s="0"/>
       <c r="L15" s="0"/>
       <c r="M15" s="0"/>
@@ -1273,13 +1743,13 @@
       <c r="AL15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="0"/>
+      <c r="D16" s="50"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0"/>
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
-      <c r="J16" s="0"/>
+      <c r="J16" s="51"/>
       <c r="K16" s="0"/>
       <c r="L16" s="0"/>
       <c r="M16" s="0"/>
@@ -1310,13 +1780,19 @@
       <c r="AL16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="0"/>
+      <c r="D17" s="50"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="0"/>
-      <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
+      <c r="F17" s="38" t="n">
+        <f aca="false">C11</f>
+        <v>7</v>
+      </c>
+      <c r="G17" s="39"/>
+      <c r="H17" s="40" t="n">
+        <f aca="false">F17+F19</f>
+        <v>13</v>
+      </c>
       <c r="I17" s="0"/>
-      <c r="J17" s="0"/>
+      <c r="J17" s="51"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0"/>
       <c r="M17" s="0"/>
@@ -1347,13 +1823,15 @@
       <c r="AL17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="0"/>
+      <c r="D18" s="50"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="0"/>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
+      <c r="F18" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="0"/>
-      <c r="J18" s="0"/>
+      <c r="J18" s="51"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
       <c r="M18" s="0"/>
@@ -1380,14 +1858,20 @@
       <c r="AK18" s="0"/>
       <c r="AL18" s="0"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0"/>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-      <c r="I19" s="0"/>
-      <c r="J19" s="0"/>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="50"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="42" t="n">
+        <f aca="false">Q4</f>
+        <v>6</v>
+      </c>
+      <c r="G19" s="43" t="n">
+        <f aca="false">H20-H17</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="44"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="51"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0"/>
       <c r="M19" s="0"/>
@@ -1415,13 +1899,19 @@
       <c r="AL19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="0"/>
+      <c r="D20" s="50"/>
       <c r="E20" s="0"/>
-      <c r="F20" s="0"/>
-      <c r="G20" s="0"/>
-      <c r="H20" s="0"/>
+      <c r="F20" s="48" t="n">
+        <f aca="false">H20-F19</f>
+        <v>7</v>
+      </c>
+      <c r="G20" s="36"/>
+      <c r="H20" s="49" t="n">
+        <f aca="false">K14</f>
+        <v>13</v>
+      </c>
       <c r="I20" s="0"/>
-      <c r="J20" s="0"/>
+      <c r="J20" s="51"/>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
       <c r="M20" s="0"/>
@@ -1450,13 +1940,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
-      <c r="D21" s="0"/>
+      <c r="D21" s="50"/>
       <c r="E21" s="0"/>
       <c r="F21" s="0"/>
       <c r="G21" s="0"/>
       <c r="H21" s="0"/>
       <c r="I21" s="0"/>
-      <c r="J21" s="0"/>
+      <c r="J21" s="51"/>
       <c r="K21" s="0"/>
       <c r="L21" s="0"/>
       <c r="M21" s="0"/>
@@ -1485,13 +1975,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="D22" s="0"/>
+      <c r="D22" s="50"/>
       <c r="E22" s="0"/>
       <c r="F22" s="0"/>
       <c r="G22" s="0"/>
       <c r="H22" s="0"/>
       <c r="I22" s="0"/>
-      <c r="J22" s="0"/>
+      <c r="J22" s="51"/>
       <c r="K22" s="0"/>
       <c r="L22" s="0"/>
       <c r="M22" s="0"/>
@@ -1520,13 +2010,19 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="D23" s="0"/>
+      <c r="D23" s="50"/>
       <c r="E23" s="0"/>
-      <c r="F23" s="0"/>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
+      <c r="F23" s="38" t="n">
+        <f aca="false">C11</f>
+        <v>7</v>
+      </c>
+      <c r="G23" s="39"/>
+      <c r="H23" s="40" t="n">
+        <f aca="false">F23+F25</f>
+        <v>10</v>
+      </c>
       <c r="I23" s="0"/>
-      <c r="J23" s="0"/>
+      <c r="J23" s="51"/>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
       <c r="M23" s="0"/>
@@ -1541,13 +2037,15 @@
       <c r="A24" s="0"/>
       <c r="B24" s="0"/>
       <c r="C24" s="0"/>
-      <c r="D24" s="0"/>
+      <c r="D24" s="50"/>
       <c r="E24" s="0"/>
-      <c r="F24" s="0"/>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
+      <c r="F24" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
       <c r="I24" s="0"/>
-      <c r="J24" s="0"/>
+      <c r="J24" s="51"/>
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
       <c r="M24" s="0"/>
@@ -1558,16 +2056,22 @@
       <c r="R24" s="0"/>
       <c r="S24" s="0"/>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0"/>
       <c r="B25" s="0"/>
       <c r="C25" s="0"/>
       <c r="D25" s="0"/>
-      <c r="E25" s="0"/>
-      <c r="F25" s="0"/>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-      <c r="I25" s="0"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="42" t="n">
+        <f aca="false">Q5</f>
+        <v>3</v>
+      </c>
+      <c r="G25" s="43" t="n">
+        <f aca="false">H26-H23</f>
+        <v>3</v>
+      </c>
+      <c r="H25" s="44"/>
+      <c r="I25" s="46"/>
       <c r="J25" s="0"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
@@ -1585,9 +2089,15 @@
       <c r="C26" s="0"/>
       <c r="D26" s="0"/>
       <c r="E26" s="0"/>
-      <c r="F26" s="0"/>
-      <c r="G26" s="0"/>
-      <c r="H26" s="0"/>
+      <c r="F26" s="48" t="n">
+        <f aca="false">H26-F25</f>
+        <v>10</v>
+      </c>
+      <c r="G26" s="36"/>
+      <c r="H26" s="49" t="n">
+        <f aca="false">K14</f>
+        <v>13</v>
+      </c>
       <c r="I26" s="0"/>
       <c r="J26" s="0"/>
       <c r="K26" s="0"/>
@@ -1748,214 +2258,214 @@
       <c r="L37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="39"/>
-      <c r="B38" s="40"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
+      <c r="A38" s="52"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
+      <c r="L38" s="53"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="39"/>
+      <c r="A39" s="52"/>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="40"/>
+      <c r="L39" s="53"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="39"/>
-      <c r="B40" s="41" t="s">
+      <c r="A40" s="52"/>
+      <c r="B40" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="F40" s="42" t="s">
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="F40" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
-      <c r="L40" s="40"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="55"/>
+      <c r="L40" s="53"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="39"/>
-      <c r="B41" s="43" t="s">
+      <c r="A41" s="52"/>
+      <c r="B41" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="44" t="s">
+      <c r="C41" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="43" t="s">
+      <c r="D41" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="L41" s="40"/>
+      <c r="L41" s="53"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="39"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L42" s="40"/>
+      <c r="L42" s="53"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="39"/>
-      <c r="L43" s="40"/>
+      <c r="A43" s="52"/>
+      <c r="L43" s="53"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="39"/>
-      <c r="B44" s="45" t="s">
+      <c r="A44" s="52"/>
+      <c r="B44" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="C44" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="40"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="53"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="39"/>
-      <c r="B45" s="45" t="s">
+      <c r="A45" s="52"/>
+      <c r="B45" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="40"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="36"/>
+      <c r="J45" s="36"/>
+      <c r="K45" s="36"/>
+      <c r="L45" s="53"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="39"/>
-      <c r="B46" s="45" t="s">
+      <c r="A46" s="52"/>
+      <c r="B46" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="C46" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="40"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="53"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="39"/>
-      <c r="B47" s="45" t="s">
+      <c r="A47" s="52"/>
+      <c r="B47" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="36" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="40"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="36"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="53"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="39"/>
-      <c r="B48" s="43" t="s">
+      <c r="A48" s="52"/>
+      <c r="B48" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="28" t="s">
+      <c r="C48" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="40"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="36"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="36"/>
+      <c r="J48" s="36"/>
+      <c r="K48" s="36"/>
+      <c r="L48" s="53"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="39"/>
-      <c r="B49" s="44" t="s">
+      <c r="A49" s="52"/>
+      <c r="B49" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="28" t="s">
+      <c r="C49" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="40"/>
+      <c r="D49" s="36"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="36"/>
+      <c r="H49" s="36"/>
+      <c r="I49" s="36"/>
+      <c r="J49" s="36"/>
+      <c r="K49" s="36"/>
+      <c r="L49" s="53"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="39"/>
-      <c r="B50" s="46" t="s">
+      <c r="A50" s="52"/>
+      <c r="B50" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="40" t="s">
+      <c r="C50" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="40"/>
-      <c r="L50" s="40"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="53"/>
+      <c r="K50" s="53"/>
+      <c r="L50" s="53"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="39"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="40"/>
-      <c r="L51" s="40"/>
+      <c r="A51" s="52"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="53"/>
+      <c r="K51" s="53"/>
+      <c r="L51" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="23">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:P1"/>
@@ -1966,6 +2476,11 @@
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="F40:J40"/>
     <mergeCell ref="C44:K44"/>
@@ -1975,7 +2490,7 @@
     <mergeCell ref="C48:K48"/>
     <mergeCell ref="C49:K49"/>
   </mergeCells>
-  <conditionalFormatting sqref="B13">
+  <conditionalFormatting sqref="B13 G13 L13 Q13 G19 G25">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/Übungen/02_Netzplan_Firmennetzwerk.xlsx
+++ b/Übungen/02_Netzplan_Firmennetzwerk.xlsx
@@ -188,7 +188,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -198,7 +198,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAADCF7"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <bgColor rgb="FFDDDDDD"/>
       </patternFill>
     </fill>
     <fill>
@@ -211,6 +211,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF999999"/>
         <bgColor rgb="FFB2B2B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -388,7 +394,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -429,6 +435,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -461,6 +471,18 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -470,10 +492,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -489,6 +507,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -509,15 +531,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -533,6 +555,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -541,31 +567,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -597,15 +623,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -613,19 +639,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -642,12 +668,15 @@
   <dxfs count="1">
     <dxf>
       <font>
-        <name val="Alegreya Sans"/>
+        <name val="Arial"/>
         <charset val="1"/>
-        <family val="3"/>
-        <b val="1"/>
-        <color rgb="FFFF0000"/>
+        <family val="2"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDDDDD"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -675,7 +704,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -719,7 +748,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BN51"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="2" width="3.83"/>
@@ -730,7 +759,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="36" style="2" width="3.83"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="42.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -900,328 +929,328 @@
         <v>44652</v>
       </c>
       <c r="BM1" s="9"/>
-      <c r="BN1" s="9"/>
+      <c r="BN1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="15" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17" t="n">
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="R2" s="18"/>
-      <c r="S2" s="19"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="18"/>
-      <c r="Y2" s="18"/>
-      <c r="Z2" s="18"/>
-      <c r="AA2" s="18"/>
-      <c r="AB2" s="18"/>
-      <c r="AC2" s="18"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="18"/>
-      <c r="AH2" s="18"/>
-      <c r="AI2" s="18"/>
-      <c r="AJ2" s="18"/>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="19"/>
-      <c r="AN2" s="19"/>
-      <c r="AO2" s="19"/>
-      <c r="AP2" s="19"/>
-      <c r="AQ2" s="19"/>
-      <c r="AR2" s="19"/>
-      <c r="AS2" s="19"/>
-      <c r="AT2" s="19"/>
-      <c r="AU2" s="19"/>
-      <c r="AV2" s="19"/>
-      <c r="AW2" s="19"/>
-      <c r="AX2" s="19"/>
-      <c r="AY2" s="19"/>
-      <c r="AZ2" s="19"/>
-      <c r="BA2" s="19"/>
-      <c r="BB2" s="19"/>
-      <c r="BC2" s="19"/>
-      <c r="BD2" s="19"/>
-      <c r="BE2" s="19"/>
-      <c r="BF2" s="19"/>
-      <c r="BG2" s="19"/>
-      <c r="BH2" s="19"/>
-      <c r="BI2" s="19"/>
-      <c r="BJ2" s="19"/>
-      <c r="BK2" s="19"/>
-      <c r="BL2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="19"/>
+      <c r="Z2" s="19"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="22"/>
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="22"/>
+      <c r="AH2" s="22"/>
+      <c r="AI2" s="22"/>
+      <c r="AJ2" s="22"/>
+      <c r="AK2" s="22"/>
+      <c r="AL2" s="22"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
+      <c r="AQ2" s="23"/>
+      <c r="AR2" s="23"/>
+      <c r="AS2" s="23"/>
+      <c r="AT2" s="23"/>
+      <c r="AU2" s="23"/>
+      <c r="AV2" s="23"/>
+      <c r="AW2" s="23"/>
+      <c r="AX2" s="23"/>
+      <c r="AY2" s="23"/>
+      <c r="AZ2" s="23"/>
+      <c r="BA2" s="23"/>
+      <c r="BB2" s="23"/>
+      <c r="BC2" s="23"/>
+      <c r="BD2" s="23"/>
+      <c r="BE2" s="23"/>
+      <c r="BF2" s="23"/>
+      <c r="BG2" s="23"/>
+      <c r="BH2" s="23"/>
+      <c r="BI2" s="23"/>
+      <c r="BJ2" s="23"/>
+      <c r="BK2" s="23"/>
+      <c r="BL2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="23" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="26" t="s">
         <v>5</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="23" t="s">
+      <c r="L3" s="27"/>
+      <c r="M3" s="26" t="s">
         <v>10</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24" t="n">
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="R3" s="18"/>
-      <c r="S3" s="19"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="18"/>
-      <c r="X3" s="18"/>
-      <c r="Y3" s="18"/>
-      <c r="Z3" s="18"/>
-      <c r="AA3" s="18"/>
-      <c r="AB3" s="18"/>
-      <c r="AC3" s="18"/>
-      <c r="AD3" s="18"/>
-      <c r="AE3" s="18"/>
-      <c r="AF3" s="18"/>
-      <c r="AG3" s="18"/>
-      <c r="AH3" s="18"/>
-      <c r="AI3" s="18"/>
-      <c r="AJ3" s="18"/>
-      <c r="AK3" s="18"/>
-      <c r="AL3" s="18"/>
-      <c r="AM3" s="19"/>
-      <c r="AN3" s="19"/>
-      <c r="AO3" s="19"/>
-      <c r="AP3" s="19"/>
-      <c r="AQ3" s="19"/>
-      <c r="AR3" s="19"/>
-      <c r="AS3" s="19"/>
-      <c r="AT3" s="19"/>
-      <c r="AU3" s="19"/>
-      <c r="AV3" s="19"/>
-      <c r="AW3" s="19"/>
-      <c r="AX3" s="19"/>
-      <c r="AY3" s="19"/>
-      <c r="AZ3" s="19"/>
-      <c r="BA3" s="19"/>
-      <c r="BB3" s="19"/>
-      <c r="BC3" s="19"/>
-      <c r="BD3" s="19"/>
-      <c r="BE3" s="19"/>
-      <c r="BF3" s="19"/>
-      <c r="BG3" s="19"/>
-      <c r="BH3" s="19"/>
-      <c r="BI3" s="19"/>
-      <c r="BJ3" s="19"/>
-      <c r="BK3" s="19"/>
-      <c r="BL3" s="19"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="22"/>
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="22"/>
+      <c r="AE3" s="22"/>
+      <c r="AF3" s="22"/>
+      <c r="AG3" s="22"/>
+      <c r="AH3" s="22"/>
+      <c r="AI3" s="22"/>
+      <c r="AJ3" s="22"/>
+      <c r="AK3" s="22"/>
+      <c r="AL3" s="22"/>
+      <c r="AM3" s="23"/>
+      <c r="AN3" s="23"/>
+      <c r="AO3" s="23"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="23"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="23"/>
+      <c r="AT3" s="23"/>
+      <c r="AU3" s="23"/>
+      <c r="AV3" s="23"/>
+      <c r="AW3" s="23"/>
+      <c r="AX3" s="23"/>
+      <c r="AY3" s="23"/>
+      <c r="AZ3" s="23"/>
+      <c r="BA3" s="23"/>
+      <c r="BB3" s="23"/>
+      <c r="BC3" s="23"/>
+      <c r="BD3" s="23"/>
+      <c r="BE3" s="23"/>
+      <c r="BF3" s="23"/>
+      <c r="BG3" s="23"/>
+      <c r="BH3" s="23"/>
+      <c r="BI3" s="23"/>
+      <c r="BJ3" s="23"/>
+      <c r="BK3" s="23"/>
+      <c r="BL3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="23" t="s">
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="26" t="s">
         <v>5</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="23" t="s">
+      <c r="L4" s="27"/>
+      <c r="M4" s="26" t="s">
         <v>10</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24" t="n">
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="18"/>
-      <c r="S4" s="19"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="18"/>
-      <c r="X4" s="18"/>
-      <c r="Y4" s="18"/>
-      <c r="Z4" s="18"/>
-      <c r="AA4" s="18"/>
-      <c r="AB4" s="18"/>
-      <c r="AC4" s="18"/>
-      <c r="AD4" s="18"/>
-      <c r="AE4" s="18"/>
-      <c r="AF4" s="18"/>
-      <c r="AG4" s="18"/>
-      <c r="AH4" s="18"/>
-      <c r="AI4" s="18"/>
-      <c r="AJ4" s="18"/>
-      <c r="AK4" s="18"/>
-      <c r="AL4" s="18"/>
-      <c r="AM4" s="19"/>
-      <c r="AN4" s="19"/>
-      <c r="AO4" s="19"/>
-      <c r="AP4" s="19"/>
-      <c r="AQ4" s="19"/>
-      <c r="AR4" s="19"/>
-      <c r="AS4" s="19"/>
-      <c r="AT4" s="19"/>
-      <c r="AU4" s="19"/>
-      <c r="AV4" s="19"/>
-      <c r="AW4" s="19"/>
-      <c r="AX4" s="19"/>
-      <c r="AY4" s="19"/>
-      <c r="AZ4" s="19"/>
-      <c r="BA4" s="19"/>
-      <c r="BB4" s="19"/>
-      <c r="BC4" s="19"/>
-      <c r="BD4" s="19"/>
-      <c r="BE4" s="19"/>
-      <c r="BF4" s="19"/>
-      <c r="BG4" s="19"/>
-      <c r="BH4" s="19"/>
-      <c r="BI4" s="19"/>
-      <c r="BJ4" s="19"/>
-      <c r="BK4" s="19"/>
-      <c r="BL4" s="19"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="23"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="22"/>
+      <c r="Z4" s="22"/>
+      <c r="AA4" s="19"/>
+      <c r="AB4" s="19"/>
+      <c r="AC4" s="19"/>
+      <c r="AD4" s="22"/>
+      <c r="AE4" s="22"/>
+      <c r="AF4" s="19"/>
+      <c r="AG4" s="19"/>
+      <c r="AH4" s="19"/>
+      <c r="AI4" s="22"/>
+      <c r="AJ4" s="22"/>
+      <c r="AK4" s="22"/>
+      <c r="AL4" s="22"/>
+      <c r="AM4" s="23"/>
+      <c r="AN4" s="23"/>
+      <c r="AO4" s="23"/>
+      <c r="AP4" s="23"/>
+      <c r="AQ4" s="23"/>
+      <c r="AR4" s="23"/>
+      <c r="AS4" s="23"/>
+      <c r="AT4" s="23"/>
+      <c r="AU4" s="23"/>
+      <c r="AV4" s="23"/>
+      <c r="AW4" s="23"/>
+      <c r="AX4" s="23"/>
+      <c r="AY4" s="23"/>
+      <c r="AZ4" s="23"/>
+      <c r="BA4" s="23"/>
+      <c r="BB4" s="23"/>
+      <c r="BC4" s="23"/>
+      <c r="BD4" s="23"/>
+      <c r="BE4" s="23"/>
+      <c r="BF4" s="23"/>
+      <c r="BG4" s="23"/>
+      <c r="BH4" s="23"/>
+      <c r="BI4" s="23"/>
+      <c r="BJ4" s="23"/>
+      <c r="BK4" s="23"/>
+      <c r="BL4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="23" t="s">
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="26" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="23" t="s">
+      <c r="L5" s="27"/>
+      <c r="M5" s="26" t="s">
         <v>10</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24" t="n">
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="R5" s="18"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="18"/>
-      <c r="X5" s="18"/>
-      <c r="Y5" s="18"/>
-      <c r="Z5" s="18"/>
-      <c r="AA5" s="18"/>
-      <c r="AB5" s="18"/>
-      <c r="AC5" s="18"/>
-      <c r="AD5" s="18"/>
-      <c r="AE5" s="18"/>
-      <c r="AF5" s="18"/>
-      <c r="AG5" s="18"/>
-      <c r="AH5" s="18"/>
-      <c r="AI5" s="18"/>
-      <c r="AJ5" s="18"/>
-      <c r="AK5" s="18"/>
-      <c r="AL5" s="18"/>
-      <c r="AM5" s="19"/>
-      <c r="AN5" s="19"/>
-      <c r="AO5" s="19"/>
-      <c r="AP5" s="19"/>
-      <c r="AQ5" s="19"/>
-      <c r="AR5" s="19"/>
-      <c r="AS5" s="19"/>
-      <c r="AT5" s="19"/>
-      <c r="AU5" s="19"/>
-      <c r="AV5" s="19"/>
-      <c r="AW5" s="19"/>
-      <c r="AX5" s="19"/>
-      <c r="AY5" s="19"/>
-      <c r="AZ5" s="19"/>
-      <c r="BA5" s="19"/>
-      <c r="BB5" s="19"/>
-      <c r="BC5" s="19"/>
-      <c r="BD5" s="19"/>
-      <c r="BE5" s="19"/>
-      <c r="BF5" s="19"/>
-      <c r="BG5" s="19"/>
-      <c r="BH5" s="19"/>
-      <c r="BI5" s="19"/>
-      <c r="BJ5" s="19"/>
-      <c r="BK5" s="19"/>
-      <c r="BL5" s="19"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="22"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="19"/>
+      <c r="AB5" s="19"/>
+      <c r="AC5" s="19"/>
+      <c r="AD5" s="22"/>
+      <c r="AE5" s="22"/>
+      <c r="AF5" s="22"/>
+      <c r="AG5" s="22"/>
+      <c r="AH5" s="22"/>
+      <c r="AI5" s="22"/>
+      <c r="AJ5" s="22"/>
+      <c r="AK5" s="22"/>
+      <c r="AL5" s="22"/>
+      <c r="AM5" s="23"/>
+      <c r="AN5" s="23"/>
+      <c r="AO5" s="23"/>
+      <c r="AP5" s="23"/>
+      <c r="AQ5" s="23"/>
+      <c r="AR5" s="23"/>
+      <c r="AS5" s="23"/>
+      <c r="AT5" s="23"/>
+      <c r="AU5" s="23"/>
+      <c r="AV5" s="23"/>
+      <c r="AW5" s="23"/>
+      <c r="AX5" s="23"/>
+      <c r="AY5" s="23"/>
+      <c r="AZ5" s="23"/>
+      <c r="BA5" s="23"/>
+      <c r="BB5" s="23"/>
+      <c r="BC5" s="23"/>
+      <c r="BD5" s="23"/>
+      <c r="BE5" s="23"/>
+      <c r="BF5" s="23"/>
+      <c r="BG5" s="23"/>
+      <c r="BH5" s="23"/>
+      <c r="BI5" s="23"/>
+      <c r="BJ5" s="23"/>
+      <c r="BK5" s="23"/>
+      <c r="BL5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="23" t="s">
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="26" t="s">
         <v>7</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1230,150 +1259,150 @@
       <c r="K6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="24"/>
-      <c r="M6" s="23" t="s">
+      <c r="L6" s="27"/>
+      <c r="M6" s="26" t="s">
         <v>14</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24" t="n">
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="R6" s="18"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="18"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="18"/>
-      <c r="AA6" s="18"/>
-      <c r="AB6" s="18"/>
-      <c r="AC6" s="18"/>
-      <c r="AD6" s="18"/>
-      <c r="AE6" s="18"/>
-      <c r="AF6" s="18"/>
-      <c r="AG6" s="18"/>
-      <c r="AH6" s="18"/>
-      <c r="AI6" s="18"/>
-      <c r="AJ6" s="18"/>
-      <c r="AK6" s="18"/>
-      <c r="AL6" s="18"/>
-      <c r="AM6" s="19"/>
-      <c r="AN6" s="19"/>
-      <c r="AO6" s="19"/>
-      <c r="AP6" s="19"/>
-      <c r="AQ6" s="19"/>
-      <c r="AR6" s="19"/>
-      <c r="AS6" s="19"/>
-      <c r="AT6" s="19"/>
-      <c r="AU6" s="19"/>
-      <c r="AV6" s="19"/>
-      <c r="AW6" s="19"/>
-      <c r="AX6" s="19"/>
-      <c r="AY6" s="19"/>
-      <c r="AZ6" s="19"/>
-      <c r="BA6" s="19"/>
-      <c r="BB6" s="19"/>
-      <c r="BC6" s="19"/>
-      <c r="BD6" s="19"/>
-      <c r="BE6" s="19"/>
-      <c r="BF6" s="19"/>
-      <c r="BG6" s="19"/>
-      <c r="BH6" s="19"/>
-      <c r="BI6" s="19"/>
-      <c r="BJ6" s="19"/>
-      <c r="BK6" s="19"/>
-      <c r="BL6" s="19"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="22"/>
+      <c r="AE6" s="22"/>
+      <c r="AF6" s="22"/>
+      <c r="AG6" s="22"/>
+      <c r="AH6" s="22"/>
+      <c r="AI6" s="19"/>
+      <c r="AJ6" s="22"/>
+      <c r="AK6" s="22"/>
+      <c r="AL6" s="22"/>
+      <c r="AM6" s="23"/>
+      <c r="AN6" s="23"/>
+      <c r="AO6" s="23"/>
+      <c r="AP6" s="23"/>
+      <c r="AQ6" s="23"/>
+      <c r="AR6" s="23"/>
+      <c r="AS6" s="23"/>
+      <c r="AT6" s="23"/>
+      <c r="AU6" s="23"/>
+      <c r="AV6" s="23"/>
+      <c r="AW6" s="23"/>
+      <c r="AX6" s="23"/>
+      <c r="AY6" s="23"/>
+      <c r="AZ6" s="23"/>
+      <c r="BA6" s="23"/>
+      <c r="BB6" s="23"/>
+      <c r="BC6" s="23"/>
+      <c r="BD6" s="23"/>
+      <c r="BE6" s="23"/>
+      <c r="BF6" s="23"/>
+      <c r="BG6" s="23"/>
+      <c r="BH6" s="23"/>
+      <c r="BI6" s="23"/>
+      <c r="BJ6" s="23"/>
+      <c r="BK6" s="23"/>
+      <c r="BL6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="27" t="s">
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="29" t="n">
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="33"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="35"/>
-      <c r="U7" s="35"/>
-      <c r="V7" s="35"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="33"/>
-      <c r="AB7" s="33"/>
-      <c r="AC7" s="33"/>
-      <c r="AD7" s="33"/>
-      <c r="AE7" s="33"/>
-      <c r="AF7" s="33"/>
-      <c r="AG7" s="33"/>
-      <c r="AH7" s="33"/>
-      <c r="AI7" s="33"/>
-      <c r="AJ7" s="33"/>
-      <c r="AK7" s="33"/>
-      <c r="AL7" s="33"/>
-      <c r="AM7" s="34"/>
-      <c r="AN7" s="34"/>
-      <c r="AO7" s="34"/>
-      <c r="AP7" s="34"/>
-      <c r="AQ7" s="34"/>
-      <c r="AR7" s="34"/>
-      <c r="AS7" s="34"/>
-      <c r="AT7" s="34"/>
-      <c r="AU7" s="34"/>
-      <c r="AV7" s="34"/>
-      <c r="AW7" s="34"/>
-      <c r="AX7" s="34"/>
-      <c r="AY7" s="34"/>
-      <c r="AZ7" s="34"/>
-      <c r="BA7" s="34"/>
-      <c r="BB7" s="34"/>
-      <c r="BC7" s="34"/>
-      <c r="BD7" s="34"/>
-      <c r="BE7" s="34"/>
-      <c r="BF7" s="34"/>
-      <c r="BG7" s="34"/>
-      <c r="BH7" s="34"/>
-      <c r="BI7" s="34"/>
-      <c r="BJ7" s="34"/>
-      <c r="BK7" s="34"/>
-      <c r="BL7" s="34"/>
+      <c r="R7" s="37"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="39"/>
+      <c r="U7" s="39"/>
+      <c r="V7" s="39"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="37"/>
+      <c r="Y7" s="37"/>
+      <c r="Z7" s="37"/>
+      <c r="AA7" s="37"/>
+      <c r="AB7" s="37"/>
+      <c r="AC7" s="37"/>
+      <c r="AD7" s="37"/>
+      <c r="AE7" s="37"/>
+      <c r="AF7" s="37"/>
+      <c r="AG7" s="37"/>
+      <c r="AH7" s="37"/>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="37"/>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="38"/>
+      <c r="AN7" s="38"/>
+      <c r="AO7" s="38"/>
+      <c r="AP7" s="38"/>
+      <c r="AQ7" s="38"/>
+      <c r="AR7" s="38"/>
+      <c r="AS7" s="38"/>
+      <c r="AT7" s="38"/>
+      <c r="AU7" s="38"/>
+      <c r="AV7" s="38"/>
+      <c r="AW7" s="38"/>
+      <c r="AX7" s="38"/>
+      <c r="AY7" s="38"/>
+      <c r="AZ7" s="38"/>
+      <c r="BA7" s="38"/>
+      <c r="BB7" s="38"/>
+      <c r="BC7" s="38"/>
+      <c r="BD7" s="38"/>
+      <c r="BE7" s="38"/>
+      <c r="BF7" s="38"/>
+      <c r="BG7" s="38"/>
+      <c r="BH7" s="38"/>
+      <c r="BI7" s="38"/>
+      <c r="BJ7" s="38"/>
+      <c r="BK7" s="38"/>
+      <c r="BL7" s="38"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="37"/>
+      <c r="B8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="42"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="42"/>
       <c r="T8" s="2"/>
       <c r="W8" s="0"/>
       <c r="X8" s="0"/>
@@ -1393,7 +1422,7 @@
       <c r="AL8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="36"/>
+      <c r="B9" s="41"/>
       <c r="D9" s="0"/>
       <c r="E9" s="0"/>
       <c r="F9" s="0"/>
@@ -1468,44 +1497,44 @@
       <c r="AL10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="38" t="n">
+      <c r="A11" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="40" t="n">
+      <c r="B11" s="44"/>
+      <c r="C11" s="45" t="n">
         <f aca="false">A11+A13</f>
         <v>7</v>
       </c>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="38" t="n">
+      <c r="F11" s="43" t="n">
         <f aca="false">C11</f>
         <v>7</v>
       </c>
-      <c r="G11" s="39"/>
-      <c r="H11" s="40" t="n">
+      <c r="G11" s="44"/>
+      <c r="H11" s="45" t="n">
         <f aca="false">F11+F13</f>
         <v>10</v>
       </c>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
-      <c r="K11" s="38" t="n">
+      <c r="K11" s="43" t="n">
         <f aca="false">MAX(H11,H17,H23)</f>
         <v>13</v>
       </c>
-      <c r="L11" s="39"/>
-      <c r="M11" s="40" t="n">
+      <c r="L11" s="44"/>
+      <c r="M11" s="45" t="n">
         <f aca="false">K11+K13</f>
         <v>14</v>
       </c>
       <c r="N11" s="0"/>
       <c r="O11" s="0"/>
-      <c r="P11" s="38" t="n">
+      <c r="P11" s="43" t="n">
         <f aca="false">M11</f>
         <v>14</v>
       </c>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="40" t="n">
+      <c r="Q11" s="44"/>
+      <c r="R11" s="45" t="n">
         <f aca="false">P11+P13</f>
         <v>15</v>
       </c>
@@ -1531,32 +1560,32 @@
       <c r="AL11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="41" t="s">
+      <c r="F12" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="41" t="s">
+      <c r="K12" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
-      <c r="P12" s="41" t="s">
+      <c r="P12" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="41"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
       <c r="U12" s="0"/>
@@ -1579,47 +1608,47 @@
       <c r="AL12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="n">
+      <c r="A13" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="43" t="n">
+      <c r="B13" s="48" t="n">
         <f aca="false">C14-C11</f>
         <v>0</v>
       </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="42" t="n">
+      <c r="C13" s="49"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="47" t="n">
         <f aca="false">Q3</f>
         <v>3</v>
       </c>
-      <c r="G13" s="43" t="n">
+      <c r="G13" s="48" t="n">
         <f aca="false">H14-H11</f>
         <v>3</v>
       </c>
-      <c r="H13" s="44"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="42" t="n">
+      <c r="H13" s="49"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="47" t="n">
         <f aca="false">Q6</f>
         <v>1</v>
       </c>
-      <c r="L13" s="43" t="n">
+      <c r="L13" s="48" t="n">
         <f aca="false">M14-M11</f>
         <v>0</v>
       </c>
-      <c r="M13" s="44"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="42" t="n">
+      <c r="M13" s="49"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="51"/>
+      <c r="P13" s="47" t="n">
         <f aca="false">Q7</f>
         <v>1</v>
       </c>
-      <c r="Q13" s="43" t="n">
+      <c r="Q13" s="48" t="n">
         <f aca="false">R14-R11</f>
         <v>0</v>
       </c>
-      <c r="R13" s="44"/>
+      <c r="R13" s="49"/>
       <c r="S13" s="0"/>
       <c r="T13" s="0"/>
       <c r="U13" s="0"/>
@@ -1642,45 +1671,45 @@
       <c r="AL13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="48" t="n">
+      <c r="A14" s="53" t="n">
         <f aca="false">C14-A13</f>
         <v>0</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="49" t="n">
+      <c r="B14" s="41"/>
+      <c r="C14" s="54" t="n">
         <f aca="false">MIN(F26,F20,F14)</f>
         <v>7</v>
       </c>
-      <c r="D14" s="50"/>
+      <c r="D14" s="55"/>
       <c r="E14" s="0"/>
-      <c r="F14" s="48" t="n">
+      <c r="F14" s="53" t="n">
         <f aca="false">H14-F13</f>
         <v>10</v>
       </c>
-      <c r="G14" s="36"/>
-      <c r="H14" s="49" t="n">
+      <c r="G14" s="41"/>
+      <c r="H14" s="54" t="n">
         <f aca="false">K14</f>
         <v>13</v>
       </c>
       <c r="I14" s="0"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="48" t="n">
+      <c r="J14" s="56"/>
+      <c r="K14" s="53" t="n">
         <f aca="false">M14-K13</f>
         <v>13</v>
       </c>
-      <c r="L14" s="36"/>
-      <c r="M14" s="49" t="n">
+      <c r="L14" s="41"/>
+      <c r="M14" s="54" t="n">
         <f aca="false">P14</f>
         <v>14</v>
       </c>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
-      <c r="P14" s="48" t="n">
+      <c r="P14" s="53" t="n">
         <f aca="false">R14-P13</f>
         <v>14</v>
       </c>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="49" t="n">
+      <c r="Q14" s="41"/>
+      <c r="R14" s="54" t="n">
         <f aca="false">R11</f>
         <v>15</v>
       </c>
@@ -1706,13 +1735,13 @@
       <c r="AL14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="50"/>
+      <c r="D15" s="55"/>
       <c r="E15" s="0"/>
       <c r="F15" s="0"/>
       <c r="G15" s="0"/>
       <c r="H15" s="0"/>
       <c r="I15" s="0"/>
-      <c r="J15" s="51"/>
+      <c r="J15" s="56"/>
       <c r="K15" s="0"/>
       <c r="L15" s="0"/>
       <c r="M15" s="0"/>
@@ -1743,13 +1772,13 @@
       <c r="AL15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="50"/>
+      <c r="D16" s="55"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0"/>
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
-      <c r="J16" s="51"/>
+      <c r="J16" s="56"/>
       <c r="K16" s="0"/>
       <c r="L16" s="0"/>
       <c r="M16" s="0"/>
@@ -1780,19 +1809,19 @@
       <c r="AL16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="50"/>
+      <c r="D17" s="55"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="38" t="n">
+      <c r="F17" s="43" t="n">
         <f aca="false">C11</f>
         <v>7</v>
       </c>
-      <c r="G17" s="39"/>
-      <c r="H17" s="40" t="n">
+      <c r="G17" s="44"/>
+      <c r="H17" s="45" t="n">
         <f aca="false">F17+F19</f>
         <v>13</v>
       </c>
       <c r="I17" s="0"/>
-      <c r="J17" s="51"/>
+      <c r="J17" s="56"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0"/>
       <c r="M17" s="0"/>
@@ -1823,15 +1852,15 @@
       <c r="AL17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="50"/>
+      <c r="D18" s="55"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
       <c r="I18" s="0"/>
-      <c r="J18" s="51"/>
+      <c r="J18" s="56"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
       <c r="M18" s="0"/>
@@ -1859,19 +1888,19 @@
       <c r="AL18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="50"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="42" t="n">
+      <c r="D19" s="55"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="47" t="n">
         <f aca="false">Q4</f>
         <v>6</v>
       </c>
-      <c r="G19" s="43" t="n">
+      <c r="G19" s="48" t="n">
         <f aca="false">H20-H17</f>
         <v>0</v>
       </c>
-      <c r="H19" s="44"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="51"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="56"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0"/>
       <c r="M19" s="0"/>
@@ -1899,19 +1928,19 @@
       <c r="AL19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="50"/>
+      <c r="D20" s="55"/>
       <c r="E20" s="0"/>
-      <c r="F20" s="48" t="n">
+      <c r="F20" s="53" t="n">
         <f aca="false">H20-F19</f>
         <v>7</v>
       </c>
-      <c r="G20" s="36"/>
-      <c r="H20" s="49" t="n">
+      <c r="G20" s="41"/>
+      <c r="H20" s="54" t="n">
         <f aca="false">K14</f>
         <v>13</v>
       </c>
       <c r="I20" s="0"/>
-      <c r="J20" s="51"/>
+      <c r="J20" s="56"/>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
       <c r="M20" s="0"/>
@@ -1940,13 +1969,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
-      <c r="D21" s="50"/>
+      <c r="D21" s="55"/>
       <c r="E21" s="0"/>
       <c r="F21" s="0"/>
       <c r="G21" s="0"/>
       <c r="H21" s="0"/>
       <c r="I21" s="0"/>
-      <c r="J21" s="51"/>
+      <c r="J21" s="56"/>
       <c r="K21" s="0"/>
       <c r="L21" s="0"/>
       <c r="M21" s="0"/>
@@ -1975,13 +2004,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="D22" s="50"/>
+      <c r="D22" s="55"/>
       <c r="E22" s="0"/>
       <c r="F22" s="0"/>
       <c r="G22" s="0"/>
       <c r="H22" s="0"/>
       <c r="I22" s="0"/>
-      <c r="J22" s="51"/>
+      <c r="J22" s="56"/>
       <c r="K22" s="0"/>
       <c r="L22" s="0"/>
       <c r="M22" s="0"/>
@@ -2010,19 +2039,19 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="D23" s="50"/>
+      <c r="D23" s="55"/>
       <c r="E23" s="0"/>
-      <c r="F23" s="38" t="n">
+      <c r="F23" s="43" t="n">
         <f aca="false">C11</f>
         <v>7</v>
       </c>
-      <c r="G23" s="39"/>
-      <c r="H23" s="40" t="n">
+      <c r="G23" s="44"/>
+      <c r="H23" s="45" t="n">
         <f aca="false">F23+F25</f>
         <v>10</v>
       </c>
       <c r="I23" s="0"/>
-      <c r="J23" s="51"/>
+      <c r="J23" s="56"/>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
       <c r="M23" s="0"/>
@@ -2037,15 +2066,15 @@
       <c r="A24" s="0"/>
       <c r="B24" s="0"/>
       <c r="C24" s="0"/>
-      <c r="D24" s="50"/>
+      <c r="D24" s="55"/>
       <c r="E24" s="0"/>
-      <c r="F24" s="41" t="s">
+      <c r="F24" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
       <c r="I24" s="0"/>
-      <c r="J24" s="51"/>
+      <c r="J24" s="56"/>
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
       <c r="M24" s="0"/>
@@ -2061,17 +2090,17 @@
       <c r="B25" s="0"/>
       <c r="C25" s="0"/>
       <c r="D25" s="0"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="42" t="n">
+      <c r="E25" s="51"/>
+      <c r="F25" s="47" t="n">
         <f aca="false">Q5</f>
         <v>3</v>
       </c>
-      <c r="G25" s="43" t="n">
+      <c r="G25" s="48" t="n">
         <f aca="false">H26-H23</f>
         <v>3</v>
       </c>
-      <c r="H25" s="44"/>
-      <c r="I25" s="46"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="51"/>
       <c r="J25" s="0"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
@@ -2089,12 +2118,12 @@
       <c r="C26" s="0"/>
       <c r="D26" s="0"/>
       <c r="E26" s="0"/>
-      <c r="F26" s="48" t="n">
+      <c r="F26" s="53" t="n">
         <f aca="false">H26-F25</f>
         <v>10</v>
       </c>
-      <c r="G26" s="36"/>
-      <c r="H26" s="49" t="n">
+      <c r="G26" s="41"/>
+      <c r="H26" s="54" t="n">
         <f aca="false">K14</f>
         <v>13</v>
       </c>
@@ -2258,211 +2287,211 @@
       <c r="L37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="52"/>
-      <c r="B38" s="53"/>
-      <c r="C38" s="53"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="53"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="53"/>
-      <c r="I38" s="53"/>
-      <c r="J38" s="53"/>
-      <c r="K38" s="53"/>
-      <c r="L38" s="53"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="58"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="52"/>
+      <c r="A39" s="57"/>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="53"/>
+      <c r="L39" s="58"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="52"/>
-      <c r="B40" s="54" t="s">
+      <c r="A40" s="57"/>
+      <c r="B40" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="F40" s="55" t="s">
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="F40" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
-      <c r="L40" s="53"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="60"/>
+      <c r="L40" s="58"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="52"/>
-      <c r="B41" s="56" t="s">
+      <c r="A41" s="57"/>
+      <c r="B41" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="57" t="s">
+      <c r="C41" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="56" t="s">
+      <c r="D41" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="L41" s="53"/>
+      <c r="L41" s="58"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="52"/>
+      <c r="A42" s="57"/>
       <c r="B42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L42" s="53"/>
+      <c r="L42" s="58"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="52"/>
-      <c r="L43" s="53"/>
+      <c r="A43" s="57"/>
+      <c r="L43" s="58"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="52"/>
-      <c r="B44" s="58" t="s">
+      <c r="A44" s="57"/>
+      <c r="B44" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="36" t="s">
+      <c r="C44" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="53"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="41"/>
+      <c r="K44" s="41"/>
+      <c r="L44" s="58"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="52"/>
-      <c r="B45" s="58" t="s">
+      <c r="A45" s="57"/>
+      <c r="B45" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="36" t="s">
+      <c r="C45" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="36"/>
-      <c r="H45" s="36"/>
-      <c r="I45" s="36"/>
-      <c r="J45" s="36"/>
-      <c r="K45" s="36"/>
-      <c r="L45" s="53"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="41"/>
+      <c r="J45" s="41"/>
+      <c r="K45" s="41"/>
+      <c r="L45" s="58"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="52"/>
-      <c r="B46" s="58" t="s">
+      <c r="A46" s="57"/>
+      <c r="B46" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="36" t="s">
+      <c r="C46" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="53"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="41"/>
+      <c r="K46" s="41"/>
+      <c r="L46" s="58"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="52"/>
-      <c r="B47" s="58" t="s">
+      <c r="A47" s="57"/>
+      <c r="B47" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="36" t="s">
+      <c r="C47" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
-      <c r="J47" s="36"/>
-      <c r="K47" s="36"/>
-      <c r="L47" s="53"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="41"/>
+      <c r="J47" s="41"/>
+      <c r="K47" s="41"/>
+      <c r="L47" s="58"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="52"/>
-      <c r="B48" s="56" t="s">
+      <c r="A48" s="57"/>
+      <c r="B48" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="36" t="s">
+      <c r="C48" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
-      <c r="J48" s="36"/>
-      <c r="K48" s="36"/>
-      <c r="L48" s="53"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="41"/>
+      <c r="J48" s="41"/>
+      <c r="K48" s="41"/>
+      <c r="L48" s="58"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="52"/>
-      <c r="B49" s="57" t="s">
+      <c r="A49" s="57"/>
+      <c r="B49" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="C49" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="36"/>
-      <c r="K49" s="36"/>
-      <c r="L49" s="53"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="58"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="52"/>
-      <c r="B50" s="59" t="s">
+      <c r="A50" s="57"/>
+      <c r="B50" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="53" t="s">
+      <c r="C50" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
-      <c r="H50" s="53"/>
-      <c r="I50" s="53"/>
-      <c r="J50" s="53"/>
-      <c r="K50" s="53"/>
-      <c r="L50" s="53"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="58"/>
+      <c r="H50" s="58"/>
+      <c r="I50" s="58"/>
+      <c r="J50" s="58"/>
+      <c r="K50" s="58"/>
+      <c r="L50" s="58"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="52"/>
-      <c r="B51" s="53"/>
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="53"/>
-      <c r="H51" s="53"/>
-      <c r="I51" s="53"/>
-      <c r="J51" s="53"/>
-      <c r="K51" s="53"/>
-      <c r="L51" s="53"/>
+      <c r="A51" s="57"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="58"/>
+      <c r="J51" s="58"/>
+      <c r="K51" s="58"/>
+      <c r="L51" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -2490,9 +2519,9 @@
     <mergeCell ref="C48:K48"/>
     <mergeCell ref="C49:K49"/>
   </mergeCells>
-  <conditionalFormatting sqref="B13 G13 L13 Q13 G19 G25">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>0</formula>
+  <conditionalFormatting sqref="R1:BL7">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>IF(WEEKDAY(R$1,2)=6,1,IF(WEEKDAY(R$1,2)=7,1,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Übungen/02_Netzplan_Firmennetzwerk.xlsx
+++ b/Übungen/02_Netzplan_Firmennetzwerk.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -119,8 +119,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -186,7 +188,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,7 +198,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAADCF7"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF729FCF"/>
+        <bgColor rgb="FF999999"/>
       </patternFill>
     </fill>
     <fill>
@@ -224,7 +232,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="18">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -316,6 +324,41 @@
       <bottom style="hair"/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top style="thick"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thick"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thick"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -345,7 +388,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="65">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -378,6 +421,18 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -386,15 +441,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -410,6 +465,26 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -446,16 +521,36 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -466,51 +561,71 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -518,19 +633,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -547,12 +662,15 @@
   <dxfs count="1">
     <dxf>
       <font>
-        <name val="Alegreya Sans"/>
+        <name val="Arial"/>
         <charset val="1"/>
-        <family val="3"/>
-        <b val="1"/>
-        <color rgb="FFFF0000"/>
+        <family val="2"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDDDDD"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -573,14 +691,14 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB2B2B2"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF729FCF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -623,19 +741,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AL51"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BN51"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="2" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="3" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="4.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="3.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="20" style="4" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="36" style="2" width="3.83"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -663,225 +781,470 @@
       <c r="Q1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R1" s="0"/>
-      <c r="T1" s="2"/>
-      <c r="W1" s="0"/>
-      <c r="X1" s="0"/>
-      <c r="Y1" s="0"/>
-      <c r="Z1" s="0"/>
-      <c r="AA1" s="0"/>
-      <c r="AB1" s="0"/>
-      <c r="AC1" s="0"/>
-      <c r="AD1" s="0"/>
-      <c r="AE1" s="0"/>
-      <c r="AF1" s="0"/>
-      <c r="AG1" s="0"/>
-      <c r="AH1" s="0"/>
-      <c r="AI1" s="0"/>
-      <c r="AJ1" s="0"/>
-      <c r="AK1" s="0"/>
-      <c r="AL1" s="0"/>
+      <c r="R1" s="8" t="n">
+        <v>44606</v>
+      </c>
+      <c r="S1" s="8" t="n">
+        <v>44607</v>
+      </c>
+      <c r="T1" s="8" t="n">
+        <v>44608</v>
+      </c>
+      <c r="U1" s="8" t="n">
+        <v>44609</v>
+      </c>
+      <c r="V1" s="8" t="n">
+        <v>44610</v>
+      </c>
+      <c r="W1" s="8" t="n">
+        <v>44611</v>
+      </c>
+      <c r="X1" s="8" t="n">
+        <v>44612</v>
+      </c>
+      <c r="Y1" s="8" t="n">
+        <v>44613</v>
+      </c>
+      <c r="Z1" s="8" t="n">
+        <v>44614</v>
+      </c>
+      <c r="AA1" s="8" t="n">
+        <v>44615</v>
+      </c>
+      <c r="AB1" s="8" t="n">
+        <v>44616</v>
+      </c>
+      <c r="AC1" s="8" t="n">
+        <v>44617</v>
+      </c>
+      <c r="AD1" s="8" t="n">
+        <v>44618</v>
+      </c>
+      <c r="AE1" s="8" t="n">
+        <v>44619</v>
+      </c>
+      <c r="AF1" s="8" t="n">
+        <v>44620</v>
+      </c>
+      <c r="AG1" s="8" t="n">
+        <v>44621</v>
+      </c>
+      <c r="AH1" s="8" t="n">
+        <v>44622</v>
+      </c>
+      <c r="AI1" s="8" t="n">
+        <v>44623</v>
+      </c>
+      <c r="AJ1" s="8" t="n">
+        <v>44624</v>
+      </c>
+      <c r="AK1" s="8" t="n">
+        <v>44625</v>
+      </c>
+      <c r="AL1" s="8" t="n">
+        <v>44626</v>
+      </c>
+      <c r="AM1" s="8" t="n">
+        <v>44627</v>
+      </c>
+      <c r="AN1" s="8" t="n">
+        <v>44628</v>
+      </c>
+      <c r="AO1" s="8" t="n">
+        <v>44629</v>
+      </c>
+      <c r="AP1" s="8" t="n">
+        <v>44630</v>
+      </c>
+      <c r="AQ1" s="8" t="n">
+        <v>44631</v>
+      </c>
+      <c r="AR1" s="8" t="n">
+        <v>44632</v>
+      </c>
+      <c r="AS1" s="8" t="n">
+        <v>44633</v>
+      </c>
+      <c r="AT1" s="8" t="n">
+        <v>44634</v>
+      </c>
+      <c r="AU1" s="8" t="n">
+        <v>44635</v>
+      </c>
+      <c r="AV1" s="8" t="n">
+        <v>44636</v>
+      </c>
+      <c r="AW1" s="8" t="n">
+        <v>44637</v>
+      </c>
+      <c r="AX1" s="8" t="n">
+        <v>44638</v>
+      </c>
+      <c r="AY1" s="8" t="n">
+        <v>44639</v>
+      </c>
+      <c r="AZ1" s="8" t="n">
+        <v>44640</v>
+      </c>
+      <c r="BA1" s="8" t="n">
+        <v>44641</v>
+      </c>
+      <c r="BB1" s="8" t="n">
+        <v>44642</v>
+      </c>
+      <c r="BC1" s="8" t="n">
+        <v>44643</v>
+      </c>
+      <c r="BD1" s="8" t="n">
+        <v>44644</v>
+      </c>
+      <c r="BE1" s="8" t="n">
+        <v>44645</v>
+      </c>
+      <c r="BF1" s="8" t="n">
+        <v>44646</v>
+      </c>
+      <c r="BG1" s="8" t="n">
+        <v>44647</v>
+      </c>
+      <c r="BH1" s="8" t="n">
+        <v>44648</v>
+      </c>
+      <c r="BI1" s="8" t="n">
+        <v>44649</v>
+      </c>
+      <c r="BJ1" s="8" t="n">
+        <v>44650</v>
+      </c>
+      <c r="BK1" s="8" t="n">
+        <v>44651</v>
+      </c>
+      <c r="BL1" s="8" t="n">
+        <v>44652</v>
+      </c>
+      <c r="BM1" s="9"/>
+      <c r="BN1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="13" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15" t="n">
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="R2" s="0"/>
-      <c r="W2" s="0"/>
-      <c r="X2" s="0"/>
-      <c r="Y2" s="0"/>
-      <c r="Z2" s="0"/>
-      <c r="AA2" s="0"/>
-      <c r="AB2" s="0"/>
-      <c r="AC2" s="0"/>
-      <c r="AD2" s="0"/>
-      <c r="AE2" s="0"/>
-      <c r="AF2" s="0"/>
-      <c r="AG2" s="0"/>
-      <c r="AH2" s="0"/>
-      <c r="AI2" s="0"/>
-      <c r="AJ2" s="0"/>
-      <c r="AK2" s="0"/>
-      <c r="AL2" s="0"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
+      <c r="Z2" s="19"/>
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="19"/>
+      <c r="AC2" s="19"/>
+      <c r="AD2" s="19"/>
+      <c r="AE2" s="19"/>
+      <c r="AF2" s="19"/>
+      <c r="AG2" s="19"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="19"/>
+      <c r="AJ2" s="19"/>
+      <c r="AK2" s="22"/>
+      <c r="AL2" s="22"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
+      <c r="AQ2" s="23"/>
+      <c r="AR2" s="23"/>
+      <c r="AS2" s="23"/>
+      <c r="AT2" s="23"/>
+      <c r="AU2" s="23"/>
+      <c r="AV2" s="23"/>
+      <c r="AW2" s="23"/>
+      <c r="AX2" s="23"/>
+      <c r="AY2" s="23"/>
+      <c r="AZ2" s="23"/>
+      <c r="BA2" s="23"/>
+      <c r="BB2" s="23"/>
+      <c r="BC2" s="23"/>
+      <c r="BD2" s="23"/>
+      <c r="BE2" s="23"/>
+      <c r="BF2" s="23"/>
+      <c r="BG2" s="23"/>
+      <c r="BH2" s="23"/>
+      <c r="BI2" s="23"/>
+      <c r="BJ2" s="23"/>
+      <c r="BK2" s="23"/>
+      <c r="BL2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="26" t="s">
         <v>5</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="18" t="s">
+      <c r="L3" s="27"/>
+      <c r="M3" s="26" t="s">
         <v>10</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19" t="n">
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="R3" s="0"/>
-      <c r="W3" s="0"/>
-      <c r="X3" s="0"/>
-      <c r="Y3" s="0"/>
-      <c r="Z3" s="0"/>
-      <c r="AA3" s="0"/>
-      <c r="AB3" s="0"/>
-      <c r="AC3" s="0"/>
-      <c r="AD3" s="0"/>
-      <c r="AE3" s="0"/>
-      <c r="AF3" s="0"/>
-      <c r="AG3" s="0"/>
-      <c r="AH3" s="0"/>
-      <c r="AI3" s="0"/>
-      <c r="AJ3" s="0"/>
-      <c r="AK3" s="0"/>
-      <c r="AL3" s="0"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+      <c r="Z3" s="19"/>
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="19"/>
+      <c r="AF3" s="19"/>
+      <c r="AG3" s="19"/>
+      <c r="AH3" s="19"/>
+      <c r="AI3" s="19"/>
+      <c r="AJ3" s="19"/>
+      <c r="AK3" s="22"/>
+      <c r="AL3" s="22"/>
+      <c r="AM3" s="23"/>
+      <c r="AN3" s="23"/>
+      <c r="AO3" s="23"/>
+      <c r="AP3" s="23"/>
+      <c r="AQ3" s="23"/>
+      <c r="AR3" s="23"/>
+      <c r="AS3" s="23"/>
+      <c r="AT3" s="23"/>
+      <c r="AU3" s="23"/>
+      <c r="AV3" s="23"/>
+      <c r="AW3" s="23"/>
+      <c r="AX3" s="23"/>
+      <c r="AY3" s="23"/>
+      <c r="AZ3" s="23"/>
+      <c r="BA3" s="23"/>
+      <c r="BB3" s="23"/>
+      <c r="BC3" s="23"/>
+      <c r="BD3" s="23"/>
+      <c r="BE3" s="23"/>
+      <c r="BF3" s="23"/>
+      <c r="BG3" s="23"/>
+      <c r="BH3" s="23"/>
+      <c r="BI3" s="23"/>
+      <c r="BJ3" s="23"/>
+      <c r="BK3" s="23"/>
+      <c r="BL3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18" t="s">
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="26" t="s">
         <v>5</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="18" t="s">
+      <c r="L4" s="27"/>
+      <c r="M4" s="26" t="s">
         <v>10</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19" t="n">
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="0"/>
-      <c r="W4" s="0"/>
-      <c r="X4" s="0"/>
-      <c r="Y4" s="0"/>
-      <c r="Z4" s="0"/>
-      <c r="AA4" s="0"/>
-      <c r="AB4" s="0"/>
-      <c r="AC4" s="0"/>
-      <c r="AD4" s="0"/>
-      <c r="AE4" s="0"/>
-      <c r="AF4" s="0"/>
-      <c r="AG4" s="0"/>
-      <c r="AH4" s="0"/>
-      <c r="AI4" s="0"/>
-      <c r="AJ4" s="0"/>
-      <c r="AK4" s="0"/>
-      <c r="AL4" s="0"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="19"/>
+      <c r="AA4" s="19"/>
+      <c r="AB4" s="19"/>
+      <c r="AC4" s="19"/>
+      <c r="AD4" s="19"/>
+      <c r="AE4" s="19"/>
+      <c r="AF4" s="19"/>
+      <c r="AG4" s="19"/>
+      <c r="AH4" s="19"/>
+      <c r="AI4" s="19"/>
+      <c r="AJ4" s="19"/>
+      <c r="AK4" s="22"/>
+      <c r="AL4" s="22"/>
+      <c r="AM4" s="23"/>
+      <c r="AN4" s="23"/>
+      <c r="AO4" s="23"/>
+      <c r="AP4" s="23"/>
+      <c r="AQ4" s="23"/>
+      <c r="AR4" s="23"/>
+      <c r="AS4" s="23"/>
+      <c r="AT4" s="23"/>
+      <c r="AU4" s="23"/>
+      <c r="AV4" s="23"/>
+      <c r="AW4" s="23"/>
+      <c r="AX4" s="23"/>
+      <c r="AY4" s="23"/>
+      <c r="AZ4" s="23"/>
+      <c r="BA4" s="23"/>
+      <c r="BB4" s="23"/>
+      <c r="BC4" s="23"/>
+      <c r="BD4" s="23"/>
+      <c r="BE4" s="23"/>
+      <c r="BF4" s="23"/>
+      <c r="BG4" s="23"/>
+      <c r="BH4" s="23"/>
+      <c r="BI4" s="23"/>
+      <c r="BJ4" s="23"/>
+      <c r="BK4" s="23"/>
+      <c r="BL4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18" t="s">
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="26" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="18" t="s">
+      <c r="L5" s="27"/>
+      <c r="M5" s="26" t="s">
         <v>10</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19" t="n">
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="R5" s="0"/>
-      <c r="W5" s="0"/>
-      <c r="X5" s="0"/>
-      <c r="Y5" s="0"/>
-      <c r="Z5" s="0"/>
-      <c r="AA5" s="0"/>
-      <c r="AB5" s="0"/>
-      <c r="AC5" s="0"/>
-      <c r="AD5" s="0"/>
-      <c r="AE5" s="0"/>
-      <c r="AF5" s="0"/>
-      <c r="AG5" s="0"/>
-      <c r="AH5" s="0"/>
-      <c r="AI5" s="0"/>
-      <c r="AJ5" s="0"/>
-      <c r="AK5" s="0"/>
-      <c r="AL5" s="0"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="19"/>
+      <c r="Y5" s="19"/>
+      <c r="Z5" s="19"/>
+      <c r="AA5" s="19"/>
+      <c r="AB5" s="19"/>
+      <c r="AC5" s="19"/>
+      <c r="AD5" s="19"/>
+      <c r="AE5" s="19"/>
+      <c r="AF5" s="19"/>
+      <c r="AG5" s="19"/>
+      <c r="AH5" s="19"/>
+      <c r="AI5" s="19"/>
+      <c r="AJ5" s="19"/>
+      <c r="AK5" s="22"/>
+      <c r="AL5" s="22"/>
+      <c r="AM5" s="23"/>
+      <c r="AN5" s="23"/>
+      <c r="AO5" s="23"/>
+      <c r="AP5" s="23"/>
+      <c r="AQ5" s="23"/>
+      <c r="AR5" s="23"/>
+      <c r="AS5" s="23"/>
+      <c r="AT5" s="23"/>
+      <c r="AU5" s="23"/>
+      <c r="AV5" s="23"/>
+      <c r="AW5" s="23"/>
+      <c r="AX5" s="23"/>
+      <c r="AY5" s="23"/>
+      <c r="AZ5" s="23"/>
+      <c r="BA5" s="23"/>
+      <c r="BB5" s="23"/>
+      <c r="BC5" s="23"/>
+      <c r="BD5" s="23"/>
+      <c r="BE5" s="23"/>
+      <c r="BF5" s="23"/>
+      <c r="BG5" s="23"/>
+      <c r="BH5" s="23"/>
+      <c r="BI5" s="23"/>
+      <c r="BJ5" s="23"/>
+      <c r="BK5" s="23"/>
+      <c r="BL5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="18" t="s">
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="26" t="s">
         <v>7</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -890,90 +1253,150 @@
       <c r="K6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="19"/>
-      <c r="M6" s="18" t="s">
+      <c r="L6" s="27"/>
+      <c r="M6" s="26" t="s">
         <v>14</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19" t="n">
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="R6" s="0"/>
-      <c r="W6" s="0"/>
-      <c r="X6" s="0"/>
-      <c r="Y6" s="0"/>
-      <c r="Z6" s="0"/>
-      <c r="AA6" s="0"/>
-      <c r="AB6" s="0"/>
-      <c r="AC6" s="0"/>
-      <c r="AD6" s="0"/>
-      <c r="AE6" s="0"/>
-      <c r="AF6" s="0"/>
-      <c r="AG6" s="0"/>
-      <c r="AH6" s="0"/>
-      <c r="AI6" s="0"/>
-      <c r="AJ6" s="0"/>
-      <c r="AK6" s="0"/>
-      <c r="AL6" s="0"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="19"/>
+      <c r="AI6" s="19"/>
+      <c r="AJ6" s="19"/>
+      <c r="AK6" s="22"/>
+      <c r="AL6" s="22"/>
+      <c r="AM6" s="23"/>
+      <c r="AN6" s="23"/>
+      <c r="AO6" s="23"/>
+      <c r="AP6" s="23"/>
+      <c r="AQ6" s="23"/>
+      <c r="AR6" s="23"/>
+      <c r="AS6" s="23"/>
+      <c r="AT6" s="23"/>
+      <c r="AU6" s="23"/>
+      <c r="AV6" s="23"/>
+      <c r="AW6" s="23"/>
+      <c r="AX6" s="23"/>
+      <c r="AY6" s="23"/>
+      <c r="AZ6" s="23"/>
+      <c r="BA6" s="23"/>
+      <c r="BB6" s="23"/>
+      <c r="BC6" s="23"/>
+      <c r="BD6" s="23"/>
+      <c r="BE6" s="23"/>
+      <c r="BF6" s="23"/>
+      <c r="BG6" s="23"/>
+      <c r="BH6" s="23"/>
+      <c r="BI6" s="23"/>
+      <c r="BJ6" s="23"/>
+      <c r="BK6" s="23"/>
+      <c r="BL6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="22" t="s">
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="24" t="n">
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="0"/>
-      <c r="W7" s="0"/>
-      <c r="X7" s="0"/>
-      <c r="Y7" s="0"/>
-      <c r="Z7" s="0"/>
-      <c r="AA7" s="0"/>
-      <c r="AB7" s="0"/>
-      <c r="AC7" s="0"/>
-      <c r="AD7" s="0"/>
-      <c r="AE7" s="0"/>
-      <c r="AF7" s="0"/>
-      <c r="AG7" s="0"/>
-      <c r="AH7" s="0"/>
-      <c r="AI7" s="0"/>
-      <c r="AJ7" s="0"/>
-      <c r="AK7" s="0"/>
-      <c r="AL7" s="0"/>
+      <c r="R7" s="36"/>
+      <c r="S7" s="37"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="36"/>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="36"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="36"/>
+      <c r="AE7" s="36"/>
+      <c r="AF7" s="36"/>
+      <c r="AG7" s="36"/>
+      <c r="AH7" s="36"/>
+      <c r="AI7" s="36"/>
+      <c r="AJ7" s="36"/>
+      <c r="AK7" s="39"/>
+      <c r="AL7" s="39"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="40"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="40"/>
+      <c r="AR7" s="40"/>
+      <c r="AS7" s="40"/>
+      <c r="AT7" s="40"/>
+      <c r="AU7" s="40"/>
+      <c r="AV7" s="40"/>
+      <c r="AW7" s="40"/>
+      <c r="AX7" s="40"/>
+      <c r="AY7" s="40"/>
+      <c r="AZ7" s="40"/>
+      <c r="BA7" s="40"/>
+      <c r="BB7" s="40"/>
+      <c r="BC7" s="40"/>
+      <c r="BD7" s="40"/>
+      <c r="BE7" s="40"/>
+      <c r="BF7" s="40"/>
+      <c r="BG7" s="40"/>
+      <c r="BH7" s="40"/>
+      <c r="BI7" s="40"/>
+      <c r="BJ7" s="40"/>
+      <c r="BK7" s="40"/>
+      <c r="BL7" s="40"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="29"/>
+      <c r="B8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="42"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="42"/>
       <c r="T8" s="2"/>
       <c r="W8" s="0"/>
       <c r="X8" s="0"/>
@@ -993,7 +1416,7 @@
       <c r="AL8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="28"/>
+      <c r="B9" s="41"/>
       <c r="D9" s="0"/>
       <c r="E9" s="0"/>
       <c r="F9" s="0"/>
@@ -1068,26 +1491,47 @@
       <c r="AL10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="32"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="45" t="n">
+        <f aca="false">A11+A13</f>
+        <v>7</v>
+      </c>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
+      <c r="F11" s="43" t="n">
+        <f aca="false">C11</f>
+        <v>7</v>
+      </c>
+      <c r="G11" s="44"/>
+      <c r="H11" s="45" t="n">
+        <f aca="false">F11+F13</f>
+        <v>10</v>
+      </c>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
-      <c r="K11" s="0"/>
-      <c r="L11" s="0"/>
-      <c r="M11" s="0"/>
+      <c r="K11" s="43" t="n">
+        <f aca="false">MAX(H11,H17,H23)</f>
+        <v>13</v>
+      </c>
+      <c r="L11" s="44"/>
+      <c r="M11" s="45" t="n">
+        <f aca="false">K11+K13</f>
+        <v>14</v>
+      </c>
       <c r="N11" s="0"/>
       <c r="O11" s="0"/>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="0"/>
-      <c r="R11" s="0"/>
+      <c r="P11" s="43" t="n">
+        <f aca="false">M11</f>
+        <v>14</v>
+      </c>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="45" t="n">
+        <f aca="false">P11+P13</f>
+        <v>15</v>
+      </c>
       <c r="S11" s="0"/>
       <c r="T11" s="0"/>
       <c r="U11" s="0"/>
@@ -1110,26 +1554,32 @@
       <c r="AL11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="0"/>
-      <c r="G12" s="0"/>
-      <c r="H12" s="0"/>
+      <c r="F12" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="0"/>
-      <c r="L12" s="0"/>
-      <c r="M12" s="0"/>
+      <c r="K12" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
-      <c r="P12" s="0"/>
-      <c r="Q12" s="0"/>
-      <c r="R12" s="0"/>
+      <c r="P12" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
       <c r="U12" s="0"/>
@@ -1151,27 +1601,48 @@
       <c r="AK12" s="0"/>
       <c r="AL12" s="0"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="n">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="0"/>
-      <c r="G13" s="0"/>
-      <c r="H13" s="0"/>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0"/>
-      <c r="K13" s="0"/>
-      <c r="L13" s="0"/>
-      <c r="M13" s="0"/>
-      <c r="N13" s="0"/>
-      <c r="O13" s="0"/>
-      <c r="P13" s="0"/>
-      <c r="Q13" s="0"/>
-      <c r="R13" s="0"/>
+      <c r="B13" s="48" t="n">
+        <f aca="false">C14-C11</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="49"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="47" t="n">
+        <f aca="false">Q3</f>
+        <v>3</v>
+      </c>
+      <c r="G13" s="48" t="n">
+        <f aca="false">H14-H11</f>
+        <v>3</v>
+      </c>
+      <c r="H13" s="49"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="47" t="n">
+        <f aca="false">Q6</f>
+        <v>1</v>
+      </c>
+      <c r="L13" s="48" t="n">
+        <f aca="false">M14-M11</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="49"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="51"/>
+      <c r="P13" s="47" t="n">
+        <f aca="false">Q7</f>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="48" t="n">
+        <f aca="false">R14-R11</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="49"/>
       <c r="S13" s="0"/>
       <c r="T13" s="0"/>
       <c r="U13" s="0"/>
@@ -1194,26 +1665,48 @@
       <c r="AL13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
+      <c r="A14" s="53" t="n">
+        <f aca="false">C14-A13</f>
         <v>0</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="0"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="54" t="n">
+        <f aca="false">MIN(F26,F20,F14)</f>
+        <v>7</v>
+      </c>
+      <c r="D14" s="55"/>
       <c r="E14" s="0"/>
-      <c r="F14" s="0"/>
-      <c r="G14" s="0"/>
-      <c r="H14" s="0"/>
+      <c r="F14" s="53" t="n">
+        <f aca="false">H14-F13</f>
+        <v>10</v>
+      </c>
+      <c r="G14" s="41"/>
+      <c r="H14" s="54" t="n">
+        <f aca="false">K14</f>
+        <v>13</v>
+      </c>
       <c r="I14" s="0"/>
-      <c r="J14" s="0"/>
-      <c r="K14" s="0"/>
-      <c r="L14" s="0"/>
-      <c r="M14" s="0"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="53" t="n">
+        <f aca="false">M14-K13</f>
+        <v>13</v>
+      </c>
+      <c r="L14" s="41"/>
+      <c r="M14" s="54" t="n">
+        <f aca="false">P14</f>
+        <v>14</v>
+      </c>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
-      <c r="P14" s="0"/>
-      <c r="Q14" s="0"/>
-      <c r="R14" s="0"/>
+      <c r="P14" s="53" t="n">
+        <f aca="false">R14-P13</f>
+        <v>14</v>
+      </c>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="54" t="n">
+        <f aca="false">R11</f>
+        <v>15</v>
+      </c>
       <c r="S14" s="0"/>
       <c r="T14" s="0"/>
       <c r="U14" s="0"/>
@@ -1236,13 +1729,13 @@
       <c r="AL14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="0"/>
+      <c r="D15" s="55"/>
       <c r="E15" s="0"/>
       <c r="F15" s="0"/>
       <c r="G15" s="0"/>
       <c r="H15" s="0"/>
       <c r="I15" s="0"/>
-      <c r="J15" s="0"/>
+      <c r="J15" s="56"/>
       <c r="K15" s="0"/>
       <c r="L15" s="0"/>
       <c r="M15" s="0"/>
@@ -1273,13 +1766,13 @@
       <c r="AL15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="0"/>
+      <c r="D16" s="55"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0"/>
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
-      <c r="J16" s="0"/>
+      <c r="J16" s="56"/>
       <c r="K16" s="0"/>
       <c r="L16" s="0"/>
       <c r="M16" s="0"/>
@@ -1310,13 +1803,19 @@
       <c r="AL16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="0"/>
+      <c r="D17" s="55"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="0"/>
-      <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
+      <c r="F17" s="43" t="n">
+        <f aca="false">C11</f>
+        <v>7</v>
+      </c>
+      <c r="G17" s="44"/>
+      <c r="H17" s="45" t="n">
+        <f aca="false">F17+F19</f>
+        <v>13</v>
+      </c>
       <c r="I17" s="0"/>
-      <c r="J17" s="0"/>
+      <c r="J17" s="56"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0"/>
       <c r="M17" s="0"/>
@@ -1347,13 +1846,15 @@
       <c r="AL17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="0"/>
+      <c r="D18" s="55"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="0"/>
-      <c r="G18" s="0"/>
-      <c r="H18" s="0"/>
+      <c r="F18" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
       <c r="I18" s="0"/>
-      <c r="J18" s="0"/>
+      <c r="J18" s="56"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
       <c r="M18" s="0"/>
@@ -1380,14 +1881,20 @@
       <c r="AK18" s="0"/>
       <c r="AL18" s="0"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="0"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="0"/>
-      <c r="G19" s="0"/>
-      <c r="H19" s="0"/>
-      <c r="I19" s="0"/>
-      <c r="J19" s="0"/>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="55"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="47" t="n">
+        <f aca="false">Q4</f>
+        <v>6</v>
+      </c>
+      <c r="G19" s="48" t="n">
+        <f aca="false">H20-H17</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="49"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="56"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0"/>
       <c r="M19" s="0"/>
@@ -1415,13 +1922,19 @@
       <c r="AL19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="0"/>
+      <c r="D20" s="55"/>
       <c r="E20" s="0"/>
-      <c r="F20" s="0"/>
-      <c r="G20" s="0"/>
-      <c r="H20" s="0"/>
+      <c r="F20" s="53" t="n">
+        <f aca="false">H20-F19</f>
+        <v>7</v>
+      </c>
+      <c r="G20" s="41"/>
+      <c r="H20" s="54" t="n">
+        <f aca="false">K14</f>
+        <v>13</v>
+      </c>
       <c r="I20" s="0"/>
-      <c r="J20" s="0"/>
+      <c r="J20" s="56"/>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
       <c r="M20" s="0"/>
@@ -1450,13 +1963,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
-      <c r="D21" s="0"/>
+      <c r="D21" s="55"/>
       <c r="E21" s="0"/>
       <c r="F21" s="0"/>
       <c r="G21" s="0"/>
       <c r="H21" s="0"/>
       <c r="I21" s="0"/>
-      <c r="J21" s="0"/>
+      <c r="J21" s="56"/>
       <c r="K21" s="0"/>
       <c r="L21" s="0"/>
       <c r="M21" s="0"/>
@@ -1485,13 +1998,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="D22" s="0"/>
+      <c r="D22" s="55"/>
       <c r="E22" s="0"/>
       <c r="F22" s="0"/>
       <c r="G22" s="0"/>
       <c r="H22" s="0"/>
       <c r="I22" s="0"/>
-      <c r="J22" s="0"/>
+      <c r="J22" s="56"/>
       <c r="K22" s="0"/>
       <c r="L22" s="0"/>
       <c r="M22" s="0"/>
@@ -1520,13 +2033,19 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="D23" s="0"/>
+      <c r="D23" s="55"/>
       <c r="E23" s="0"/>
-      <c r="F23" s="0"/>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
+      <c r="F23" s="43" t="n">
+        <f aca="false">C11</f>
+        <v>7</v>
+      </c>
+      <c r="G23" s="44"/>
+      <c r="H23" s="45" t="n">
+        <f aca="false">F23+F25</f>
+        <v>10</v>
+      </c>
       <c r="I23" s="0"/>
-      <c r="J23" s="0"/>
+      <c r="J23" s="56"/>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
       <c r="M23" s="0"/>
@@ -1541,13 +2060,15 @@
       <c r="A24" s="0"/>
       <c r="B24" s="0"/>
       <c r="C24" s="0"/>
-      <c r="D24" s="0"/>
+      <c r="D24" s="55"/>
       <c r="E24" s="0"/>
-      <c r="F24" s="0"/>
-      <c r="G24" s="0"/>
-      <c r="H24" s="0"/>
+      <c r="F24" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
       <c r="I24" s="0"/>
-      <c r="J24" s="0"/>
+      <c r="J24" s="56"/>
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
       <c r="M24" s="0"/>
@@ -1558,16 +2079,22 @@
       <c r="R24" s="0"/>
       <c r="S24" s="0"/>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0"/>
       <c r="B25" s="0"/>
       <c r="C25" s="0"/>
       <c r="D25" s="0"/>
-      <c r="E25" s="0"/>
-      <c r="F25" s="0"/>
-      <c r="G25" s="0"/>
-      <c r="H25" s="0"/>
-      <c r="I25" s="0"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="47" t="n">
+        <f aca="false">Q5</f>
+        <v>3</v>
+      </c>
+      <c r="G25" s="48" t="n">
+        <f aca="false">H26-H23</f>
+        <v>3</v>
+      </c>
+      <c r="H25" s="49"/>
+      <c r="I25" s="51"/>
       <c r="J25" s="0"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
@@ -1585,9 +2112,15 @@
       <c r="C26" s="0"/>
       <c r="D26" s="0"/>
       <c r="E26" s="0"/>
-      <c r="F26" s="0"/>
-      <c r="G26" s="0"/>
-      <c r="H26" s="0"/>
+      <c r="F26" s="53" t="n">
+        <f aca="false">H26-F25</f>
+        <v>10</v>
+      </c>
+      <c r="G26" s="41"/>
+      <c r="H26" s="54" t="n">
+        <f aca="false">K14</f>
+        <v>13</v>
+      </c>
       <c r="I26" s="0"/>
       <c r="J26" s="0"/>
       <c r="K26" s="0"/>
@@ -1748,214 +2281,214 @@
       <c r="L37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="39"/>
-      <c r="B38" s="40"/>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="40"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="40"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="58"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="39"/>
+      <c r="A39" s="57"/>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="40"/>
+      <c r="L39" s="58"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="39"/>
-      <c r="B40" s="41" t="s">
+      <c r="A40" s="57"/>
+      <c r="B40" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="F40" s="42" t="s">
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="F40" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
-      <c r="L40" s="40"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="60"/>
+      <c r="L40" s="58"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="39"/>
-      <c r="B41" s="43" t="s">
+      <c r="A41" s="57"/>
+      <c r="B41" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="44" t="s">
+      <c r="C41" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="43" t="s">
+      <c r="D41" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="L41" s="40"/>
+      <c r="L41" s="58"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="39"/>
+      <c r="A42" s="57"/>
       <c r="B42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L42" s="40"/>
+      <c r="L42" s="58"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="39"/>
-      <c r="L43" s="40"/>
+      <c r="A43" s="57"/>
+      <c r="L43" s="58"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="39"/>
-      <c r="B44" s="45" t="s">
+      <c r="A44" s="57"/>
+      <c r="B44" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="C44" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="40"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="41"/>
+      <c r="K44" s="41"/>
+      <c r="L44" s="58"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="39"/>
-      <c r="B45" s="45" t="s">
+      <c r="A45" s="57"/>
+      <c r="B45" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="40"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="41"/>
+      <c r="J45" s="41"/>
+      <c r="K45" s="41"/>
+      <c r="L45" s="58"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="39"/>
-      <c r="B46" s="45" t="s">
+      <c r="A46" s="57"/>
+      <c r="B46" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="C46" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="40"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="41"/>
+      <c r="K46" s="41"/>
+      <c r="L46" s="58"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="39"/>
-      <c r="B47" s="45" t="s">
+      <c r="A47" s="57"/>
+      <c r="B47" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="40"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="41"/>
+      <c r="J47" s="41"/>
+      <c r="K47" s="41"/>
+      <c r="L47" s="58"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="39"/>
-      <c r="B48" s="43" t="s">
+      <c r="A48" s="57"/>
+      <c r="B48" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="28" t="s">
+      <c r="C48" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="40"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="41"/>
+      <c r="J48" s="41"/>
+      <c r="K48" s="41"/>
+      <c r="L48" s="58"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="39"/>
-      <c r="B49" s="44" t="s">
+      <c r="A49" s="57"/>
+      <c r="B49" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="28" t="s">
+      <c r="C49" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="40"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="58"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="39"/>
-      <c r="B50" s="46" t="s">
+      <c r="A50" s="57"/>
+      <c r="B50" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="40" t="s">
+      <c r="C50" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="40"/>
-      <c r="K50" s="40"/>
-      <c r="L50" s="40"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="58"/>
+      <c r="H50" s="58"/>
+      <c r="I50" s="58"/>
+      <c r="J50" s="58"/>
+      <c r="K50" s="58"/>
+      <c r="L50" s="58"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="39"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="40"/>
-      <c r="L51" s="40"/>
+      <c r="A51" s="57"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="58"/>
+      <c r="J51" s="58"/>
+      <c r="K51" s="58"/>
+      <c r="L51" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="23">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:P1"/>
@@ -1966,6 +2499,11 @@
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="F40:J40"/>
     <mergeCell ref="C44:K44"/>
@@ -1975,9 +2513,9 @@
     <mergeCell ref="C48:K48"/>
     <mergeCell ref="C49:K49"/>
   </mergeCells>
-  <conditionalFormatting sqref="B13">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>0</formula>
+  <conditionalFormatting sqref="R1:BL7">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>IF(WEEKDAY(R$1,2)=6,1,IF(WEEKDAY(R$1,2)=7,1,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Übungen/02_Netzplan_Firmennetzwerk.xlsx
+++ b/Übungen/02_Netzplan_Firmennetzwerk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Netzplan" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Netzplan!$A$1:$X$30</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Netzplan!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="31">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t xml:space="preserve">Domaincontroller einrichten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastruktur fertig</t>
   </si>
   <si>
     <t xml:space="preserve">Clients in Domain einbinden</t>
@@ -124,7 +127,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -169,6 +172,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC9211E"/>
+      <name val="Alegreya Sans"/>
+      <family val="3"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="9"/>
       <name val="Alegreya Sans"/>
       <family val="3"/>
@@ -188,7 +199,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,6 +222,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF999999"/>
         <bgColor rgb="FFB2B2B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFC9211E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBF00"/>
+        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
     <fill>
@@ -388,7 +411,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="70">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -425,10 +448,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -465,20 +484,44 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -486,19 +529,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -521,15 +560,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -561,31 +600,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -597,6 +636,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -617,35 +660,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -718,7 +761,7 @@
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFFBF00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
@@ -736,16 +779,89 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>37440</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>6480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>166320</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>5040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9515160" y="1198080"/>
+          <a:ext cx="128880" cy="168840"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BN51"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BN52"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="2" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="2" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="16" min="9" style="2" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="3" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="3.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="3.83"/>
@@ -853,155 +969,108 @@
       <c r="AO1" s="8" t="n">
         <v>44629</v>
       </c>
-      <c r="AP1" s="8" t="n">
-        <v>44630</v>
-      </c>
-      <c r="AQ1" s="8" t="n">
-        <v>44631</v>
-      </c>
-      <c r="AR1" s="8" t="n">
-        <v>44632</v>
-      </c>
-      <c r="AS1" s="8" t="n">
-        <v>44633</v>
-      </c>
-      <c r="AT1" s="8" t="n">
-        <v>44634</v>
-      </c>
-      <c r="AU1" s="8" t="n">
-        <v>44635</v>
-      </c>
-      <c r="AV1" s="8" t="n">
-        <v>44636</v>
-      </c>
-      <c r="AW1" s="8" t="n">
-        <v>44637</v>
-      </c>
-      <c r="AX1" s="8" t="n">
-        <v>44638</v>
-      </c>
-      <c r="AY1" s="8" t="n">
-        <v>44639</v>
-      </c>
-      <c r="AZ1" s="8" t="n">
-        <v>44640</v>
-      </c>
-      <c r="BA1" s="8" t="n">
-        <v>44641</v>
-      </c>
-      <c r="BB1" s="8" t="n">
-        <v>44642</v>
-      </c>
-      <c r="BC1" s="8" t="n">
-        <v>44643</v>
-      </c>
-      <c r="BD1" s="8" t="n">
-        <v>44644</v>
-      </c>
-      <c r="BE1" s="8" t="n">
-        <v>44645</v>
-      </c>
-      <c r="BF1" s="8" t="n">
-        <v>44646</v>
-      </c>
-      <c r="BG1" s="8" t="n">
-        <v>44647</v>
-      </c>
-      <c r="BH1" s="8" t="n">
-        <v>44648</v>
-      </c>
-      <c r="BI1" s="8" t="n">
-        <v>44649</v>
-      </c>
-      <c r="BJ1" s="8" t="n">
-        <v>44650</v>
-      </c>
-      <c r="BK1" s="8" t="n">
-        <v>44651</v>
-      </c>
-      <c r="BL1" s="8" t="n">
-        <v>44652</v>
-      </c>
-      <c r="BM1" s="9"/>
-      <c r="BN1" s="10"/>
+      <c r="AP1" s="0"/>
+      <c r="AQ1" s="0"/>
+      <c r="AR1" s="0"/>
+      <c r="AS1" s="0"/>
+      <c r="AT1" s="0"/>
+      <c r="AU1" s="0"/>
+      <c r="AV1" s="0"/>
+      <c r="AW1" s="0"/>
+      <c r="AX1" s="0"/>
+      <c r="AY1" s="0"/>
+      <c r="AZ1" s="0"/>
+      <c r="BA1" s="0"/>
+      <c r="BB1" s="0"/>
+      <c r="BC1" s="0"/>
+      <c r="BD1" s="0"/>
+      <c r="BE1" s="0"/>
+      <c r="BF1" s="0"/>
+      <c r="BG1" s="0"/>
+      <c r="BH1" s="0"/>
+      <c r="BI1" s="0"/>
+      <c r="BJ1" s="0"/>
+      <c r="BK1" s="0"/>
+      <c r="BL1" s="0"/>
+      <c r="BN1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="16" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18" t="n">
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="R2" s="19"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="19"/>
-      <c r="X2" s="19"/>
-      <c r="Y2" s="19"/>
-      <c r="Z2" s="19"/>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19"/>
-      <c r="AE2" s="19"/>
-      <c r="AF2" s="19"/>
-      <c r="AG2" s="19"/>
-      <c r="AH2" s="19"/>
-      <c r="AI2" s="19"/>
-      <c r="AJ2" s="19"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
+      <c r="AH2" s="21"/>
+      <c r="AI2" s="21"/>
+      <c r="AJ2" s="21"/>
       <c r="AK2" s="22"/>
       <c r="AL2" s="22"/>
       <c r="AM2" s="23"/>
       <c r="AN2" s="23"/>
       <c r="AO2" s="23"/>
-      <c r="AP2" s="23"/>
-      <c r="AQ2" s="23"/>
-      <c r="AR2" s="23"/>
-      <c r="AS2" s="23"/>
-      <c r="AT2" s="23"/>
-      <c r="AU2" s="23"/>
-      <c r="AV2" s="23"/>
-      <c r="AW2" s="23"/>
-      <c r="AX2" s="23"/>
-      <c r="AY2" s="23"/>
-      <c r="AZ2" s="23"/>
-      <c r="BA2" s="23"/>
-      <c r="BB2" s="23"/>
-      <c r="BC2" s="23"/>
-      <c r="BD2" s="23"/>
-      <c r="BE2" s="23"/>
-      <c r="BF2" s="23"/>
-      <c r="BG2" s="23"/>
-      <c r="BH2" s="23"/>
-      <c r="BI2" s="23"/>
-      <c r="BJ2" s="23"/>
-      <c r="BK2" s="23"/>
-      <c r="BL2" s="23"/>
+      <c r="AP2" s="0"/>
+      <c r="AQ2" s="0"/>
+      <c r="AR2" s="0"/>
+      <c r="AS2" s="0"/>
+      <c r="AT2" s="0"/>
+      <c r="AU2" s="0"/>
+      <c r="AV2" s="0"/>
+      <c r="AW2" s="0"/>
+      <c r="AX2" s="0"/>
+      <c r="AY2" s="0"/>
+      <c r="AZ2" s="0"/>
+      <c r="BA2" s="0"/>
+      <c r="BB2" s="0"/>
+      <c r="BC2" s="0"/>
+      <c r="BD2" s="0"/>
+      <c r="BE2" s="0"/>
+      <c r="BF2" s="0"/>
+      <c r="BG2" s="0"/>
+      <c r="BH2" s="0"/>
+      <c r="BI2" s="0"/>
+      <c r="BJ2" s="0"/>
+      <c r="BK2" s="0"/>
+      <c r="BL2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="24" t="s">
@@ -1031,53 +1100,53 @@
       <c r="Q3" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="R3" s="19"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="19"/>
-      <c r="X3" s="19"/>
-      <c r="Y3" s="19"/>
-      <c r="Z3" s="19"/>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="19"/>
-      <c r="AC3" s="19"/>
-      <c r="AD3" s="19"/>
-      <c r="AE3" s="19"/>
-      <c r="AF3" s="19"/>
-      <c r="AG3" s="19"/>
-      <c r="AH3" s="19"/>
-      <c r="AI3" s="19"/>
-      <c r="AJ3" s="19"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+      <c r="W3" s="21"/>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="30"/>
+      <c r="AC3" s="30"/>
+      <c r="AD3" s="21"/>
+      <c r="AE3" s="21"/>
+      <c r="AF3" s="21"/>
+      <c r="AG3" s="21"/>
+      <c r="AH3" s="21"/>
+      <c r="AI3" s="21"/>
+      <c r="AJ3" s="21"/>
       <c r="AK3" s="22"/>
       <c r="AL3" s="22"/>
       <c r="AM3" s="23"/>
       <c r="AN3" s="23"/>
       <c r="AO3" s="23"/>
-      <c r="AP3" s="23"/>
-      <c r="AQ3" s="23"/>
-      <c r="AR3" s="23"/>
-      <c r="AS3" s="23"/>
-      <c r="AT3" s="23"/>
-      <c r="AU3" s="23"/>
-      <c r="AV3" s="23"/>
-      <c r="AW3" s="23"/>
-      <c r="AX3" s="23"/>
-      <c r="AY3" s="23"/>
-      <c r="AZ3" s="23"/>
-      <c r="BA3" s="23"/>
-      <c r="BB3" s="23"/>
-      <c r="BC3" s="23"/>
-      <c r="BD3" s="23"/>
-      <c r="BE3" s="23"/>
-      <c r="BF3" s="23"/>
-      <c r="BG3" s="23"/>
-      <c r="BH3" s="23"/>
-      <c r="BI3" s="23"/>
-      <c r="BJ3" s="23"/>
-      <c r="BK3" s="23"/>
-      <c r="BL3" s="23"/>
+      <c r="AP3" s="0"/>
+      <c r="AQ3" s="0"/>
+      <c r="AR3" s="0"/>
+      <c r="AS3" s="0"/>
+      <c r="AT3" s="0"/>
+      <c r="AU3" s="0"/>
+      <c r="AV3" s="0"/>
+      <c r="AW3" s="0"/>
+      <c r="AX3" s="0"/>
+      <c r="AY3" s="0"/>
+      <c r="AZ3" s="0"/>
+      <c r="BA3" s="0"/>
+      <c r="BB3" s="0"/>
+      <c r="BC3" s="0"/>
+      <c r="BD3" s="0"/>
+      <c r="BE3" s="0"/>
+      <c r="BF3" s="0"/>
+      <c r="BG3" s="0"/>
+      <c r="BH3" s="0"/>
+      <c r="BI3" s="0"/>
+      <c r="BJ3" s="0"/>
+      <c r="BK3" s="0"/>
+      <c r="BL3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
@@ -1107,53 +1176,53 @@
       <c r="Q4" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="19"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="19"/>
-      <c r="AC4" s="19"/>
-      <c r="AD4" s="19"/>
-      <c r="AE4" s="19"/>
-      <c r="AF4" s="19"/>
-      <c r="AG4" s="19"/>
-      <c r="AH4" s="19"/>
-      <c r="AI4" s="19"/>
-      <c r="AJ4" s="19"/>
+      <c r="R4" s="21"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="21"/>
+      <c r="X4" s="21"/>
+      <c r="Y4" s="21"/>
+      <c r="Z4" s="21"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="20"/>
+      <c r="AC4" s="20"/>
+      <c r="AD4" s="21"/>
+      <c r="AE4" s="21"/>
+      <c r="AF4" s="20"/>
+      <c r="AG4" s="20"/>
+      <c r="AH4" s="20"/>
+      <c r="AI4" s="0"/>
+      <c r="AJ4" s="0"/>
       <c r="AK4" s="22"/>
       <c r="AL4" s="22"/>
-      <c r="AM4" s="23"/>
-      <c r="AN4" s="23"/>
+      <c r="AM4" s="0"/>
+      <c r="AN4" s="29"/>
       <c r="AO4" s="23"/>
-      <c r="AP4" s="23"/>
-      <c r="AQ4" s="23"/>
-      <c r="AR4" s="23"/>
-      <c r="AS4" s="23"/>
-      <c r="AT4" s="23"/>
-      <c r="AU4" s="23"/>
-      <c r="AV4" s="23"/>
-      <c r="AW4" s="23"/>
-      <c r="AX4" s="23"/>
-      <c r="AY4" s="23"/>
-      <c r="AZ4" s="23"/>
-      <c r="BA4" s="23"/>
-      <c r="BB4" s="23"/>
-      <c r="BC4" s="23"/>
-      <c r="BD4" s="23"/>
-      <c r="BE4" s="23"/>
-      <c r="BF4" s="23"/>
-      <c r="BG4" s="23"/>
-      <c r="BH4" s="23"/>
-      <c r="BI4" s="23"/>
-      <c r="BJ4" s="23"/>
-      <c r="BK4" s="23"/>
-      <c r="BL4" s="23"/>
+      <c r="AP4" s="0"/>
+      <c r="AQ4" s="0"/>
+      <c r="AR4" s="0"/>
+      <c r="AS4" s="0"/>
+      <c r="AT4" s="0"/>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
+      <c r="AW4" s="0"/>
+      <c r="AX4" s="0"/>
+      <c r="AY4" s="0"/>
+      <c r="AZ4" s="0"/>
+      <c r="BA4" s="0"/>
+      <c r="BB4" s="0"/>
+      <c r="BC4" s="0"/>
+      <c r="BD4" s="0"/>
+      <c r="BE4" s="0"/>
+      <c r="BF4" s="0"/>
+      <c r="BG4" s="0"/>
+      <c r="BH4" s="0"/>
+      <c r="BI4" s="0"/>
+      <c r="BJ4" s="0"/>
+      <c r="BK4" s="0"/>
+      <c r="BL4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
@@ -1183,259 +1252,289 @@
       <c r="Q5" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="R5" s="19"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="19"/>
-      <c r="Y5" s="19"/>
-      <c r="Z5" s="19"/>
-      <c r="AA5" s="19"/>
-      <c r="AB5" s="19"/>
-      <c r="AC5" s="19"/>
-      <c r="AD5" s="19"/>
-      <c r="AE5" s="19"/>
-      <c r="AF5" s="19"/>
-      <c r="AG5" s="19"/>
-      <c r="AH5" s="19"/>
-      <c r="AI5" s="19"/>
-      <c r="AJ5" s="19"/>
+      <c r="R5" s="21"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="21"/>
+      <c r="X5" s="21"/>
+      <c r="Y5" s="21"/>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="30"/>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="30"/>
+      <c r="AD5" s="21"/>
+      <c r="AE5" s="21"/>
+      <c r="AF5" s="21"/>
+      <c r="AG5" s="21"/>
+      <c r="AH5" s="21"/>
+      <c r="AI5" s="21"/>
+      <c r="AJ5" s="21"/>
       <c r="AK5" s="22"/>
       <c r="AL5" s="22"/>
       <c r="AM5" s="23"/>
       <c r="AN5" s="23"/>
       <c r="AO5" s="23"/>
-      <c r="AP5" s="23"/>
-      <c r="AQ5" s="23"/>
-      <c r="AR5" s="23"/>
-      <c r="AS5" s="23"/>
-      <c r="AT5" s="23"/>
-      <c r="AU5" s="23"/>
-      <c r="AV5" s="23"/>
-      <c r="AW5" s="23"/>
-      <c r="AX5" s="23"/>
-      <c r="AY5" s="23"/>
-      <c r="AZ5" s="23"/>
-      <c r="BA5" s="23"/>
-      <c r="BB5" s="23"/>
-      <c r="BC5" s="23"/>
-      <c r="BD5" s="23"/>
-      <c r="BE5" s="23"/>
-      <c r="BF5" s="23"/>
-      <c r="BG5" s="23"/>
-      <c r="BH5" s="23"/>
-      <c r="BI5" s="23"/>
-      <c r="BJ5" s="23"/>
-      <c r="BK5" s="23"/>
-      <c r="BL5" s="23"/>
+      <c r="AP5" s="0"/>
+      <c r="AQ5" s="0"/>
+      <c r="AR5" s="0"/>
+      <c r="AS5" s="0"/>
+      <c r="AT5" s="0"/>
+      <c r="AU5" s="0"/>
+      <c r="AV5" s="0"/>
+      <c r="AW5" s="0"/>
+      <c r="AX5" s="0"/>
+      <c r="AY5" s="0"/>
+      <c r="AZ5" s="0"/>
+      <c r="BA5" s="0"/>
+      <c r="BB5" s="0"/>
+      <c r="BC5" s="0"/>
+      <c r="BD5" s="0"/>
+      <c r="BE5" s="0"/>
+      <c r="BF5" s="0"/>
+      <c r="BG5" s="0"/>
+      <c r="BH5" s="0"/>
+      <c r="BI5" s="0"/>
+      <c r="BJ5" s="0"/>
+      <c r="BK5" s="0"/>
+      <c r="BL5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="25" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
       <c r="L6" s="27"/>
-      <c r="M6" s="26" t="s">
-        <v>14</v>
-      </c>
+      <c r="M6" s="26"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="27"/>
-      <c r="Q6" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="19"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="21"/>
-      <c r="V6" s="21"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="19"/>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="19"/>
-      <c r="AE6" s="19"/>
-      <c r="AF6" s="19"/>
-      <c r="AG6" s="19"/>
-      <c r="AH6" s="19"/>
-      <c r="AI6" s="19"/>
-      <c r="AJ6" s="19"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="21"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="21"/>
+      <c r="X6" s="21"/>
+      <c r="Y6" s="21"/>
+      <c r="Z6" s="0"/>
+      <c r="AA6" s="0"/>
+      <c r="AB6" s="0"/>
+      <c r="AC6" s="0"/>
+      <c r="AD6" s="21"/>
+      <c r="AE6" s="21"/>
+      <c r="AF6" s="21"/>
+      <c r="AG6" s="21"/>
+      <c r="AH6" s="21"/>
+      <c r="AI6" s="0"/>
+      <c r="AJ6" s="21"/>
       <c r="AK6" s="22"/>
       <c r="AL6" s="22"/>
       <c r="AM6" s="23"/>
       <c r="AN6" s="23"/>
       <c r="AO6" s="23"/>
-      <c r="AP6" s="23"/>
-      <c r="AQ6" s="23"/>
-      <c r="AR6" s="23"/>
-      <c r="AS6" s="23"/>
-      <c r="AT6" s="23"/>
-      <c r="AU6" s="23"/>
-      <c r="AV6" s="23"/>
-      <c r="AW6" s="23"/>
-      <c r="AX6" s="23"/>
-      <c r="AY6" s="23"/>
-      <c r="AZ6" s="23"/>
-      <c r="BA6" s="23"/>
-      <c r="BB6" s="23"/>
-      <c r="BC6" s="23"/>
-      <c r="BD6" s="23"/>
-      <c r="BE6" s="23"/>
-      <c r="BF6" s="23"/>
-      <c r="BG6" s="23"/>
-      <c r="BH6" s="23"/>
-      <c r="BI6" s="23"/>
-      <c r="BJ6" s="23"/>
-      <c r="BK6" s="23"/>
-      <c r="BL6" s="23"/>
+      <c r="AP6" s="0"/>
+      <c r="AQ6" s="0"/>
+      <c r="AR6" s="0"/>
+      <c r="AS6" s="0"/>
+      <c r="AT6" s="0"/>
+      <c r="AU6" s="0"/>
+      <c r="AV6" s="0"/>
+      <c r="AW6" s="0"/>
+      <c r="AX6" s="0"/>
+      <c r="AY6" s="0"/>
+      <c r="AZ6" s="0"/>
+      <c r="BA6" s="0"/>
+      <c r="BB6" s="0"/>
+      <c r="BC6" s="0"/>
+      <c r="BD6" s="0"/>
+      <c r="BE6" s="0"/>
+      <c r="BF6" s="0"/>
+      <c r="BG6" s="0"/>
+      <c r="BH6" s="0"/>
+      <c r="BI6" s="0"/>
+      <c r="BJ6" s="0"/>
+      <c r="BK6" s="0"/>
+      <c r="BL6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="27"/>
+      <c r="M7" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="30" t="s">
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="21"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="21"/>
+      <c r="X7" s="21"/>
+      <c r="Y7" s="21"/>
+      <c r="Z7" s="21"/>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="21"/>
+      <c r="AC7" s="21"/>
+      <c r="AD7" s="21"/>
+      <c r="AE7" s="21"/>
+      <c r="AF7" s="21"/>
+      <c r="AG7" s="21"/>
+      <c r="AH7" s="21"/>
+      <c r="AI7" s="0"/>
+      <c r="AJ7" s="20"/>
+      <c r="AK7" s="22"/>
+      <c r="AL7" s="22"/>
+      <c r="AM7" s="23"/>
+      <c r="AN7" s="23"/>
+      <c r="AO7" s="23"/>
+      <c r="AP7" s="0"/>
+      <c r="AQ7" s="0"/>
+      <c r="AR7" s="0"/>
+      <c r="AS7" s="0"/>
+      <c r="AT7" s="0"/>
+      <c r="AU7" s="0"/>
+      <c r="AV7" s="0"/>
+      <c r="AW7" s="0"/>
+      <c r="AX7" s="0"/>
+      <c r="AY7" s="0"/>
+      <c r="AZ7" s="0"/>
+      <c r="BA7" s="0"/>
+      <c r="BB7" s="0"/>
+      <c r="BC7" s="0"/>
+      <c r="BD7" s="0"/>
+      <c r="BE7" s="0"/>
+      <c r="BF7" s="0"/>
+      <c r="BG7" s="0"/>
+      <c r="BH7" s="0"/>
+      <c r="BI7" s="0"/>
+      <c r="BJ7" s="0"/>
+      <c r="BK7" s="0"/>
+      <c r="BL7" s="0"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="32" t="n">
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="37"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="36"/>
-      <c r="S7" s="37"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="36"/>
-      <c r="AA7" s="36"/>
-      <c r="AB7" s="36"/>
-      <c r="AC7" s="36"/>
-      <c r="AD7" s="36"/>
-      <c r="AE7" s="36"/>
-      <c r="AF7" s="36"/>
-      <c r="AG7" s="36"/>
-      <c r="AH7" s="36"/>
-      <c r="AI7" s="36"/>
-      <c r="AJ7" s="36"/>
-      <c r="AK7" s="39"/>
-      <c r="AL7" s="39"/>
-      <c r="AM7" s="40"/>
-      <c r="AN7" s="40"/>
-      <c r="AO7" s="40"/>
-      <c r="AP7" s="40"/>
-      <c r="AQ7" s="40"/>
-      <c r="AR7" s="40"/>
-      <c r="AS7" s="40"/>
-      <c r="AT7" s="40"/>
-      <c r="AU7" s="40"/>
-      <c r="AV7" s="40"/>
-      <c r="AW7" s="40"/>
-      <c r="AX7" s="40"/>
-      <c r="AY7" s="40"/>
-      <c r="AZ7" s="40"/>
-      <c r="BA7" s="40"/>
-      <c r="BB7" s="40"/>
-      <c r="BC7" s="40"/>
-      <c r="BD7" s="40"/>
-      <c r="BE7" s="40"/>
-      <c r="BF7" s="40"/>
-      <c r="BG7" s="40"/>
-      <c r="BH7" s="40"/>
-      <c r="BI7" s="40"/>
-      <c r="BJ7" s="40"/>
-      <c r="BK7" s="40"/>
-      <c r="BL7" s="40"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="42"/>
-      <c r="T8" s="2"/>
-      <c r="W8" s="0"/>
-      <c r="X8" s="0"/>
-      <c r="Y8" s="0"/>
-      <c r="Z8" s="0"/>
-      <c r="AA8" s="0"/>
-      <c r="AB8" s="0"/>
-      <c r="AC8" s="0"/>
-      <c r="AD8" s="0"/>
-      <c r="AE8" s="0"/>
-      <c r="AF8" s="0"/>
-      <c r="AG8" s="0"/>
-      <c r="AH8" s="0"/>
-      <c r="AI8" s="0"/>
+      <c r="R8" s="40"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="42"/>
+      <c r="U8" s="42"/>
+      <c r="V8" s="42"/>
+      <c r="W8" s="40"/>
+      <c r="X8" s="40"/>
+      <c r="Y8" s="40"/>
+      <c r="Z8" s="40"/>
+      <c r="AA8" s="40"/>
+      <c r="AB8" s="40"/>
+      <c r="AC8" s="40"/>
+      <c r="AD8" s="40"/>
+      <c r="AE8" s="40"/>
+      <c r="AF8" s="40"/>
+      <c r="AG8" s="40"/>
+      <c r="AH8" s="40"/>
+      <c r="AI8" s="40"/>
       <c r="AJ8" s="0"/>
-      <c r="AK8" s="0"/>
-      <c r="AL8" s="0"/>
+      <c r="AK8" s="43"/>
+      <c r="AL8" s="43"/>
+      <c r="AM8" s="20"/>
+      <c r="AN8" s="44"/>
+      <c r="AO8" s="44"/>
+      <c r="AP8" s="0"/>
+      <c r="AQ8" s="0"/>
+      <c r="AR8" s="0"/>
+      <c r="AS8" s="0"/>
+      <c r="AT8" s="0"/>
+      <c r="AU8" s="0"/>
+      <c r="AV8" s="0"/>
+      <c r="AW8" s="0"/>
+      <c r="AX8" s="0"/>
+      <c r="AY8" s="0"/>
+      <c r="AZ8" s="0"/>
+      <c r="BA8" s="0"/>
+      <c r="BB8" s="0"/>
+      <c r="BC8" s="0"/>
+      <c r="BD8" s="0"/>
+      <c r="BE8" s="0"/>
+      <c r="BF8" s="0"/>
+      <c r="BG8" s="0"/>
+      <c r="BH8" s="0"/>
+      <c r="BI8" s="0"/>
+      <c r="BJ8" s="0"/>
+      <c r="BK8" s="0"/>
+      <c r="BL8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="41"/>
-      <c r="D9" s="0"/>
-      <c r="E9" s="0"/>
-      <c r="F9" s="0"/>
-      <c r="G9" s="0"/>
-      <c r="H9" s="0"/>
-      <c r="I9" s="0"/>
-      <c r="J9" s="0"/>
-      <c r="K9" s="0"/>
-      <c r="L9" s="0"/>
-      <c r="M9" s="0"/>
-      <c r="N9" s="0"/>
-      <c r="O9" s="0"/>
-      <c r="P9" s="0"/>
-      <c r="Q9" s="0"/>
-      <c r="R9" s="0"/>
-      <c r="S9" s="0"/>
-      <c r="T9" s="0"/>
-      <c r="U9" s="0"/>
-      <c r="V9" s="0"/>
+      <c r="B9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="T9" s="2"/>
       <c r="W9" s="0"/>
       <c r="X9" s="0"/>
       <c r="Y9" s="0"/>
@@ -1454,6 +1553,7 @@
       <c r="AL9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="45"/>
       <c r="D10" s="0"/>
       <c r="E10" s="0"/>
       <c r="F10" s="0"/>
@@ -1491,47 +1591,21 @@
       <c r="AL10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="B11" s="44"/>
-      <c r="C11" s="45" t="n">
-        <f aca="false">A11+A13</f>
-        <v>7</v>
-      </c>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="43" t="n">
-        <f aca="false">C11</f>
-        <v>7</v>
-      </c>
-      <c r="G11" s="44"/>
-      <c r="H11" s="45" t="n">
-        <f aca="false">F11+F13</f>
-        <v>10</v>
-      </c>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
-      <c r="K11" s="43" t="n">
-        <f aca="false">MAX(H11,H17,H23)</f>
-        <v>13</v>
-      </c>
-      <c r="L11" s="44"/>
-      <c r="M11" s="45" t="n">
-        <f aca="false">K11+K13</f>
-        <v>14</v>
-      </c>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
       <c r="N11" s="0"/>
       <c r="O11" s="0"/>
-      <c r="P11" s="43" t="n">
-        <f aca="false">M11</f>
-        <v>14</v>
-      </c>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="45" t="n">
-        <f aca="false">P11+P13</f>
-        <v>15</v>
-      </c>
+      <c r="P11" s="0"/>
+      <c r="Q11" s="0"/>
+      <c r="R11" s="0"/>
       <c r="S11" s="0"/>
       <c r="T11" s="0"/>
       <c r="U11" s="0"/>
@@ -1554,32 +1628,47 @@
       <c r="AL11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
+      <c r="A12" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" s="48"/>
+      <c r="C12" s="49" t="n">
+        <f aca="false">A12+A14</f>
+        <v>7</v>
+      </c>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="47" t="n">
+        <f aca="false">C12</f>
         <v>7</v>
       </c>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="49" t="n">
+        <f aca="false">F12+F14</f>
+        <v>10</v>
+      </c>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
+      <c r="K12" s="47" t="n">
+        <f aca="false">MAX(H12,H18,H24)</f>
+        <v>13</v>
+      </c>
+      <c r="L12" s="48"/>
+      <c r="M12" s="49" t="n">
+        <f aca="false">K12+K14</f>
+        <v>14</v>
+      </c>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
-      <c r="P12" s="46" t="s">
+      <c r="P12" s="47" t="n">
+        <f aca="false">M12</f>
         <v>14</v>
       </c>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="46"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="49" t="n">
+        <f aca="false">P12+P14</f>
+        <v>15</v>
+      </c>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
       <c r="U12" s="0"/>
@@ -1601,48 +1690,33 @@
       <c r="AK12" s="0"/>
       <c r="AL12" s="0"/>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="47" t="n">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="50"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="48" t="n">
-        <f aca="false">C14-C11</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="47" t="n">
-        <f aca="false">Q3</f>
-        <v>3</v>
-      </c>
-      <c r="G13" s="48" t="n">
-        <f aca="false">H14-H11</f>
-        <v>3</v>
-      </c>
-      <c r="H13" s="49"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="47" t="n">
-        <f aca="false">Q6</f>
-        <v>1</v>
-      </c>
-      <c r="L13" s="48" t="n">
-        <f aca="false">M14-M11</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="49"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="47" t="n">
-        <f aca="false">Q7</f>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="48" t="n">
-        <f aca="false">R14-R11</f>
-        <v>0</v>
-      </c>
-      <c r="R13" s="49"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="0"/>
+      <c r="J13" s="0"/>
+      <c r="K13" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="0"/>
+      <c r="O13" s="0"/>
+      <c r="P13" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
       <c r="S13" s="0"/>
       <c r="T13" s="0"/>
       <c r="U13" s="0"/>
@@ -1664,49 +1738,48 @@
       <c r="AK13" s="0"/>
       <c r="AL13" s="0"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="53" t="n">
-        <f aca="false">C14-A13</f>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="52" t="n">
+        <f aca="false">C15-C12</f>
         <v>0</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="54" t="n">
-        <f aca="false">MIN(F26,F20,F14)</f>
-        <v>7</v>
-      </c>
-      <c r="D14" s="55"/>
-      <c r="E14" s="0"/>
-      <c r="F14" s="53" t="n">
-        <f aca="false">H14-F13</f>
-        <v>10</v>
-      </c>
-      <c r="G14" s="41"/>
-      <c r="H14" s="54" t="n">
-        <f aca="false">K14</f>
-        <v>13</v>
-      </c>
-      <c r="I14" s="0"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="53" t="n">
-        <f aca="false">M14-K13</f>
-        <v>13</v>
-      </c>
-      <c r="L14" s="41"/>
-      <c r="M14" s="54" t="n">
-        <f aca="false">P14</f>
-        <v>14</v>
-      </c>
-      <c r="N14" s="0"/>
-      <c r="O14" s="0"/>
-      <c r="P14" s="53" t="n">
-        <f aca="false">R14-P13</f>
-        <v>14</v>
-      </c>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="54" t="n">
-        <f aca="false">R11</f>
-        <v>15</v>
-      </c>
+      <c r="C14" s="53"/>
+      <c r="D14" s="54"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="51" t="n">
+        <f aca="false">Q3</f>
+        <v>3</v>
+      </c>
+      <c r="G14" s="56" t="n">
+        <f aca="false">H15-H12</f>
+        <v>3</v>
+      </c>
+      <c r="H14" s="53"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="51" t="n">
+        <f aca="false">Q7</f>
+        <v>1</v>
+      </c>
+      <c r="L14" s="52" t="n">
+        <f aca="false">M15-M12</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="53"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="55"/>
+      <c r="P14" s="51" t="n">
+        <f aca="false">Q8</f>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="52" t="n">
+        <f aca="false">R15-R12</f>
+        <v>0</v>
+      </c>
+      <c r="R14" s="53"/>
       <c r="S14" s="0"/>
       <c r="T14" s="0"/>
       <c r="U14" s="0"/>
@@ -1729,21 +1802,48 @@
       <c r="AL14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="55"/>
+      <c r="A15" s="58" t="n">
+        <f aca="false">C15-A14</f>
+        <v>0</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="59" t="n">
+        <f aca="false">MIN(F27,F21,F15)</f>
+        <v>7</v>
+      </c>
+      <c r="D15" s="60"/>
       <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
+      <c r="F15" s="58" t="n">
+        <f aca="false">H15-F14</f>
+        <v>10</v>
+      </c>
+      <c r="G15" s="45"/>
+      <c r="H15" s="59" t="n">
+        <f aca="false">K15</f>
+        <v>13</v>
+      </c>
       <c r="I15" s="0"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="0"/>
-      <c r="L15" s="0"/>
-      <c r="M15" s="0"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="58" t="n">
+        <f aca="false">M15-K14</f>
+        <v>13</v>
+      </c>
+      <c r="L15" s="45"/>
+      <c r="M15" s="59" t="n">
+        <f aca="false">P15</f>
+        <v>14</v>
+      </c>
       <c r="N15" s="0"/>
       <c r="O15" s="0"/>
-      <c r="P15" s="0"/>
-      <c r="Q15" s="0"/>
-      <c r="R15" s="0"/>
+      <c r="P15" s="58" t="n">
+        <f aca="false">R15-P14</f>
+        <v>14</v>
+      </c>
+      <c r="Q15" s="45"/>
+      <c r="R15" s="59" t="n">
+        <f aca="false">R12</f>
+        <v>15</v>
+      </c>
       <c r="S15" s="0"/>
       <c r="T15" s="0"/>
       <c r="U15" s="0"/>
@@ -1766,13 +1866,13 @@
       <c r="AL15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="55"/>
+      <c r="D16" s="60"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0"/>
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
-      <c r="J16" s="56"/>
+      <c r="J16" s="61"/>
       <c r="K16" s="0"/>
       <c r="L16" s="0"/>
       <c r="M16" s="0"/>
@@ -1803,19 +1903,13 @@
       <c r="AL16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="55"/>
+      <c r="D17" s="60"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="43" t="n">
-        <f aca="false">C11</f>
-        <v>7</v>
-      </c>
-      <c r="G17" s="44"/>
-      <c r="H17" s="45" t="n">
-        <f aca="false">F17+F19</f>
-        <v>13</v>
-      </c>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
       <c r="I17" s="0"/>
-      <c r="J17" s="56"/>
+      <c r="J17" s="61"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0"/>
       <c r="M17" s="0"/>
@@ -1846,15 +1940,19 @@
       <c r="AL17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="55"/>
+      <c r="D18" s="60"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
+      <c r="F18" s="47" t="n">
+        <f aca="false">C12</f>
+        <v>7</v>
+      </c>
+      <c r="G18" s="48"/>
+      <c r="H18" s="49" t="n">
+        <f aca="false">F18+F20</f>
+        <v>13</v>
+      </c>
       <c r="I18" s="0"/>
-      <c r="J18" s="56"/>
+      <c r="J18" s="61"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
       <c r="M18" s="0"/>
@@ -1864,6 +1962,9 @@
       <c r="Q18" s="0"/>
       <c r="R18" s="0"/>
       <c r="S18" s="0"/>
+      <c r="T18" s="0"/>
+      <c r="U18" s="0"/>
+      <c r="V18" s="0"/>
       <c r="W18" s="0"/>
       <c r="X18" s="0"/>
       <c r="Y18" s="0"/>
@@ -1881,20 +1982,16 @@
       <c r="AK18" s="0"/>
       <c r="AL18" s="0"/>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="55"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="47" t="n">
-        <f aca="false">Q4</f>
-        <v>6</v>
-      </c>
-      <c r="G19" s="48" t="n">
-        <f aca="false">H20-H17</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="49"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="56"/>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="60"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="0"/>
+      <c r="J19" s="61"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0"/>
       <c r="M19" s="0"/>
@@ -1921,20 +2018,20 @@
       <c r="AK19" s="0"/>
       <c r="AL19" s="0"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="55"/>
-      <c r="E20" s="0"/>
-      <c r="F20" s="53" t="n">
-        <f aca="false">H20-F19</f>
-        <v>7</v>
-      </c>
-      <c r="G20" s="41"/>
-      <c r="H20" s="54" t="n">
-        <f aca="false">K14</f>
-        <v>13</v>
-      </c>
-      <c r="I20" s="0"/>
-      <c r="J20" s="56"/>
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D20" s="60"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="51" t="n">
+        <f aca="false">Q4</f>
+        <v>6</v>
+      </c>
+      <c r="G20" s="52" t="n">
+        <f aca="false">H21-H18</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="53"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="61"/>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
       <c r="M20" s="0"/>
@@ -1962,14 +2059,19 @@
       <c r="AL20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="D21" s="55"/>
+      <c r="D21" s="60"/>
       <c r="E21" s="0"/>
-      <c r="F21" s="0"/>
-      <c r="G21" s="0"/>
-      <c r="H21" s="0"/>
+      <c r="F21" s="58" t="n">
+        <f aca="false">H21-F20</f>
+        <v>7</v>
+      </c>
+      <c r="G21" s="45"/>
+      <c r="H21" s="59" t="n">
+        <f aca="false">K15</f>
+        <v>13</v>
+      </c>
       <c r="I21" s="0"/>
-      <c r="J21" s="56"/>
+      <c r="J21" s="61"/>
       <c r="K21" s="0"/>
       <c r="L21" s="0"/>
       <c r="M21" s="0"/>
@@ -1998,13 +2100,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="D22" s="55"/>
+      <c r="D22" s="60"/>
       <c r="E22" s="0"/>
       <c r="F22" s="0"/>
       <c r="G22" s="0"/>
       <c r="H22" s="0"/>
       <c r="I22" s="0"/>
-      <c r="J22" s="56"/>
+      <c r="J22" s="61"/>
       <c r="K22" s="0"/>
       <c r="L22" s="0"/>
       <c r="M22" s="0"/>
@@ -2033,19 +2135,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="D23" s="55"/>
+      <c r="D23" s="60"/>
       <c r="E23" s="0"/>
-      <c r="F23" s="43" t="n">
-        <f aca="false">C11</f>
-        <v>7</v>
-      </c>
-      <c r="G23" s="44"/>
-      <c r="H23" s="45" t="n">
-        <f aca="false">F23+F25</f>
-        <v>10</v>
-      </c>
+      <c r="F23" s="0"/>
+      <c r="G23" s="0"/>
+      <c r="H23" s="0"/>
       <c r="I23" s="0"/>
-      <c r="J23" s="56"/>
+      <c r="J23" s="61"/>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
       <c r="M23" s="0"/>
@@ -2055,20 +2151,38 @@
       <c r="Q23" s="0"/>
       <c r="R23" s="0"/>
       <c r="S23" s="0"/>
+      <c r="W23" s="0"/>
+      <c r="X23" s="0"/>
+      <c r="Y23" s="0"/>
+      <c r="Z23" s="0"/>
+      <c r="AA23" s="0"/>
+      <c r="AB23" s="0"/>
+      <c r="AC23" s="0"/>
+      <c r="AD23" s="0"/>
+      <c r="AE23" s="0"/>
+      <c r="AF23" s="0"/>
+      <c r="AG23" s="0"/>
+      <c r="AH23" s="0"/>
+      <c r="AI23" s="0"/>
+      <c r="AJ23" s="0"/>
+      <c r="AK23" s="0"/>
+      <c r="AL23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0"/>
-      <c r="B24" s="0"/>
-      <c r="C24" s="0"/>
-      <c r="D24" s="55"/>
+      <c r="A24" s="2"/>
+      <c r="D24" s="60"/>
       <c r="E24" s="0"/>
-      <c r="F24" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
+      <c r="F24" s="47" t="n">
+        <f aca="false">C12</f>
+        <v>7</v>
+      </c>
+      <c r="G24" s="48"/>
+      <c r="H24" s="49" t="n">
+        <f aca="false">F24+F26</f>
+        <v>10</v>
+      </c>
       <c r="I24" s="0"/>
-      <c r="J24" s="56"/>
+      <c r="J24" s="61"/>
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
       <c r="M24" s="0"/>
@@ -2079,23 +2193,19 @@
       <c r="R24" s="0"/>
       <c r="S24" s="0"/>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0"/>
       <c r="B25" s="0"/>
       <c r="C25" s="0"/>
-      <c r="D25" s="0"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="47" t="n">
-        <f aca="false">Q5</f>
-        <v>3</v>
-      </c>
-      <c r="G25" s="48" t="n">
-        <f aca="false">H26-H23</f>
-        <v>3</v>
-      </c>
-      <c r="H25" s="49"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="0"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="0"/>
+      <c r="F25" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="0"/>
+      <c r="J25" s="61"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
       <c r="M25" s="0"/>
@@ -2106,25 +2216,32 @@
       <c r="R25" s="0"/>
       <c r="S25" s="0"/>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0"/>
       <c r="B26" s="0"/>
       <c r="C26" s="0"/>
       <c r="D26" s="0"/>
-      <c r="E26" s="0"/>
-      <c r="F26" s="53" t="n">
-        <f aca="false">H26-F25</f>
-        <v>10</v>
-      </c>
-      <c r="G26" s="41"/>
-      <c r="H26" s="54" t="n">
-        <f aca="false">K14</f>
-        <v>13</v>
-      </c>
-      <c r="I26" s="0"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="51" t="n">
+        <f aca="false">Q5</f>
+        <v>3</v>
+      </c>
+      <c r="G26" s="56" t="n">
+        <f aca="false">H27-H24</f>
+        <v>3</v>
+      </c>
+      <c r="H26" s="53"/>
+      <c r="I26" s="55"/>
       <c r="J26" s="0"/>
       <c r="K26" s="0"/>
       <c r="L26" s="0"/>
+      <c r="M26" s="0"/>
+      <c r="N26" s="0"/>
+      <c r="O26" s="0"/>
+      <c r="P26" s="0"/>
+      <c r="Q26" s="0"/>
+      <c r="R26" s="0"/>
+      <c r="S26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0"/>
@@ -2132,9 +2249,15 @@
       <c r="C27" s="0"/>
       <c r="D27" s="0"/>
       <c r="E27" s="0"/>
-      <c r="F27" s="0"/>
-      <c r="G27" s="0"/>
-      <c r="H27" s="0"/>
+      <c r="F27" s="58" t="n">
+        <f aca="false">H27-F26</f>
+        <v>10</v>
+      </c>
+      <c r="G27" s="45"/>
+      <c r="H27" s="59" t="n">
+        <f aca="false">K15</f>
+        <v>13</v>
+      </c>
       <c r="I27" s="0"/>
       <c r="J27" s="0"/>
       <c r="K27" s="0"/>
@@ -2281,214 +2404,228 @@
       <c r="L37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="57"/>
-      <c r="B38" s="58"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="58"/>
+      <c r="A38" s="0"/>
+      <c r="B38" s="0"/>
+      <c r="C38" s="0"/>
+      <c r="D38" s="0"/>
+      <c r="E38" s="0"/>
+      <c r="F38" s="0"/>
+      <c r="G38" s="0"/>
+      <c r="H38" s="0"/>
+      <c r="I38" s="0"/>
+      <c r="J38" s="0"/>
+      <c r="K38" s="0"/>
+      <c r="L38" s="0"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="57"/>
-      <c r="B39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="A39" s="62"/>
+      <c r="B39" s="63"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="63"/>
+      <c r="J39" s="63"/>
+      <c r="K39" s="63"/>
+      <c r="L39" s="63"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="62"/>
+      <c r="B40" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="58"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="57"/>
-      <c r="B40" s="59" t="s">
+      <c r="D40" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" s="63"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="62"/>
+      <c r="B41" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="F40" s="60" t="s">
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
+      <c r="F41" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="65"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="L41" s="63"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="62"/>
+      <c r="B42" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="63"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="62"/>
+      <c r="B43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="63"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="62"/>
+      <c r="L44" s="63"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="62"/>
+      <c r="B45" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="45"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="45"/>
+      <c r="I45" s="45"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="63"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="62"/>
+      <c r="B46" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="45"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="63"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="62"/>
+      <c r="B47" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
-      <c r="I40" s="60"/>
-      <c r="J40" s="60"/>
-      <c r="L40" s="58"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="57"/>
-      <c r="B41" s="61" t="s">
+      <c r="C47" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="45"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="45"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="63"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="62"/>
+      <c r="B48" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="45"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="63"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="62"/>
+      <c r="B49" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="61" t="s">
+      <c r="C49" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="45"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="45"/>
+      <c r="H49" s="45"/>
+      <c r="I49" s="45"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="63"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="62"/>
+      <c r="B50" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="L41" s="58"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="57"/>
-      <c r="B42" s="2" t="s">
+      <c r="C50" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="45"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
+      <c r="I50" s="45"/>
+      <c r="J50" s="45"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="63"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="62"/>
+      <c r="B51" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L42" s="58"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="57"/>
-      <c r="L43" s="58"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="57"/>
-      <c r="B44" s="63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="58"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="57"/>
-      <c r="B45" s="63" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="58"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="57"/>
-      <c r="B46" s="63" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="58"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="57"/>
-      <c r="B47" s="63" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="41"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="58"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="57"/>
-      <c r="B48" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="41"/>
-      <c r="J48" s="41"/>
-      <c r="K48" s="41"/>
-      <c r="L48" s="58"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="57"/>
-      <c r="B49" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="58"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="57"/>
-      <c r="B50" s="64" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="58"/>
-      <c r="K50" s="58"/>
-      <c r="L50" s="58"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="57"/>
-      <c r="B51" s="58"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
-      <c r="I51" s="58"/>
-      <c r="J51" s="58"/>
-      <c r="K51" s="58"/>
-      <c r="L51" s="58"/>
+      <c r="C51" s="63" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="63"/>
+      <c r="J51" s="63"/>
+      <c r="K51" s="63"/>
+      <c r="L51" s="63"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="62"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="63"/>
+      <c r="J52" s="63"/>
+      <c r="K52" s="63"/>
+      <c r="L52" s="63"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:P1"/>
@@ -2498,22 +2635,23 @@
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:J40"/>
-    <mergeCell ref="C44:K44"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="P13:R13"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="F41:J41"/>
     <mergeCell ref="C45:K45"/>
     <mergeCell ref="C46:K46"/>
     <mergeCell ref="C47:K47"/>
     <mergeCell ref="C48:K48"/>
     <mergeCell ref="C49:K49"/>
+    <mergeCell ref="C50:K50"/>
   </mergeCells>
-  <conditionalFormatting sqref="R1:BL7">
+  <conditionalFormatting sqref="AD1:AO3 AK4:AL4 AN4:AO4 AD5:AO5 R6:Y6 AK6:AO8 AD7:AH7 AD6:AH6 AJ6:AJ7 AD8:AI8 AD4:AH4 R2:AC5 R7:AC8 R1:AA5 AB1:AC1">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>IF(WEEKDAY(R$1,2)=6,1,IF(WEEKDAY(R$1,2)=7,1,0))</formula>
     </cfRule>
@@ -2525,5 +2663,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Übungen/02_Netzplan_Firmennetzwerk.xlsx
+++ b/Übungen/02_Netzplan_Firmennetzwerk.xlsx
@@ -119,8 +119,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -186,7 +188,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,7 +198,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAADCF7"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF729FCF"/>
+        <bgColor rgb="FF999999"/>
       </patternFill>
     </fill>
     <fill>
@@ -380,7 +388,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -413,6 +421,18 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -421,15 +441,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -445,6 +465,18 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -481,16 +513,28 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -501,31 +545,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -541,11 +585,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -557,15 +601,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -573,19 +617,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -602,12 +646,15 @@
   <dxfs count="1">
     <dxf>
       <font>
-        <name val="Alegreya Sans"/>
+        <name val="Arial"/>
         <charset val="1"/>
-        <family val="3"/>
-        <b val="1"/>
-        <color rgb="FFFF0000"/>
+        <family val="2"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDDDDD"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -628,14 +675,14 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB2B2B2"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF729FCF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -678,19 +725,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AL51"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BN51"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="2" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="3" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="4.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="3.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="20" style="4" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="36" style="2" width="3.83"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="40.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -718,225 +765,470 @@
       <c r="Q1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="R1" s="0"/>
-      <c r="T1" s="2"/>
-      <c r="W1" s="0"/>
-      <c r="X1" s="0"/>
-      <c r="Y1" s="0"/>
-      <c r="Z1" s="0"/>
-      <c r="AA1" s="0"/>
-      <c r="AB1" s="0"/>
-      <c r="AC1" s="0"/>
-      <c r="AD1" s="0"/>
-      <c r="AE1" s="0"/>
-      <c r="AF1" s="0"/>
-      <c r="AG1" s="0"/>
-      <c r="AH1" s="0"/>
-      <c r="AI1" s="0"/>
-      <c r="AJ1" s="0"/>
-      <c r="AK1" s="0"/>
-      <c r="AL1" s="0"/>
+      <c r="R1" s="8" t="n">
+        <v>44606</v>
+      </c>
+      <c r="S1" s="8" t="n">
+        <v>44607</v>
+      </c>
+      <c r="T1" s="8" t="n">
+        <v>44608</v>
+      </c>
+      <c r="U1" s="8" t="n">
+        <v>44609</v>
+      </c>
+      <c r="V1" s="8" t="n">
+        <v>44610</v>
+      </c>
+      <c r="W1" s="8" t="n">
+        <v>44611</v>
+      </c>
+      <c r="X1" s="8" t="n">
+        <v>44612</v>
+      </c>
+      <c r="Y1" s="8" t="n">
+        <v>44613</v>
+      </c>
+      <c r="Z1" s="8" t="n">
+        <v>44614</v>
+      </c>
+      <c r="AA1" s="8" t="n">
+        <v>44615</v>
+      </c>
+      <c r="AB1" s="8" t="n">
+        <v>44616</v>
+      </c>
+      <c r="AC1" s="8" t="n">
+        <v>44617</v>
+      </c>
+      <c r="AD1" s="8" t="n">
+        <v>44618</v>
+      </c>
+      <c r="AE1" s="8" t="n">
+        <v>44619</v>
+      </c>
+      <c r="AF1" s="8" t="n">
+        <v>44620</v>
+      </c>
+      <c r="AG1" s="8" t="n">
+        <v>44621</v>
+      </c>
+      <c r="AH1" s="8" t="n">
+        <v>44622</v>
+      </c>
+      <c r="AI1" s="8" t="n">
+        <v>44623</v>
+      </c>
+      <c r="AJ1" s="8" t="n">
+        <v>44624</v>
+      </c>
+      <c r="AK1" s="8" t="n">
+        <v>44625</v>
+      </c>
+      <c r="AL1" s="8" t="n">
+        <v>44626</v>
+      </c>
+      <c r="AM1" s="8" t="n">
+        <v>44627</v>
+      </c>
+      <c r="AN1" s="8" t="n">
+        <v>44628</v>
+      </c>
+      <c r="AO1" s="8" t="n">
+        <v>44629</v>
+      </c>
+      <c r="AP1" s="8" t="n">
+        <v>44630</v>
+      </c>
+      <c r="AQ1" s="8" t="n">
+        <v>44631</v>
+      </c>
+      <c r="AR1" s="8" t="n">
+        <v>44632</v>
+      </c>
+      <c r="AS1" s="8" t="n">
+        <v>44633</v>
+      </c>
+      <c r="AT1" s="8" t="n">
+        <v>44634</v>
+      </c>
+      <c r="AU1" s="8" t="n">
+        <v>44635</v>
+      </c>
+      <c r="AV1" s="8" t="n">
+        <v>44636</v>
+      </c>
+      <c r="AW1" s="8" t="n">
+        <v>44637</v>
+      </c>
+      <c r="AX1" s="8" t="n">
+        <v>44638</v>
+      </c>
+      <c r="AY1" s="8" t="n">
+        <v>44639</v>
+      </c>
+      <c r="AZ1" s="8" t="n">
+        <v>44640</v>
+      </c>
+      <c r="BA1" s="8" t="n">
+        <v>44641</v>
+      </c>
+      <c r="BB1" s="8" t="n">
+        <v>44642</v>
+      </c>
+      <c r="BC1" s="8" t="n">
+        <v>44643</v>
+      </c>
+      <c r="BD1" s="8" t="n">
+        <v>44644</v>
+      </c>
+      <c r="BE1" s="8" t="n">
+        <v>44645</v>
+      </c>
+      <c r="BF1" s="8" t="n">
+        <v>44646</v>
+      </c>
+      <c r="BG1" s="8" t="n">
+        <v>44647</v>
+      </c>
+      <c r="BH1" s="8" t="n">
+        <v>44648</v>
+      </c>
+      <c r="BI1" s="8" t="n">
+        <v>44649</v>
+      </c>
+      <c r="BJ1" s="8" t="n">
+        <v>44650</v>
+      </c>
+      <c r="BK1" s="8" t="n">
+        <v>44651</v>
+      </c>
+      <c r="BL1" s="8" t="n">
+        <v>44652</v>
+      </c>
+      <c r="BM1" s="9"/>
+      <c r="BN1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="13" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="14" t="s">
+      <c r="N2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15" t="n">
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="R2" s="0"/>
-      <c r="W2" s="0"/>
-      <c r="X2" s="0"/>
-      <c r="Y2" s="0"/>
-      <c r="Z2" s="0"/>
-      <c r="AA2" s="0"/>
-      <c r="AB2" s="0"/>
-      <c r="AC2" s="0"/>
-      <c r="AD2" s="0"/>
-      <c r="AE2" s="0"/>
-      <c r="AF2" s="0"/>
-      <c r="AG2" s="0"/>
-      <c r="AH2" s="0"/>
-      <c r="AI2" s="0"/>
-      <c r="AJ2" s="0"/>
-      <c r="AK2" s="0"/>
-      <c r="AL2" s="0"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
+      <c r="Z2" s="19"/>
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="19"/>
+      <c r="AC2" s="19"/>
+      <c r="AD2" s="19"/>
+      <c r="AE2" s="19"/>
+      <c r="AF2" s="19"/>
+      <c r="AG2" s="19"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="19"/>
+      <c r="AJ2" s="19"/>
+      <c r="AK2" s="19"/>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="20"/>
+      <c r="AN2" s="20"/>
+      <c r="AO2" s="20"/>
+      <c r="AP2" s="20"/>
+      <c r="AQ2" s="20"/>
+      <c r="AR2" s="20"/>
+      <c r="AS2" s="20"/>
+      <c r="AT2" s="20"/>
+      <c r="AU2" s="20"/>
+      <c r="AV2" s="20"/>
+      <c r="AW2" s="20"/>
+      <c r="AX2" s="20"/>
+      <c r="AY2" s="20"/>
+      <c r="AZ2" s="20"/>
+      <c r="BA2" s="20"/>
+      <c r="BB2" s="20"/>
+      <c r="BC2" s="20"/>
+      <c r="BD2" s="20"/>
+      <c r="BE2" s="20"/>
+      <c r="BF2" s="20"/>
+      <c r="BG2" s="20"/>
+      <c r="BH2" s="20"/>
+      <c r="BI2" s="20"/>
+      <c r="BJ2" s="20"/>
+      <c r="BK2" s="20"/>
+      <c r="BL2" s="20"/>
     </row>
     <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="18" t="s">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="24" t="s">
         <v>5</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="18" t="s">
+      <c r="L3" s="25"/>
+      <c r="M3" s="24" t="s">
         <v>10</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19" t="n">
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="R3" s="0"/>
-      <c r="W3" s="0"/>
-      <c r="X3" s="0"/>
-      <c r="Y3" s="0"/>
-      <c r="Z3" s="0"/>
-      <c r="AA3" s="0"/>
-      <c r="AB3" s="0"/>
-      <c r="AC3" s="0"/>
-      <c r="AD3" s="0"/>
-      <c r="AE3" s="0"/>
-      <c r="AF3" s="0"/>
-      <c r="AG3" s="0"/>
-      <c r="AH3" s="0"/>
-      <c r="AI3" s="0"/>
-      <c r="AJ3" s="0"/>
-      <c r="AK3" s="0"/>
-      <c r="AL3" s="0"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+      <c r="Z3" s="19"/>
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="19"/>
+      <c r="AF3" s="19"/>
+      <c r="AG3" s="19"/>
+      <c r="AH3" s="19"/>
+      <c r="AI3" s="19"/>
+      <c r="AJ3" s="19"/>
+      <c r="AK3" s="19"/>
+      <c r="AL3" s="19"/>
+      <c r="AM3" s="20"/>
+      <c r="AN3" s="20"/>
+      <c r="AO3" s="20"/>
+      <c r="AP3" s="20"/>
+      <c r="AQ3" s="20"/>
+      <c r="AR3" s="20"/>
+      <c r="AS3" s="20"/>
+      <c r="AT3" s="20"/>
+      <c r="AU3" s="20"/>
+      <c r="AV3" s="20"/>
+      <c r="AW3" s="20"/>
+      <c r="AX3" s="20"/>
+      <c r="AY3" s="20"/>
+      <c r="AZ3" s="20"/>
+      <c r="BA3" s="20"/>
+      <c r="BB3" s="20"/>
+      <c r="BC3" s="20"/>
+      <c r="BD3" s="20"/>
+      <c r="BE3" s="20"/>
+      <c r="BF3" s="20"/>
+      <c r="BG3" s="20"/>
+      <c r="BH3" s="20"/>
+      <c r="BI3" s="20"/>
+      <c r="BJ3" s="20"/>
+      <c r="BK3" s="20"/>
+      <c r="BL3" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18" t="s">
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="24" t="s">
         <v>5</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="18" t="s">
+      <c r="L4" s="25"/>
+      <c r="M4" s="24" t="s">
         <v>10</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19" t="n">
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="0"/>
-      <c r="W4" s="0"/>
-      <c r="X4" s="0"/>
-      <c r="Y4" s="0"/>
-      <c r="Z4" s="0"/>
-      <c r="AA4" s="0"/>
-      <c r="AB4" s="0"/>
-      <c r="AC4" s="0"/>
-      <c r="AD4" s="0"/>
-      <c r="AE4" s="0"/>
-      <c r="AF4" s="0"/>
-      <c r="AG4" s="0"/>
-      <c r="AH4" s="0"/>
-      <c r="AI4" s="0"/>
-      <c r="AJ4" s="0"/>
-      <c r="AK4" s="0"/>
-      <c r="AL4" s="0"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="19"/>
+      <c r="AA4" s="19"/>
+      <c r="AB4" s="19"/>
+      <c r="AC4" s="19"/>
+      <c r="AD4" s="19"/>
+      <c r="AE4" s="19"/>
+      <c r="AF4" s="19"/>
+      <c r="AG4" s="19"/>
+      <c r="AH4" s="19"/>
+      <c r="AI4" s="19"/>
+      <c r="AJ4" s="19"/>
+      <c r="AK4" s="19"/>
+      <c r="AL4" s="19"/>
+      <c r="AM4" s="20"/>
+      <c r="AN4" s="20"/>
+      <c r="AO4" s="20"/>
+      <c r="AP4" s="20"/>
+      <c r="AQ4" s="20"/>
+      <c r="AR4" s="20"/>
+      <c r="AS4" s="20"/>
+      <c r="AT4" s="20"/>
+      <c r="AU4" s="20"/>
+      <c r="AV4" s="20"/>
+      <c r="AW4" s="20"/>
+      <c r="AX4" s="20"/>
+      <c r="AY4" s="20"/>
+      <c r="AZ4" s="20"/>
+      <c r="BA4" s="20"/>
+      <c r="BB4" s="20"/>
+      <c r="BC4" s="20"/>
+      <c r="BD4" s="20"/>
+      <c r="BE4" s="20"/>
+      <c r="BF4" s="20"/>
+      <c r="BG4" s="20"/>
+      <c r="BH4" s="20"/>
+      <c r="BI4" s="20"/>
+      <c r="BJ4" s="20"/>
+      <c r="BK4" s="20"/>
+      <c r="BL4" s="20"/>
     </row>
     <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="24" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="18" t="s">
+      <c r="L5" s="25"/>
+      <c r="M5" s="24" t="s">
         <v>10</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19" t="n">
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="R5" s="0"/>
-      <c r="W5" s="0"/>
-      <c r="X5" s="0"/>
-      <c r="Y5" s="0"/>
-      <c r="Z5" s="0"/>
-      <c r="AA5" s="0"/>
-      <c r="AB5" s="0"/>
-      <c r="AC5" s="0"/>
-      <c r="AD5" s="0"/>
-      <c r="AE5" s="0"/>
-      <c r="AF5" s="0"/>
-      <c r="AG5" s="0"/>
-      <c r="AH5" s="0"/>
-      <c r="AI5" s="0"/>
-      <c r="AJ5" s="0"/>
-      <c r="AK5" s="0"/>
-      <c r="AL5" s="0"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="19"/>
+      <c r="Y5" s="19"/>
+      <c r="Z5" s="19"/>
+      <c r="AA5" s="19"/>
+      <c r="AB5" s="19"/>
+      <c r="AC5" s="19"/>
+      <c r="AD5" s="19"/>
+      <c r="AE5" s="19"/>
+      <c r="AF5" s="19"/>
+      <c r="AG5" s="19"/>
+      <c r="AH5" s="19"/>
+      <c r="AI5" s="19"/>
+      <c r="AJ5" s="19"/>
+      <c r="AK5" s="19"/>
+      <c r="AL5" s="19"/>
+      <c r="AM5" s="20"/>
+      <c r="AN5" s="20"/>
+      <c r="AO5" s="20"/>
+      <c r="AP5" s="20"/>
+      <c r="AQ5" s="20"/>
+      <c r="AR5" s="20"/>
+      <c r="AS5" s="20"/>
+      <c r="AT5" s="20"/>
+      <c r="AU5" s="20"/>
+      <c r="AV5" s="20"/>
+      <c r="AW5" s="20"/>
+      <c r="AX5" s="20"/>
+      <c r="AY5" s="20"/>
+      <c r="AZ5" s="20"/>
+      <c r="BA5" s="20"/>
+      <c r="BB5" s="20"/>
+      <c r="BC5" s="20"/>
+      <c r="BD5" s="20"/>
+      <c r="BE5" s="20"/>
+      <c r="BF5" s="20"/>
+      <c r="BG5" s="20"/>
+      <c r="BH5" s="20"/>
+      <c r="BI5" s="20"/>
+      <c r="BJ5" s="20"/>
+      <c r="BK5" s="20"/>
+      <c r="BL5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="18" t="s">
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="24" t="s">
         <v>7</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -945,90 +1237,150 @@
       <c r="K6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="19"/>
-      <c r="M6" s="18" t="s">
+      <c r="L6" s="25"/>
+      <c r="M6" s="24" t="s">
         <v>14</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19" t="n">
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="R6" s="0"/>
-      <c r="W6" s="0"/>
-      <c r="X6" s="0"/>
-      <c r="Y6" s="0"/>
-      <c r="Z6" s="0"/>
-      <c r="AA6" s="0"/>
-      <c r="AB6" s="0"/>
-      <c r="AC6" s="0"/>
-      <c r="AD6" s="0"/>
-      <c r="AE6" s="0"/>
-      <c r="AF6" s="0"/>
-      <c r="AG6" s="0"/>
-      <c r="AH6" s="0"/>
-      <c r="AI6" s="0"/>
-      <c r="AJ6" s="0"/>
-      <c r="AK6" s="0"/>
-      <c r="AL6" s="0"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="19"/>
+      <c r="AI6" s="19"/>
+      <c r="AJ6" s="19"/>
+      <c r="AK6" s="19"/>
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="20"/>
+      <c r="AN6" s="20"/>
+      <c r="AO6" s="20"/>
+      <c r="AP6" s="20"/>
+      <c r="AQ6" s="20"/>
+      <c r="AR6" s="20"/>
+      <c r="AS6" s="20"/>
+      <c r="AT6" s="20"/>
+      <c r="AU6" s="20"/>
+      <c r="AV6" s="20"/>
+      <c r="AW6" s="20"/>
+      <c r="AX6" s="20"/>
+      <c r="AY6" s="20"/>
+      <c r="AZ6" s="20"/>
+      <c r="BA6" s="20"/>
+      <c r="BB6" s="20"/>
+      <c r="BC6" s="20"/>
+      <c r="BD6" s="20"/>
+      <c r="BE6" s="20"/>
+      <c r="BF6" s="20"/>
+      <c r="BG6" s="20"/>
+      <c r="BH6" s="20"/>
+      <c r="BI6" s="20"/>
+      <c r="BJ6" s="20"/>
+      <c r="BK6" s="20"/>
+      <c r="BL6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="22" t="s">
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="24" t="n">
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="0"/>
-      <c r="W7" s="0"/>
-      <c r="X7" s="0"/>
-      <c r="Y7" s="0"/>
-      <c r="Z7" s="0"/>
-      <c r="AA7" s="0"/>
-      <c r="AB7" s="0"/>
-      <c r="AC7" s="0"/>
-      <c r="AD7" s="0"/>
-      <c r="AE7" s="0"/>
-      <c r="AF7" s="0"/>
-      <c r="AG7" s="0"/>
-      <c r="AH7" s="0"/>
-      <c r="AI7" s="0"/>
-      <c r="AJ7" s="0"/>
-      <c r="AK7" s="0"/>
-      <c r="AL7" s="0"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="34"/>
+      <c r="Y7" s="34"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="34"/>
+      <c r="AB7" s="34"/>
+      <c r="AC7" s="34"/>
+      <c r="AD7" s="34"/>
+      <c r="AE7" s="34"/>
+      <c r="AF7" s="34"/>
+      <c r="AG7" s="34"/>
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="34"/>
+      <c r="AJ7" s="34"/>
+      <c r="AK7" s="34"/>
+      <c r="AL7" s="34"/>
+      <c r="AM7" s="35"/>
+      <c r="AN7" s="35"/>
+      <c r="AO7" s="35"/>
+      <c r="AP7" s="35"/>
+      <c r="AQ7" s="35"/>
+      <c r="AR7" s="35"/>
+      <c r="AS7" s="35"/>
+      <c r="AT7" s="35"/>
+      <c r="AU7" s="35"/>
+      <c r="AV7" s="35"/>
+      <c r="AW7" s="35"/>
+      <c r="AX7" s="35"/>
+      <c r="AY7" s="35"/>
+      <c r="AZ7" s="35"/>
+      <c r="BA7" s="35"/>
+      <c r="BB7" s="35"/>
+      <c r="BC7" s="35"/>
+      <c r="BD7" s="35"/>
+      <c r="BE7" s="35"/>
+      <c r="BF7" s="35"/>
+      <c r="BG7" s="35"/>
+      <c r="BH7" s="35"/>
+      <c r="BI7" s="35"/>
+      <c r="BJ7" s="35"/>
+      <c r="BK7" s="35"/>
+      <c r="BL7" s="35"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="29"/>
+      <c r="B8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="38"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
       <c r="T8" s="2"/>
       <c r="W8" s="0"/>
       <c r="X8" s="0"/>
@@ -1048,7 +1400,7 @@
       <c r="AL8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="28"/>
+      <c r="B9" s="37"/>
       <c r="D9" s="0"/>
       <c r="E9" s="0"/>
       <c r="F9" s="0"/>
@@ -1123,38 +1475,45 @@
       <c r="AL10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="32" t="n">
+      <c r="B11" s="40"/>
+      <c r="C11" s="41" t="n">
+        <f aca="false">A11+A13</f>
         <v>7</v>
       </c>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="39" t="n">
+        <f aca="false">C11</f>
         <v>7</v>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32" t="n">
+      <c r="G11" s="40"/>
+      <c r="H11" s="41" t="n">
+        <f aca="false">F11+F13</f>
         <v>10</v>
       </c>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
-      <c r="K11" s="30" t="n">
+      <c r="K11" s="39" t="n">
+        <f aca="false">MAX(H11,H17,H23)</f>
         <v>13</v>
       </c>
-      <c r="L11" s="31"/>
-      <c r="M11" s="32" t="n">
+      <c r="L11" s="40"/>
+      <c r="M11" s="41" t="n">
+        <f aca="false">K11+K13</f>
         <v>14</v>
       </c>
       <c r="N11" s="0"/>
       <c r="O11" s="0"/>
-      <c r="P11" s="30" t="n">
+      <c r="P11" s="39" t="n">
+        <f aca="false">M11</f>
         <v>14</v>
       </c>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="32" t="n">
+      <c r="Q11" s="40"/>
+      <c r="R11" s="41" t="n">
+        <f aca="false">P11+P13</f>
         <v>15</v>
       </c>
       <c r="S11" s="0"/>
@@ -1179,32 +1538,32 @@
       <c r="AL11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="33" t="s">
+      <c r="F12" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="33" t="s">
+      <c r="K12" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
-      <c r="P12" s="33" t="s">
+      <c r="P12" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
       <c r="U12" s="0"/>
@@ -1226,50 +1585,48 @@
       <c r="AK12" s="0"/>
       <c r="AL12" s="0"/>
     </row>
-    <row r="13" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="n">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="44" t="n">
+        <f aca="false">C14-C11</f>
         <v>0</v>
       </c>
-      <c r="C13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="34" t="n">
+      <c r="C13" s="45"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="43" t="n">
         <f aca="false">Q3</f>
         <v>3</v>
       </c>
-      <c r="G13" s="35" t="n">
+      <c r="G13" s="44" t="n">
+        <f aca="false">H14-H11</f>
         <v>3</v>
       </c>
-      <c r="H13" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="38"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="34" t="n">
+      <c r="H13" s="45"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="43" t="n">
         <f aca="false">Q6</f>
         <v>1</v>
       </c>
-      <c r="L13" s="35" t="n">
+      <c r="L13" s="44" t="n">
+        <f aca="false">M14-M11</f>
         <v>0</v>
       </c>
-      <c r="M13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="34" t="n">
+      <c r="M13" s="45"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="43" t="n">
         <f aca="false">Q7</f>
         <v>1</v>
       </c>
-      <c r="Q13" s="35" t="n">
+      <c r="Q13" s="44" t="n">
+        <f aca="false">R14-R11</f>
         <v>0</v>
       </c>
-      <c r="R13" s="36"/>
+      <c r="R13" s="45"/>
       <c r="S13" s="0"/>
       <c r="T13" s="0"/>
       <c r="U13" s="0"/>
@@ -1292,38 +1649,46 @@
       <c r="AL13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="40" t="n">
+      <c r="A14" s="49" t="n">
+        <f aca="false">C14-A13</f>
         <v>0</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="41" t="n">
+      <c r="B14" s="37"/>
+      <c r="C14" s="50" t="n">
+        <f aca="false">MIN(F26,F20,F14)</f>
         <v>7</v>
       </c>
-      <c r="D14" s="42"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="0"/>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="49" t="n">
+        <f aca="false">H14-F13</f>
         <v>10</v>
       </c>
-      <c r="G14" s="28"/>
-      <c r="H14" s="41" t="n">
+      <c r="G14" s="37"/>
+      <c r="H14" s="50" t="n">
+        <f aca="false">K14</f>
         <v>13</v>
       </c>
       <c r="I14" s="0"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="40" t="n">
+      <c r="J14" s="52"/>
+      <c r="K14" s="49" t="n">
+        <f aca="false">M14-K13</f>
         <v>13</v>
       </c>
-      <c r="L14" s="28"/>
-      <c r="M14" s="41" t="n">
+      <c r="L14" s="37"/>
+      <c r="M14" s="50" t="n">
+        <f aca="false">P14</f>
         <v>14</v>
       </c>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
-      <c r="P14" s="40" t="n">
+      <c r="P14" s="49" t="n">
+        <f aca="false">R14-P13</f>
         <v>14</v>
       </c>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="41" t="n">
+      <c r="Q14" s="37"/>
+      <c r="R14" s="50" t="n">
+        <f aca="false">R11</f>
         <v>15</v>
       </c>
       <c r="S14" s="0"/>
@@ -1348,13 +1713,13 @@
       <c r="AL14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="42"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="0"/>
       <c r="F15" s="0"/>
       <c r="G15" s="0"/>
       <c r="H15" s="0"/>
       <c r="I15" s="0"/>
-      <c r="J15" s="43"/>
+      <c r="J15" s="52"/>
       <c r="K15" s="0"/>
       <c r="L15" s="0"/>
       <c r="M15" s="0"/>
@@ -1385,13 +1750,13 @@
       <c r="AL15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="42"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0"/>
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
-      <c r="J16" s="43"/>
+      <c r="J16" s="52"/>
       <c r="K16" s="0"/>
       <c r="L16" s="0"/>
       <c r="M16" s="0"/>
@@ -1422,17 +1787,19 @@
       <c r="AL16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="42"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="39" t="n">
+        <f aca="false">C11</f>
         <v>7</v>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="32" t="n">
+      <c r="G17" s="40"/>
+      <c r="H17" s="41" t="n">
+        <f aca="false">F17+F19</f>
         <v>13</v>
       </c>
       <c r="I17" s="0"/>
-      <c r="J17" s="43"/>
+      <c r="J17" s="52"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0"/>
       <c r="M17" s="0"/>
@@ -1463,15 +1830,15 @@
       <c r="AL17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="42"/>
+      <c r="D18" s="51"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="33" t="s">
+      <c r="F18" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
       <c r="I18" s="0"/>
-      <c r="J18" s="43"/>
+      <c r="J18" s="52"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
       <c r="M18" s="0"/>
@@ -1498,21 +1865,20 @@
       <c r="AK18" s="0"/>
       <c r="AL18" s="0"/>
     </row>
-    <row r="19" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="42"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="34" t="n">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="51"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="43" t="n">
         <f aca="false">Q4</f>
         <v>6</v>
       </c>
-      <c r="G19" s="35" t="n">
+      <c r="G19" s="44" t="n">
+        <f aca="false">H20-H17</f>
         <v>0</v>
       </c>
-      <c r="H19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="38"/>
-      <c r="J19" s="43"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="52"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0"/>
       <c r="M19" s="0"/>
@@ -1540,17 +1906,19 @@
       <c r="AL19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="42"/>
+      <c r="D20" s="51"/>
       <c r="E20" s="0"/>
-      <c r="F20" s="40" t="n">
+      <c r="F20" s="49" t="n">
+        <f aca="false">H20-F19</f>
         <v>7</v>
       </c>
-      <c r="G20" s="28"/>
-      <c r="H20" s="41" t="n">
+      <c r="G20" s="37"/>
+      <c r="H20" s="50" t="n">
+        <f aca="false">K14</f>
         <v>13</v>
       </c>
       <c r="I20" s="0"/>
-      <c r="J20" s="43"/>
+      <c r="J20" s="52"/>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
       <c r="M20" s="0"/>
@@ -1579,13 +1947,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
-      <c r="D21" s="42"/>
+      <c r="D21" s="51"/>
       <c r="E21" s="0"/>
       <c r="F21" s="0"/>
       <c r="G21" s="0"/>
       <c r="H21" s="0"/>
       <c r="I21" s="0"/>
-      <c r="J21" s="43"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="0"/>
       <c r="L21" s="0"/>
       <c r="M21" s="0"/>
@@ -1614,13 +1982,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="D22" s="42"/>
+      <c r="D22" s="51"/>
       <c r="E22" s="0"/>
       <c r="F22" s="0"/>
       <c r="G22" s="0"/>
       <c r="H22" s="0"/>
       <c r="I22" s="0"/>
-      <c r="J22" s="43"/>
+      <c r="J22" s="52"/>
       <c r="K22" s="0"/>
       <c r="L22" s="0"/>
       <c r="M22" s="0"/>
@@ -1649,17 +2017,19 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="D23" s="42"/>
+      <c r="D23" s="51"/>
       <c r="E23" s="0"/>
-      <c r="F23" s="30" t="n">
+      <c r="F23" s="39" t="n">
+        <f aca="false">C11</f>
         <v>7</v>
       </c>
-      <c r="G23" s="31"/>
-      <c r="H23" s="32" t="n">
+      <c r="G23" s="40"/>
+      <c r="H23" s="41" t="n">
+        <f aca="false">F23+F25</f>
         <v>10</v>
       </c>
       <c r="I23" s="0"/>
-      <c r="J23" s="43"/>
+      <c r="J23" s="52"/>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
       <c r="M23" s="0"/>
@@ -1674,15 +2044,15 @@
       <c r="A24" s="0"/>
       <c r="B24" s="0"/>
       <c r="C24" s="0"/>
-      <c r="D24" s="42"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="0"/>
-      <c r="F24" s="33" t="s">
+      <c r="F24" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
       <c r="I24" s="0"/>
-      <c r="J24" s="43"/>
+      <c r="J24" s="52"/>
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
       <c r="M24" s="0"/>
@@ -1693,23 +2063,22 @@
       <c r="R24" s="0"/>
       <c r="S24" s="0"/>
     </row>
-    <row r="25" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0"/>
       <c r="B25" s="0"/>
       <c r="C25" s="0"/>
       <c r="D25" s="0"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="34" t="n">
+      <c r="E25" s="47"/>
+      <c r="F25" s="43" t="n">
         <f aca="false">Q5</f>
         <v>3</v>
       </c>
-      <c r="G25" s="35" t="n">
+      <c r="G25" s="44" t="n">
+        <f aca="false">H26-H23</f>
         <v>3</v>
       </c>
-      <c r="H25" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" s="38"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="47"/>
       <c r="J25" s="0"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
@@ -1727,11 +2096,13 @@
       <c r="C26" s="0"/>
       <c r="D26" s="0"/>
       <c r="E26" s="0"/>
-      <c r="F26" s="40" t="n">
+      <c r="F26" s="49" t="n">
+        <f aca="false">H26-F25</f>
         <v>10</v>
       </c>
-      <c r="G26" s="28"/>
-      <c r="H26" s="41" t="n">
+      <c r="G26" s="37"/>
+      <c r="H26" s="50" t="n">
+        <f aca="false">K14</f>
         <v>13</v>
       </c>
       <c r="I26" s="0"/>
@@ -1894,211 +2265,211 @@
       <c r="L37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="44"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="45"/>
+      <c r="A38" s="53"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="54"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="44"/>
+      <c r="A39" s="53"/>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="45"/>
+      <c r="L39" s="54"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="44"/>
-      <c r="B40" s="46" t="s">
+      <c r="A40" s="53"/>
+      <c r="B40" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-      <c r="F40" s="47" t="s">
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="F40" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="47"/>
-      <c r="H40" s="47"/>
-      <c r="I40" s="47"/>
-      <c r="J40" s="47"/>
-      <c r="L40" s="45"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="L40" s="54"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="44"/>
-      <c r="B41" s="48" t="s">
+      <c r="A41" s="53"/>
+      <c r="B41" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="49" t="s">
+      <c r="C41" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="48" t="s">
+      <c r="D41" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="L41" s="45"/>
+      <c r="L41" s="54"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="44"/>
+      <c r="A42" s="53"/>
       <c r="B42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L42" s="45"/>
+      <c r="L42" s="54"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="44"/>
-      <c r="L43" s="45"/>
+      <c r="A43" s="53"/>
+      <c r="L43" s="54"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="44"/>
-      <c r="B44" s="50" t="s">
+      <c r="A44" s="53"/>
+      <c r="B44" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="C44" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="45"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="37"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="54"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="44"/>
-      <c r="B45" s="50" t="s">
+      <c r="A45" s="53"/>
+      <c r="B45" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="28" t="s">
+      <c r="C45" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="45"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="37"/>
+      <c r="K45" s="37"/>
+      <c r="L45" s="54"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="44"/>
-      <c r="B46" s="50" t="s">
+      <c r="A46" s="53"/>
+      <c r="B46" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="C46" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="45"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="37"/>
+      <c r="I46" s="37"/>
+      <c r="J46" s="37"/>
+      <c r="K46" s="37"/>
+      <c r="L46" s="54"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="44"/>
-      <c r="B47" s="50" t="s">
+      <c r="A47" s="53"/>
+      <c r="B47" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="45"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
+      <c r="I47" s="37"/>
+      <c r="J47" s="37"/>
+      <c r="K47" s="37"/>
+      <c r="L47" s="54"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="44"/>
-      <c r="B48" s="48" t="s">
+      <c r="A48" s="53"/>
+      <c r="B48" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="28" t="s">
+      <c r="C48" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="45"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="37"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="37"/>
+      <c r="K48" s="37"/>
+      <c r="L48" s="54"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="44"/>
-      <c r="B49" s="49" t="s">
+      <c r="A49" s="53"/>
+      <c r="B49" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="28" t="s">
+      <c r="C49" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="45"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="37"/>
+      <c r="I49" s="37"/>
+      <c r="J49" s="37"/>
+      <c r="K49" s="37"/>
+      <c r="L49" s="54"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="44"/>
-      <c r="B50" s="51" t="s">
+      <c r="A50" s="53"/>
+      <c r="B50" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="45" t="s">
+      <c r="C50" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="45"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="45"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="44"/>
-      <c r="B51" s="45"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
-      <c r="G51" s="45"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45"/>
-      <c r="J51" s="45"/>
-      <c r="K51" s="45"/>
-      <c r="L51" s="45"/>
+      <c r="A51" s="53"/>
+      <c r="B51" s="54"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="54"/>
+      <c r="J51" s="54"/>
+      <c r="K51" s="54"/>
+      <c r="L51" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -2126,9 +2497,9 @@
     <mergeCell ref="C48:K48"/>
     <mergeCell ref="C49:K49"/>
   </mergeCells>
-  <conditionalFormatting sqref="B13 G13 G19 G25 L13 Q13">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>0</formula>
+  <conditionalFormatting sqref="R1:BL7">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>IF(WEEKDAY(R$1,2)=6,1,IF(WEEKDAY(R$1,2)=7,1,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Übungen/02_Netzplan_Firmennetzwerk.xlsx
+++ b/Übungen/02_Netzplan_Firmennetzwerk.xlsx
@@ -188,7 +188,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,12 +211,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF999999"/>
         <bgColor rgb="FFB2B2B2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -394,7 +388,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -471,18 +465,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -492,6 +474,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -507,10 +493,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -531,15 +513,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -555,10 +537,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -567,31 +545,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -623,15 +601,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -639,19 +617,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -748,7 +726,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BN51"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="2" width="3.83"/>
@@ -966,291 +944,291 @@
       <c r="T2" s="21"/>
       <c r="U2" s="21"/>
       <c r="V2" s="21"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
       <c r="Y2" s="19"/>
       <c r="Z2" s="19"/>
-      <c r="AA2" s="22"/>
-      <c r="AB2" s="22"/>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="22"/>
-      <c r="AH2" s="22"/>
-      <c r="AI2" s="22"/>
-      <c r="AJ2" s="22"/>
-      <c r="AK2" s="22"/>
-      <c r="AL2" s="22"/>
-      <c r="AM2" s="23"/>
-      <c r="AN2" s="23"/>
-      <c r="AO2" s="23"/>
-      <c r="AP2" s="23"/>
-      <c r="AQ2" s="23"/>
-      <c r="AR2" s="23"/>
-      <c r="AS2" s="23"/>
-      <c r="AT2" s="23"/>
-      <c r="AU2" s="23"/>
-      <c r="AV2" s="23"/>
-      <c r="AW2" s="23"/>
-      <c r="AX2" s="23"/>
-      <c r="AY2" s="23"/>
-      <c r="AZ2" s="23"/>
-      <c r="BA2" s="23"/>
-      <c r="BB2" s="23"/>
-      <c r="BC2" s="23"/>
-      <c r="BD2" s="23"/>
-      <c r="BE2" s="23"/>
-      <c r="BF2" s="23"/>
-      <c r="BG2" s="23"/>
-      <c r="BH2" s="23"/>
-      <c r="BI2" s="23"/>
-      <c r="BJ2" s="23"/>
-      <c r="BK2" s="23"/>
-      <c r="BL2" s="23"/>
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="19"/>
+      <c r="AC2" s="19"/>
+      <c r="AD2" s="19"/>
+      <c r="AE2" s="19"/>
+      <c r="AF2" s="19"/>
+      <c r="AG2" s="19"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="19"/>
+      <c r="AJ2" s="19"/>
+      <c r="AK2" s="19"/>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="20"/>
+      <c r="AN2" s="20"/>
+      <c r="AO2" s="20"/>
+      <c r="AP2" s="20"/>
+      <c r="AQ2" s="20"/>
+      <c r="AR2" s="20"/>
+      <c r="AS2" s="20"/>
+      <c r="AT2" s="20"/>
+      <c r="AU2" s="20"/>
+      <c r="AV2" s="20"/>
+      <c r="AW2" s="20"/>
+      <c r="AX2" s="20"/>
+      <c r="AY2" s="20"/>
+      <c r="AZ2" s="20"/>
+      <c r="BA2" s="20"/>
+      <c r="BB2" s="20"/>
+      <c r="BC2" s="20"/>
+      <c r="BD2" s="20"/>
+      <c r="BE2" s="20"/>
+      <c r="BF2" s="20"/>
+      <c r="BG2" s="20"/>
+      <c r="BH2" s="20"/>
+      <c r="BI2" s="20"/>
+      <c r="BJ2" s="20"/>
+      <c r="BK2" s="20"/>
+      <c r="BL2" s="20"/>
     </row>
     <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="26" t="s">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="24" t="s">
         <v>5</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="26" t="s">
+      <c r="L3" s="25"/>
+      <c r="M3" s="24" t="s">
         <v>10</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27" t="n">
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="R3" s="22"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="22"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="22"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+      <c r="Z3" s="19"/>
       <c r="AA3" s="19"/>
       <c r="AB3" s="19"/>
       <c r="AC3" s="19"/>
-      <c r="AD3" s="22"/>
-      <c r="AE3" s="22"/>
-      <c r="AF3" s="22"/>
-      <c r="AG3" s="22"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="22"/>
-      <c r="AJ3" s="22"/>
-      <c r="AK3" s="22"/>
-      <c r="AL3" s="22"/>
-      <c r="AM3" s="23"/>
-      <c r="AN3" s="23"/>
-      <c r="AO3" s="23"/>
-      <c r="AP3" s="23"/>
-      <c r="AQ3" s="23"/>
-      <c r="AR3" s="23"/>
-      <c r="AS3" s="23"/>
-      <c r="AT3" s="23"/>
-      <c r="AU3" s="23"/>
-      <c r="AV3" s="23"/>
-      <c r="AW3" s="23"/>
-      <c r="AX3" s="23"/>
-      <c r="AY3" s="23"/>
-      <c r="AZ3" s="23"/>
-      <c r="BA3" s="23"/>
-      <c r="BB3" s="23"/>
-      <c r="BC3" s="23"/>
-      <c r="BD3" s="23"/>
-      <c r="BE3" s="23"/>
-      <c r="BF3" s="23"/>
-      <c r="BG3" s="23"/>
-      <c r="BH3" s="23"/>
-      <c r="BI3" s="23"/>
-      <c r="BJ3" s="23"/>
-      <c r="BK3" s="23"/>
-      <c r="BL3" s="23"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="19"/>
+      <c r="AF3" s="19"/>
+      <c r="AG3" s="19"/>
+      <c r="AH3" s="19"/>
+      <c r="AI3" s="19"/>
+      <c r="AJ3" s="19"/>
+      <c r="AK3" s="19"/>
+      <c r="AL3" s="19"/>
+      <c r="AM3" s="20"/>
+      <c r="AN3" s="20"/>
+      <c r="AO3" s="20"/>
+      <c r="AP3" s="20"/>
+      <c r="AQ3" s="20"/>
+      <c r="AR3" s="20"/>
+      <c r="AS3" s="20"/>
+      <c r="AT3" s="20"/>
+      <c r="AU3" s="20"/>
+      <c r="AV3" s="20"/>
+      <c r="AW3" s="20"/>
+      <c r="AX3" s="20"/>
+      <c r="AY3" s="20"/>
+      <c r="AZ3" s="20"/>
+      <c r="BA3" s="20"/>
+      <c r="BB3" s="20"/>
+      <c r="BC3" s="20"/>
+      <c r="BD3" s="20"/>
+      <c r="BE3" s="20"/>
+      <c r="BF3" s="20"/>
+      <c r="BG3" s="20"/>
+      <c r="BH3" s="20"/>
+      <c r="BI3" s="20"/>
+      <c r="BJ3" s="20"/>
+      <c r="BK3" s="20"/>
+      <c r="BL3" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="26" t="s">
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="24" t="s">
         <v>5</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="26" t="s">
+      <c r="L4" s="25"/>
+      <c r="M4" s="24" t="s">
         <v>10</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27" t="n">
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="22"/>
-      <c r="S4" s="23"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="22"/>
-      <c r="X4" s="22"/>
-      <c r="Y4" s="22"/>
-      <c r="Z4" s="22"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="19"/>
       <c r="AA4" s="19"/>
       <c r="AB4" s="19"/>
       <c r="AC4" s="19"/>
-      <c r="AD4" s="22"/>
-      <c r="AE4" s="22"/>
+      <c r="AD4" s="19"/>
+      <c r="AE4" s="19"/>
       <c r="AF4" s="19"/>
       <c r="AG4" s="19"/>
       <c r="AH4" s="19"/>
-      <c r="AI4" s="22"/>
-      <c r="AJ4" s="22"/>
-      <c r="AK4" s="22"/>
-      <c r="AL4" s="22"/>
-      <c r="AM4" s="23"/>
-      <c r="AN4" s="23"/>
-      <c r="AO4" s="23"/>
-      <c r="AP4" s="23"/>
-      <c r="AQ4" s="23"/>
-      <c r="AR4" s="23"/>
-      <c r="AS4" s="23"/>
-      <c r="AT4" s="23"/>
-      <c r="AU4" s="23"/>
-      <c r="AV4" s="23"/>
-      <c r="AW4" s="23"/>
-      <c r="AX4" s="23"/>
-      <c r="AY4" s="23"/>
-      <c r="AZ4" s="23"/>
-      <c r="BA4" s="23"/>
-      <c r="BB4" s="23"/>
-      <c r="BC4" s="23"/>
-      <c r="BD4" s="23"/>
-      <c r="BE4" s="23"/>
-      <c r="BF4" s="23"/>
-      <c r="BG4" s="23"/>
-      <c r="BH4" s="23"/>
-      <c r="BI4" s="23"/>
-      <c r="BJ4" s="23"/>
-      <c r="BK4" s="23"/>
-      <c r="BL4" s="23"/>
+      <c r="AI4" s="19"/>
+      <c r="AJ4" s="19"/>
+      <c r="AK4" s="19"/>
+      <c r="AL4" s="19"/>
+      <c r="AM4" s="20"/>
+      <c r="AN4" s="20"/>
+      <c r="AO4" s="20"/>
+      <c r="AP4" s="20"/>
+      <c r="AQ4" s="20"/>
+      <c r="AR4" s="20"/>
+      <c r="AS4" s="20"/>
+      <c r="AT4" s="20"/>
+      <c r="AU4" s="20"/>
+      <c r="AV4" s="20"/>
+      <c r="AW4" s="20"/>
+      <c r="AX4" s="20"/>
+      <c r="AY4" s="20"/>
+      <c r="AZ4" s="20"/>
+      <c r="BA4" s="20"/>
+      <c r="BB4" s="20"/>
+      <c r="BC4" s="20"/>
+      <c r="BD4" s="20"/>
+      <c r="BE4" s="20"/>
+      <c r="BF4" s="20"/>
+      <c r="BG4" s="20"/>
+      <c r="BH4" s="20"/>
+      <c r="BI4" s="20"/>
+      <c r="BJ4" s="20"/>
+      <c r="BK4" s="20"/>
+      <c r="BL4" s="20"/>
     </row>
     <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="26" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="24" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="26" t="s">
+      <c r="L5" s="25"/>
+      <c r="M5" s="24" t="s">
         <v>10</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27" t="n">
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="R5" s="22"/>
-      <c r="S5" s="23"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="22"/>
-      <c r="Z5" s="22"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="19"/>
+      <c r="Y5" s="19"/>
+      <c r="Z5" s="19"/>
       <c r="AA5" s="19"/>
       <c r="AB5" s="19"/>
       <c r="AC5" s="19"/>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="22"/>
-      <c r="AF5" s="22"/>
-      <c r="AG5" s="22"/>
-      <c r="AH5" s="22"/>
-      <c r="AI5" s="22"/>
-      <c r="AJ5" s="22"/>
-      <c r="AK5" s="22"/>
-      <c r="AL5" s="22"/>
-      <c r="AM5" s="23"/>
-      <c r="AN5" s="23"/>
-      <c r="AO5" s="23"/>
-      <c r="AP5" s="23"/>
-      <c r="AQ5" s="23"/>
-      <c r="AR5" s="23"/>
-      <c r="AS5" s="23"/>
-      <c r="AT5" s="23"/>
-      <c r="AU5" s="23"/>
-      <c r="AV5" s="23"/>
-      <c r="AW5" s="23"/>
-      <c r="AX5" s="23"/>
-      <c r="AY5" s="23"/>
-      <c r="AZ5" s="23"/>
-      <c r="BA5" s="23"/>
-      <c r="BB5" s="23"/>
-      <c r="BC5" s="23"/>
-      <c r="BD5" s="23"/>
-      <c r="BE5" s="23"/>
-      <c r="BF5" s="23"/>
-      <c r="BG5" s="23"/>
-      <c r="BH5" s="23"/>
-      <c r="BI5" s="23"/>
-      <c r="BJ5" s="23"/>
-      <c r="BK5" s="23"/>
-      <c r="BL5" s="23"/>
+      <c r="AD5" s="19"/>
+      <c r="AE5" s="19"/>
+      <c r="AF5" s="19"/>
+      <c r="AG5" s="19"/>
+      <c r="AH5" s="19"/>
+      <c r="AI5" s="19"/>
+      <c r="AJ5" s="19"/>
+      <c r="AK5" s="19"/>
+      <c r="AL5" s="19"/>
+      <c r="AM5" s="20"/>
+      <c r="AN5" s="20"/>
+      <c r="AO5" s="20"/>
+      <c r="AP5" s="20"/>
+      <c r="AQ5" s="20"/>
+      <c r="AR5" s="20"/>
+      <c r="AS5" s="20"/>
+      <c r="AT5" s="20"/>
+      <c r="AU5" s="20"/>
+      <c r="AV5" s="20"/>
+      <c r="AW5" s="20"/>
+      <c r="AX5" s="20"/>
+      <c r="AY5" s="20"/>
+      <c r="AZ5" s="20"/>
+      <c r="BA5" s="20"/>
+      <c r="BB5" s="20"/>
+      <c r="BC5" s="20"/>
+      <c r="BD5" s="20"/>
+      <c r="BE5" s="20"/>
+      <c r="BF5" s="20"/>
+      <c r="BG5" s="20"/>
+      <c r="BH5" s="20"/>
+      <c r="BI5" s="20"/>
+      <c r="BJ5" s="20"/>
+      <c r="BK5" s="20"/>
+      <c r="BL5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="26" t="s">
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="24" t="s">
         <v>7</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1259,150 +1237,150 @@
       <c r="K6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="27"/>
-      <c r="M6" s="26" t="s">
+      <c r="L6" s="25"/>
+      <c r="M6" s="24" t="s">
         <v>14</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27" t="n">
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="R6" s="22"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="28"/>
-      <c r="W6" s="22"/>
-      <c r="X6" s="22"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="22"/>
-      <c r="AC6" s="22"/>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="22"/>
-      <c r="AF6" s="22"/>
-      <c r="AG6" s="22"/>
-      <c r="AH6" s="22"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="19"/>
       <c r="AI6" s="19"/>
-      <c r="AJ6" s="22"/>
-      <c r="AK6" s="22"/>
-      <c r="AL6" s="22"/>
-      <c r="AM6" s="23"/>
-      <c r="AN6" s="23"/>
-      <c r="AO6" s="23"/>
-      <c r="AP6" s="23"/>
-      <c r="AQ6" s="23"/>
-      <c r="AR6" s="23"/>
-      <c r="AS6" s="23"/>
-      <c r="AT6" s="23"/>
-      <c r="AU6" s="23"/>
-      <c r="AV6" s="23"/>
-      <c r="AW6" s="23"/>
-      <c r="AX6" s="23"/>
-      <c r="AY6" s="23"/>
-      <c r="AZ6" s="23"/>
-      <c r="BA6" s="23"/>
-      <c r="BB6" s="23"/>
-      <c r="BC6" s="23"/>
-      <c r="BD6" s="23"/>
-      <c r="BE6" s="23"/>
-      <c r="BF6" s="23"/>
-      <c r="BG6" s="23"/>
-      <c r="BH6" s="23"/>
-      <c r="BI6" s="23"/>
-      <c r="BJ6" s="23"/>
-      <c r="BK6" s="23"/>
-      <c r="BL6" s="23"/>
+      <c r="AJ6" s="19"/>
+      <c r="AK6" s="19"/>
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="20"/>
+      <c r="AN6" s="20"/>
+      <c r="AO6" s="20"/>
+      <c r="AP6" s="20"/>
+      <c r="AQ6" s="20"/>
+      <c r="AR6" s="20"/>
+      <c r="AS6" s="20"/>
+      <c r="AT6" s="20"/>
+      <c r="AU6" s="20"/>
+      <c r="AV6" s="20"/>
+      <c r="AW6" s="20"/>
+      <c r="AX6" s="20"/>
+      <c r="AY6" s="20"/>
+      <c r="AZ6" s="20"/>
+      <c r="BA6" s="20"/>
+      <c r="BB6" s="20"/>
+      <c r="BC6" s="20"/>
+      <c r="BD6" s="20"/>
+      <c r="BE6" s="20"/>
+      <c r="BF6" s="20"/>
+      <c r="BG6" s="20"/>
+      <c r="BH6" s="20"/>
+      <c r="BI6" s="20"/>
+      <c r="BJ6" s="20"/>
+      <c r="BK6" s="20"/>
+      <c r="BL6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="31" t="s">
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="33" t="n">
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="37"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="39"/>
-      <c r="W7" s="37"/>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="37"/>
-      <c r="Z7" s="37"/>
-      <c r="AA7" s="37"/>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="37"/>
-      <c r="AD7" s="37"/>
-      <c r="AE7" s="37"/>
-      <c r="AF7" s="37"/>
-      <c r="AG7" s="37"/>
-      <c r="AH7" s="37"/>
-      <c r="AI7" s="37"/>
-      <c r="AJ7" s="40"/>
-      <c r="AK7" s="37"/>
-      <c r="AL7" s="37"/>
-      <c r="AM7" s="38"/>
-      <c r="AN7" s="38"/>
-      <c r="AO7" s="38"/>
-      <c r="AP7" s="38"/>
-      <c r="AQ7" s="38"/>
-      <c r="AR7" s="38"/>
-      <c r="AS7" s="38"/>
-      <c r="AT7" s="38"/>
-      <c r="AU7" s="38"/>
-      <c r="AV7" s="38"/>
-      <c r="AW7" s="38"/>
-      <c r="AX7" s="38"/>
-      <c r="AY7" s="38"/>
-      <c r="AZ7" s="38"/>
-      <c r="BA7" s="38"/>
-      <c r="BB7" s="38"/>
-      <c r="BC7" s="38"/>
-      <c r="BD7" s="38"/>
-      <c r="BE7" s="38"/>
-      <c r="BF7" s="38"/>
-      <c r="BG7" s="38"/>
-      <c r="BH7" s="38"/>
-      <c r="BI7" s="38"/>
-      <c r="BJ7" s="38"/>
-      <c r="BK7" s="38"/>
-      <c r="BL7" s="38"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="34"/>
+      <c r="Y7" s="34"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="34"/>
+      <c r="AB7" s="34"/>
+      <c r="AC7" s="34"/>
+      <c r="AD7" s="34"/>
+      <c r="AE7" s="34"/>
+      <c r="AF7" s="34"/>
+      <c r="AG7" s="34"/>
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="34"/>
+      <c r="AJ7" s="34"/>
+      <c r="AK7" s="34"/>
+      <c r="AL7" s="34"/>
+      <c r="AM7" s="35"/>
+      <c r="AN7" s="35"/>
+      <c r="AO7" s="35"/>
+      <c r="AP7" s="35"/>
+      <c r="AQ7" s="35"/>
+      <c r="AR7" s="35"/>
+      <c r="AS7" s="35"/>
+      <c r="AT7" s="35"/>
+      <c r="AU7" s="35"/>
+      <c r="AV7" s="35"/>
+      <c r="AW7" s="35"/>
+      <c r="AX7" s="35"/>
+      <c r="AY7" s="35"/>
+      <c r="AZ7" s="35"/>
+      <c r="BA7" s="35"/>
+      <c r="BB7" s="35"/>
+      <c r="BC7" s="35"/>
+      <c r="BD7" s="35"/>
+      <c r="BE7" s="35"/>
+      <c r="BF7" s="35"/>
+      <c r="BG7" s="35"/>
+      <c r="BH7" s="35"/>
+      <c r="BI7" s="35"/>
+      <c r="BJ7" s="35"/>
+      <c r="BK7" s="35"/>
+      <c r="BL7" s="35"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="41"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="42"/>
+      <c r="B8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="38"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="42"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
       <c r="T8" s="2"/>
       <c r="W8" s="0"/>
       <c r="X8" s="0"/>
@@ -1422,7 +1400,7 @@
       <c r="AL8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="41"/>
+      <c r="B9" s="37"/>
       <c r="D9" s="0"/>
       <c r="E9" s="0"/>
       <c r="F9" s="0"/>
@@ -1497,44 +1475,44 @@
       <c r="AL10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="n">
+      <c r="A11" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="44"/>
-      <c r="C11" s="45" t="n">
+      <c r="B11" s="40"/>
+      <c r="C11" s="41" t="n">
         <f aca="false">A11+A13</f>
         <v>7</v>
       </c>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="39" t="n">
         <f aca="false">C11</f>
         <v>7</v>
       </c>
-      <c r="G11" s="44"/>
-      <c r="H11" s="45" t="n">
+      <c r="G11" s="40"/>
+      <c r="H11" s="41" t="n">
         <f aca="false">F11+F13</f>
         <v>10</v>
       </c>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
-      <c r="K11" s="43" t="n">
+      <c r="K11" s="39" t="n">
         <f aca="false">MAX(H11,H17,H23)</f>
         <v>13</v>
       </c>
-      <c r="L11" s="44"/>
-      <c r="M11" s="45" t="n">
+      <c r="L11" s="40"/>
+      <c r="M11" s="41" t="n">
         <f aca="false">K11+K13</f>
         <v>14</v>
       </c>
       <c r="N11" s="0"/>
       <c r="O11" s="0"/>
-      <c r="P11" s="43" t="n">
+      <c r="P11" s="39" t="n">
         <f aca="false">M11</f>
         <v>14</v>
       </c>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="45" t="n">
+      <c r="Q11" s="40"/>
+      <c r="R11" s="41" t="n">
         <f aca="false">P11+P13</f>
         <v>15</v>
       </c>
@@ -1560,32 +1538,32 @@
       <c r="AL11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="46" t="s">
+      <c r="K12" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
-      <c r="P12" s="46" t="s">
+      <c r="P12" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="46"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
       <c r="U12" s="0"/>
@@ -1608,47 +1586,47 @@
       <c r="AL12" s="0"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="47" t="n">
+      <c r="A13" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="48" t="n">
+      <c r="B13" s="44" t="n">
         <f aca="false">C14-C11</f>
         <v>0</v>
       </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="47" t="n">
+      <c r="C13" s="45"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="43" t="n">
         <f aca="false">Q3</f>
         <v>3</v>
       </c>
-      <c r="G13" s="48" t="n">
+      <c r="G13" s="44" t="n">
         <f aca="false">H14-H11</f>
         <v>3</v>
       </c>
-      <c r="H13" s="49"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="47" t="n">
+      <c r="H13" s="45"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="43" t="n">
         <f aca="false">Q6</f>
         <v>1</v>
       </c>
-      <c r="L13" s="48" t="n">
+      <c r="L13" s="44" t="n">
         <f aca="false">M14-M11</f>
         <v>0</v>
       </c>
-      <c r="M13" s="49"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="47" t="n">
+      <c r="M13" s="45"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="43" t="n">
         <f aca="false">Q7</f>
         <v>1</v>
       </c>
-      <c r="Q13" s="48" t="n">
+      <c r="Q13" s="44" t="n">
         <f aca="false">R14-R11</f>
         <v>0</v>
       </c>
-      <c r="R13" s="49"/>
+      <c r="R13" s="45"/>
       <c r="S13" s="0"/>
       <c r="T13" s="0"/>
       <c r="U13" s="0"/>
@@ -1671,45 +1649,45 @@
       <c r="AL13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="53" t="n">
+      <c r="A14" s="49" t="n">
         <f aca="false">C14-A13</f>
         <v>0</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="54" t="n">
+      <c r="B14" s="37"/>
+      <c r="C14" s="50" t="n">
         <f aca="false">MIN(F26,F20,F14)</f>
         <v>7</v>
       </c>
-      <c r="D14" s="55"/>
+      <c r="D14" s="51"/>
       <c r="E14" s="0"/>
-      <c r="F14" s="53" t="n">
+      <c r="F14" s="49" t="n">
         <f aca="false">H14-F13</f>
         <v>10</v>
       </c>
-      <c r="G14" s="41"/>
-      <c r="H14" s="54" t="n">
+      <c r="G14" s="37"/>
+      <c r="H14" s="50" t="n">
         <f aca="false">K14</f>
         <v>13</v>
       </c>
       <c r="I14" s="0"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="53" t="n">
+      <c r="J14" s="52"/>
+      <c r="K14" s="49" t="n">
         <f aca="false">M14-K13</f>
         <v>13</v>
       </c>
-      <c r="L14" s="41"/>
-      <c r="M14" s="54" t="n">
+      <c r="L14" s="37"/>
+      <c r="M14" s="50" t="n">
         <f aca="false">P14</f>
         <v>14</v>
       </c>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
-      <c r="P14" s="53" t="n">
+      <c r="P14" s="49" t="n">
         <f aca="false">R14-P13</f>
         <v>14</v>
       </c>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="54" t="n">
+      <c r="Q14" s="37"/>
+      <c r="R14" s="50" t="n">
         <f aca="false">R11</f>
         <v>15</v>
       </c>
@@ -1735,13 +1713,13 @@
       <c r="AL14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="55"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="0"/>
       <c r="F15" s="0"/>
       <c r="G15" s="0"/>
       <c r="H15" s="0"/>
       <c r="I15" s="0"/>
-      <c r="J15" s="56"/>
+      <c r="J15" s="52"/>
       <c r="K15" s="0"/>
       <c r="L15" s="0"/>
       <c r="M15" s="0"/>
@@ -1772,13 +1750,13 @@
       <c r="AL15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="55"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0"/>
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
-      <c r="J16" s="56"/>
+      <c r="J16" s="52"/>
       <c r="K16" s="0"/>
       <c r="L16" s="0"/>
       <c r="M16" s="0"/>
@@ -1809,19 +1787,19 @@
       <c r="AL16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="55"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="43" t="n">
+      <c r="F17" s="39" t="n">
         <f aca="false">C11</f>
         <v>7</v>
       </c>
-      <c r="G17" s="44"/>
-      <c r="H17" s="45" t="n">
+      <c r="G17" s="40"/>
+      <c r="H17" s="41" t="n">
         <f aca="false">F17+F19</f>
         <v>13</v>
       </c>
       <c r="I17" s="0"/>
-      <c r="J17" s="56"/>
+      <c r="J17" s="52"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0"/>
       <c r="M17" s="0"/>
@@ -1852,15 +1830,15 @@
       <c r="AL17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="55"/>
+      <c r="D18" s="51"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="46" t="s">
+      <c r="F18" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
       <c r="I18" s="0"/>
-      <c r="J18" s="56"/>
+      <c r="J18" s="52"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
       <c r="M18" s="0"/>
@@ -1888,19 +1866,19 @@
       <c r="AL18" s="0"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="55"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="47" t="n">
+      <c r="D19" s="51"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="43" t="n">
         <f aca="false">Q4</f>
         <v>6</v>
       </c>
-      <c r="G19" s="48" t="n">
+      <c r="G19" s="44" t="n">
         <f aca="false">H20-H17</f>
         <v>0</v>
       </c>
-      <c r="H19" s="49"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="56"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="52"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0"/>
       <c r="M19" s="0"/>
@@ -1928,19 +1906,19 @@
       <c r="AL19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="55"/>
+      <c r="D20" s="51"/>
       <c r="E20" s="0"/>
-      <c r="F20" s="53" t="n">
+      <c r="F20" s="49" t="n">
         <f aca="false">H20-F19</f>
         <v>7</v>
       </c>
-      <c r="G20" s="41"/>
-      <c r="H20" s="54" t="n">
+      <c r="G20" s="37"/>
+      <c r="H20" s="50" t="n">
         <f aca="false">K14</f>
         <v>13</v>
       </c>
       <c r="I20" s="0"/>
-      <c r="J20" s="56"/>
+      <c r="J20" s="52"/>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
       <c r="M20" s="0"/>
@@ -1969,13 +1947,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
-      <c r="D21" s="55"/>
+      <c r="D21" s="51"/>
       <c r="E21" s="0"/>
       <c r="F21" s="0"/>
       <c r="G21" s="0"/>
       <c r="H21" s="0"/>
       <c r="I21" s="0"/>
-      <c r="J21" s="56"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="0"/>
       <c r="L21" s="0"/>
       <c r="M21" s="0"/>
@@ -2004,13 +1982,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="D22" s="55"/>
+      <c r="D22" s="51"/>
       <c r="E22" s="0"/>
       <c r="F22" s="0"/>
       <c r="G22" s="0"/>
       <c r="H22" s="0"/>
       <c r="I22" s="0"/>
-      <c r="J22" s="56"/>
+      <c r="J22" s="52"/>
       <c r="K22" s="0"/>
       <c r="L22" s="0"/>
       <c r="M22" s="0"/>
@@ -2039,19 +2017,19 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="D23" s="55"/>
+      <c r="D23" s="51"/>
       <c r="E23" s="0"/>
-      <c r="F23" s="43" t="n">
+      <c r="F23" s="39" t="n">
         <f aca="false">C11</f>
         <v>7</v>
       </c>
-      <c r="G23" s="44"/>
-      <c r="H23" s="45" t="n">
+      <c r="G23" s="40"/>
+      <c r="H23" s="41" t="n">
         <f aca="false">F23+F25</f>
         <v>10</v>
       </c>
       <c r="I23" s="0"/>
-      <c r="J23" s="56"/>
+      <c r="J23" s="52"/>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
       <c r="M23" s="0"/>
@@ -2066,15 +2044,15 @@
       <c r="A24" s="0"/>
       <c r="B24" s="0"/>
       <c r="C24" s="0"/>
-      <c r="D24" s="55"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="0"/>
-      <c r="F24" s="46" t="s">
+      <c r="F24" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
       <c r="I24" s="0"/>
-      <c r="J24" s="56"/>
+      <c r="J24" s="52"/>
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
       <c r="M24" s="0"/>
@@ -2090,17 +2068,17 @@
       <c r="B25" s="0"/>
       <c r="C25" s="0"/>
       <c r="D25" s="0"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="47" t="n">
+      <c r="E25" s="47"/>
+      <c r="F25" s="43" t="n">
         <f aca="false">Q5</f>
         <v>3</v>
       </c>
-      <c r="G25" s="48" t="n">
+      <c r="G25" s="44" t="n">
         <f aca="false">H26-H23</f>
         <v>3</v>
       </c>
-      <c r="H25" s="49"/>
-      <c r="I25" s="51"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="47"/>
       <c r="J25" s="0"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
@@ -2118,12 +2096,12 @@
       <c r="C26" s="0"/>
       <c r="D26" s="0"/>
       <c r="E26" s="0"/>
-      <c r="F26" s="53" t="n">
+      <c r="F26" s="49" t="n">
         <f aca="false">H26-F25</f>
         <v>10</v>
       </c>
-      <c r="G26" s="41"/>
-      <c r="H26" s="54" t="n">
+      <c r="G26" s="37"/>
+      <c r="H26" s="50" t="n">
         <f aca="false">K14</f>
         <v>13</v>
       </c>
@@ -2287,211 +2265,211 @@
       <c r="L37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="57"/>
-      <c r="B38" s="58"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="58"/>
+      <c r="A38" s="53"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="54"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="57"/>
+      <c r="A39" s="53"/>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L39" s="58"/>
+      <c r="L39" s="54"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="57"/>
-      <c r="B40" s="59" t="s">
+      <c r="A40" s="53"/>
+      <c r="B40" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="F40" s="60" t="s">
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="F40" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
-      <c r="I40" s="60"/>
-      <c r="J40" s="60"/>
-      <c r="L40" s="58"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="L40" s="54"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="57"/>
-      <c r="B41" s="61" t="s">
+      <c r="A41" s="53"/>
+      <c r="B41" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="62" t="s">
+      <c r="C41" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="61" t="s">
+      <c r="D41" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="L41" s="58"/>
+      <c r="L41" s="54"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="57"/>
+      <c r="A42" s="53"/>
       <c r="B42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L42" s="58"/>
+      <c r="L42" s="54"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="57"/>
-      <c r="L43" s="58"/>
+      <c r="A43" s="53"/>
+      <c r="L43" s="54"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="57"/>
-      <c r="B44" s="63" t="s">
+      <c r="A44" s="53"/>
+      <c r="B44" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="41" t="s">
+      <c r="C44" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="58"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="37"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="54"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="57"/>
-      <c r="B45" s="63" t="s">
+      <c r="A45" s="53"/>
+      <c r="B45" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="41" t="s">
+      <c r="C45" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="58"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="37"/>
+      <c r="K45" s="37"/>
+      <c r="L45" s="54"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="57"/>
-      <c r="B46" s="63" t="s">
+      <c r="A46" s="53"/>
+      <c r="B46" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="41" t="s">
+      <c r="C46" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="58"/>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="37"/>
+      <c r="I46" s="37"/>
+      <c r="J46" s="37"/>
+      <c r="K46" s="37"/>
+      <c r="L46" s="54"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="57"/>
-      <c r="B47" s="63" t="s">
+      <c r="A47" s="53"/>
+      <c r="B47" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="41" t="s">
+      <c r="C47" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="41"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="58"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
+      <c r="I47" s="37"/>
+      <c r="J47" s="37"/>
+      <c r="K47" s="37"/>
+      <c r="L47" s="54"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="57"/>
-      <c r="B48" s="61" t="s">
+      <c r="A48" s="53"/>
+      <c r="B48" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="41" t="s">
+      <c r="C48" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="41"/>
-      <c r="J48" s="41"/>
-      <c r="K48" s="41"/>
-      <c r="L48" s="58"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="37"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="37"/>
+      <c r="K48" s="37"/>
+      <c r="L48" s="54"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="57"/>
-      <c r="B49" s="62" t="s">
+      <c r="A49" s="53"/>
+      <c r="B49" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="41" t="s">
+      <c r="C49" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="58"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="37"/>
+      <c r="I49" s="37"/>
+      <c r="J49" s="37"/>
+      <c r="K49" s="37"/>
+      <c r="L49" s="54"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="57"/>
-      <c r="B50" s="64" t="s">
+      <c r="A50" s="53"/>
+      <c r="B50" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
-      <c r="J50" s="58"/>
-      <c r="K50" s="58"/>
-      <c r="L50" s="58"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="57"/>
-      <c r="B51" s="58"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
-      <c r="I51" s="58"/>
-      <c r="J51" s="58"/>
-      <c r="K51" s="58"/>
-      <c r="L51" s="58"/>
+      <c r="A51" s="53"/>
+      <c r="B51" s="54"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="54"/>
+      <c r="J51" s="54"/>
+      <c r="K51" s="54"/>
+      <c r="L51" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/Übungen/02_Netzplan_Firmennetzwerk.xlsx
+++ b/Übungen/02_Netzplan_Firmennetzwerk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Netzplan" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Netzplan!$A$1:$X$31</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Netzplan!$A$1:$X$30</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -62,9 +62,6 @@
   </si>
   <si>
     <t xml:space="preserve">Domaincontroller einrichten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastruktur fertig</t>
   </si>
   <si>
     <t xml:space="preserve">Clients in Domain einbinden</t>
@@ -127,7 +124,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -172,14 +169,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFC9211E"/>
-      <name val="Alegreya Sans"/>
-      <family val="3"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="9"/>
       <name val="Alegreya Sans"/>
       <family val="3"/>
@@ -199,7 +188,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -222,18 +211,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF999999"/>
         <bgColor rgb="FFB2B2B2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFC9211E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFBF00"/>
-        <bgColor rgb="FFFF9900"/>
       </patternFill>
     </fill>
     <fill>
@@ -411,7 +388,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -448,6 +425,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -484,31 +465,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -524,22 +493,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -560,15 +513,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -584,14 +537,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -600,31 +545,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -636,10 +581,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -660,35 +601,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -761,7 +702,7 @@
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFBF00"/>
+      <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
@@ -779,89 +720,16 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>37440</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>6480</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>166320</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>5040</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name=""/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9515160" y="1198080"/>
-          <a:ext cx="128880" cy="168840"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:rect l="l" t="t" r="r" b="b"/>
-          <a:pathLst>
-            <a:path w="21600" h="21600">
-              <a:moveTo>
-                <a:pt x="10800" y="0"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="21600" y="10800"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="10800" y="21600"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="10800"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="10800" y="0"/>
-              </a:lnTo>
-              <a:close/>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="729fcf"/>
-        </a:solidFill>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="3465a4"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BN52"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
+  <dimension ref="A1:BN51"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="2" width="3.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="16" min="9" style="2" width="3.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="2" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="3" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="3.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="3.83"/>
@@ -969,572 +837,589 @@
       <c r="AO1" s="8" t="n">
         <v>44629</v>
       </c>
-      <c r="AP1" s="0"/>
-      <c r="AQ1" s="0"/>
-      <c r="AR1" s="0"/>
-      <c r="AS1" s="0"/>
-      <c r="AT1" s="0"/>
-      <c r="AU1" s="0"/>
-      <c r="AV1" s="0"/>
-      <c r="AW1" s="0"/>
-      <c r="AX1" s="0"/>
-      <c r="AY1" s="0"/>
-      <c r="AZ1" s="0"/>
-      <c r="BA1" s="0"/>
-      <c r="BB1" s="0"/>
-      <c r="BC1" s="0"/>
-      <c r="BD1" s="0"/>
-      <c r="BE1" s="0"/>
-      <c r="BF1" s="0"/>
-      <c r="BG1" s="0"/>
-      <c r="BH1" s="0"/>
-      <c r="BI1" s="0"/>
-      <c r="BJ1" s="0"/>
-      <c r="BK1" s="0"/>
-      <c r="BL1" s="0"/>
-      <c r="BN1" s="9"/>
+      <c r="AP1" s="8" t="n">
+        <v>44630</v>
+      </c>
+      <c r="AQ1" s="8" t="n">
+        <v>44631</v>
+      </c>
+      <c r="AR1" s="8" t="n">
+        <v>44632</v>
+      </c>
+      <c r="AS1" s="8" t="n">
+        <v>44633</v>
+      </c>
+      <c r="AT1" s="8" t="n">
+        <v>44634</v>
+      </c>
+      <c r="AU1" s="8" t="n">
+        <v>44635</v>
+      </c>
+      <c r="AV1" s="8" t="n">
+        <v>44636</v>
+      </c>
+      <c r="AW1" s="8" t="n">
+        <v>44637</v>
+      </c>
+      <c r="AX1" s="8" t="n">
+        <v>44638</v>
+      </c>
+      <c r="AY1" s="8" t="n">
+        <v>44639</v>
+      </c>
+      <c r="AZ1" s="8" t="n">
+        <v>44640</v>
+      </c>
+      <c r="BA1" s="8" t="n">
+        <v>44641</v>
+      </c>
+      <c r="BB1" s="8" t="n">
+        <v>44642</v>
+      </c>
+      <c r="BC1" s="8" t="n">
+        <v>44643</v>
+      </c>
+      <c r="BD1" s="8" t="n">
+        <v>44644</v>
+      </c>
+      <c r="BE1" s="8" t="n">
+        <v>44645</v>
+      </c>
+      <c r="BF1" s="8" t="n">
+        <v>44646</v>
+      </c>
+      <c r="BG1" s="8" t="n">
+        <v>44647</v>
+      </c>
+      <c r="BH1" s="8" t="n">
+        <v>44648</v>
+      </c>
+      <c r="BI1" s="8" t="n">
+        <v>44649</v>
+      </c>
+      <c r="BJ1" s="8" t="n">
+        <v>44650</v>
+      </c>
+      <c r="BK1" s="8" t="n">
+        <v>44651</v>
+      </c>
+      <c r="BL1" s="8" t="n">
+        <v>44652</v>
+      </c>
+      <c r="BM1" s="9"/>
+      <c r="BN1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="15" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17" t="n">
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="R2" s="18"/>
-      <c r="S2" s="19"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
-      <c r="AD2" s="21"/>
-      <c r="AE2" s="21"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
-      <c r="AH2" s="21"/>
-      <c r="AI2" s="21"/>
-      <c r="AJ2" s="21"/>
-      <c r="AK2" s="22"/>
-      <c r="AL2" s="22"/>
-      <c r="AM2" s="23"/>
-      <c r="AN2" s="23"/>
-      <c r="AO2" s="23"/>
-      <c r="AP2" s="0"/>
-      <c r="AQ2" s="0"/>
-      <c r="AR2" s="0"/>
-      <c r="AS2" s="0"/>
-      <c r="AT2" s="0"/>
-      <c r="AU2" s="0"/>
-      <c r="AV2" s="0"/>
-      <c r="AW2" s="0"/>
-      <c r="AX2" s="0"/>
-      <c r="AY2" s="0"/>
-      <c r="AZ2" s="0"/>
-      <c r="BA2" s="0"/>
-      <c r="BB2" s="0"/>
-      <c r="BC2" s="0"/>
-      <c r="BD2" s="0"/>
-      <c r="BE2" s="0"/>
-      <c r="BF2" s="0"/>
-      <c r="BG2" s="0"/>
-      <c r="BH2" s="0"/>
-      <c r="BI2" s="0"/>
-      <c r="BJ2" s="0"/>
-      <c r="BK2" s="0"/>
-      <c r="BL2" s="0"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
+      <c r="Z2" s="19"/>
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="19"/>
+      <c r="AC2" s="19"/>
+      <c r="AD2" s="19"/>
+      <c r="AE2" s="19"/>
+      <c r="AF2" s="19"/>
+      <c r="AG2" s="19"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="19"/>
+      <c r="AJ2" s="19"/>
+      <c r="AK2" s="19"/>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="20"/>
+      <c r="AN2" s="20"/>
+      <c r="AO2" s="20"/>
+      <c r="AP2" s="20"/>
+      <c r="AQ2" s="20"/>
+      <c r="AR2" s="20"/>
+      <c r="AS2" s="20"/>
+      <c r="AT2" s="20"/>
+      <c r="AU2" s="20"/>
+      <c r="AV2" s="20"/>
+      <c r="AW2" s="20"/>
+      <c r="AX2" s="20"/>
+      <c r="AY2" s="20"/>
+      <c r="AZ2" s="20"/>
+      <c r="BA2" s="20"/>
+      <c r="BB2" s="20"/>
+      <c r="BC2" s="20"/>
+      <c r="BD2" s="20"/>
+      <c r="BE2" s="20"/>
+      <c r="BF2" s="20"/>
+      <c r="BG2" s="20"/>
+      <c r="BH2" s="20"/>
+      <c r="BI2" s="20"/>
+      <c r="BJ2" s="20"/>
+      <c r="BK2" s="20"/>
+      <c r="BL2" s="20"/>
     </row>
     <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="26" t="s">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="24" t="s">
         <v>5</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="26" t="s">
+      <c r="L3" s="25"/>
+      <c r="M3" s="24" t="s">
         <v>10</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27" t="n">
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="R3" s="21"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-      <c r="W3" s="21"/>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="21"/>
-      <c r="AE3" s="21"/>
-      <c r="AF3" s="21"/>
-      <c r="AG3" s="21"/>
-      <c r="AH3" s="21"/>
-      <c r="AI3" s="21"/>
-      <c r="AJ3" s="21"/>
-      <c r="AK3" s="22"/>
-      <c r="AL3" s="22"/>
-      <c r="AM3" s="23"/>
-      <c r="AN3" s="23"/>
-      <c r="AO3" s="23"/>
-      <c r="AP3" s="0"/>
-      <c r="AQ3" s="0"/>
-      <c r="AR3" s="0"/>
-      <c r="AS3" s="0"/>
-      <c r="AT3" s="0"/>
-      <c r="AU3" s="0"/>
-      <c r="AV3" s="0"/>
-      <c r="AW3" s="0"/>
-      <c r="AX3" s="0"/>
-      <c r="AY3" s="0"/>
-      <c r="AZ3" s="0"/>
-      <c r="BA3" s="0"/>
-      <c r="BB3" s="0"/>
-      <c r="BC3" s="0"/>
-      <c r="BD3" s="0"/>
-      <c r="BE3" s="0"/>
-      <c r="BF3" s="0"/>
-      <c r="BG3" s="0"/>
-      <c r="BH3" s="0"/>
-      <c r="BI3" s="0"/>
-      <c r="BJ3" s="0"/>
-      <c r="BK3" s="0"/>
-      <c r="BL3" s="0"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+      <c r="Z3" s="19"/>
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="19"/>
+      <c r="AF3" s="19"/>
+      <c r="AG3" s="19"/>
+      <c r="AH3" s="19"/>
+      <c r="AI3" s="19"/>
+      <c r="AJ3" s="19"/>
+      <c r="AK3" s="19"/>
+      <c r="AL3" s="19"/>
+      <c r="AM3" s="20"/>
+      <c r="AN3" s="20"/>
+      <c r="AO3" s="20"/>
+      <c r="AP3" s="20"/>
+      <c r="AQ3" s="20"/>
+      <c r="AR3" s="20"/>
+      <c r="AS3" s="20"/>
+      <c r="AT3" s="20"/>
+      <c r="AU3" s="20"/>
+      <c r="AV3" s="20"/>
+      <c r="AW3" s="20"/>
+      <c r="AX3" s="20"/>
+      <c r="AY3" s="20"/>
+      <c r="AZ3" s="20"/>
+      <c r="BA3" s="20"/>
+      <c r="BB3" s="20"/>
+      <c r="BC3" s="20"/>
+      <c r="BD3" s="20"/>
+      <c r="BE3" s="20"/>
+      <c r="BF3" s="20"/>
+      <c r="BG3" s="20"/>
+      <c r="BH3" s="20"/>
+      <c r="BI3" s="20"/>
+      <c r="BJ3" s="20"/>
+      <c r="BK3" s="20"/>
+      <c r="BL3" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="26" t="s">
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="24" t="s">
         <v>5</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="26" t="s">
+      <c r="L4" s="25"/>
+      <c r="M4" s="24" t="s">
         <v>10</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27" t="n">
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="21"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="21"/>
-      <c r="X4" s="21"/>
-      <c r="Y4" s="21"/>
-      <c r="Z4" s="21"/>
-      <c r="AA4" s="20"/>
-      <c r="AB4" s="20"/>
-      <c r="AC4" s="20"/>
-      <c r="AD4" s="21"/>
-      <c r="AE4" s="21"/>
-      <c r="AF4" s="20"/>
-      <c r="AG4" s="20"/>
-      <c r="AH4" s="20"/>
-      <c r="AI4" s="0"/>
-      <c r="AJ4" s="0"/>
-      <c r="AK4" s="22"/>
-      <c r="AL4" s="22"/>
-      <c r="AM4" s="0"/>
-      <c r="AN4" s="29"/>
-      <c r="AO4" s="23"/>
-      <c r="AP4" s="0"/>
-      <c r="AQ4" s="0"/>
-      <c r="AR4" s="0"/>
-      <c r="AS4" s="0"/>
-      <c r="AT4" s="0"/>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
-      <c r="AW4" s="0"/>
-      <c r="AX4" s="0"/>
-      <c r="AY4" s="0"/>
-      <c r="AZ4" s="0"/>
-      <c r="BA4" s="0"/>
-      <c r="BB4" s="0"/>
-      <c r="BC4" s="0"/>
-      <c r="BD4" s="0"/>
-      <c r="BE4" s="0"/>
-      <c r="BF4" s="0"/>
-      <c r="BG4" s="0"/>
-      <c r="BH4" s="0"/>
-      <c r="BI4" s="0"/>
-      <c r="BJ4" s="0"/>
-      <c r="BK4" s="0"/>
-      <c r="BL4" s="0"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+      <c r="V4" s="21"/>
+      <c r="W4" s="19"/>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="19"/>
+      <c r="Z4" s="19"/>
+      <c r="AA4" s="19"/>
+      <c r="AB4" s="19"/>
+      <c r="AC4" s="19"/>
+      <c r="AD4" s="19"/>
+      <c r="AE4" s="19"/>
+      <c r="AF4" s="19"/>
+      <c r="AG4" s="19"/>
+      <c r="AH4" s="19"/>
+      <c r="AI4" s="19"/>
+      <c r="AJ4" s="19"/>
+      <c r="AK4" s="19"/>
+      <c r="AL4" s="19"/>
+      <c r="AM4" s="20"/>
+      <c r="AN4" s="20"/>
+      <c r="AO4" s="20"/>
+      <c r="AP4" s="20"/>
+      <c r="AQ4" s="20"/>
+      <c r="AR4" s="20"/>
+      <c r="AS4" s="20"/>
+      <c r="AT4" s="20"/>
+      <c r="AU4" s="20"/>
+      <c r="AV4" s="20"/>
+      <c r="AW4" s="20"/>
+      <c r="AX4" s="20"/>
+      <c r="AY4" s="20"/>
+      <c r="AZ4" s="20"/>
+      <c r="BA4" s="20"/>
+      <c r="BB4" s="20"/>
+      <c r="BC4" s="20"/>
+      <c r="BD4" s="20"/>
+      <c r="BE4" s="20"/>
+      <c r="BF4" s="20"/>
+      <c r="BG4" s="20"/>
+      <c r="BH4" s="20"/>
+      <c r="BI4" s="20"/>
+      <c r="BJ4" s="20"/>
+      <c r="BK4" s="20"/>
+      <c r="BL4" s="20"/>
     </row>
     <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="26" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="24" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="26" t="s">
+      <c r="L5" s="25"/>
+      <c r="M5" s="24" t="s">
         <v>10</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27" t="n">
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="R5" s="21"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="21"/>
-      <c r="X5" s="21"/>
-      <c r="Y5" s="21"/>
-      <c r="Z5" s="21"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="30"/>
-      <c r="AD5" s="21"/>
-      <c r="AE5" s="21"/>
-      <c r="AF5" s="21"/>
-      <c r="AG5" s="21"/>
-      <c r="AH5" s="21"/>
-      <c r="AI5" s="21"/>
-      <c r="AJ5" s="21"/>
-      <c r="AK5" s="22"/>
-      <c r="AL5" s="22"/>
-      <c r="AM5" s="23"/>
-      <c r="AN5" s="23"/>
-      <c r="AO5" s="23"/>
-      <c r="AP5" s="0"/>
-      <c r="AQ5" s="0"/>
-      <c r="AR5" s="0"/>
-      <c r="AS5" s="0"/>
-      <c r="AT5" s="0"/>
-      <c r="AU5" s="0"/>
-      <c r="AV5" s="0"/>
-      <c r="AW5" s="0"/>
-      <c r="AX5" s="0"/>
-      <c r="AY5" s="0"/>
-      <c r="AZ5" s="0"/>
-      <c r="BA5" s="0"/>
-      <c r="BB5" s="0"/>
-      <c r="BC5" s="0"/>
-      <c r="BD5" s="0"/>
-      <c r="BE5" s="0"/>
-      <c r="BF5" s="0"/>
-      <c r="BG5" s="0"/>
-      <c r="BH5" s="0"/>
-      <c r="BI5" s="0"/>
-      <c r="BJ5" s="0"/>
-      <c r="BK5" s="0"/>
-      <c r="BL5" s="0"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="21"/>
+      <c r="V5" s="21"/>
+      <c r="W5" s="19"/>
+      <c r="X5" s="19"/>
+      <c r="Y5" s="19"/>
+      <c r="Z5" s="19"/>
+      <c r="AA5" s="19"/>
+      <c r="AB5" s="19"/>
+      <c r="AC5" s="19"/>
+      <c r="AD5" s="19"/>
+      <c r="AE5" s="19"/>
+      <c r="AF5" s="19"/>
+      <c r="AG5" s="19"/>
+      <c r="AH5" s="19"/>
+      <c r="AI5" s="19"/>
+      <c r="AJ5" s="19"/>
+      <c r="AK5" s="19"/>
+      <c r="AL5" s="19"/>
+      <c r="AM5" s="20"/>
+      <c r="AN5" s="20"/>
+      <c r="AO5" s="20"/>
+      <c r="AP5" s="20"/>
+      <c r="AQ5" s="20"/>
+      <c r="AR5" s="20"/>
+      <c r="AS5" s="20"/>
+      <c r="AT5" s="20"/>
+      <c r="AU5" s="20"/>
+      <c r="AV5" s="20"/>
+      <c r="AW5" s="20"/>
+      <c r="AX5" s="20"/>
+      <c r="AY5" s="20"/>
+      <c r="AZ5" s="20"/>
+      <c r="BA5" s="20"/>
+      <c r="BB5" s="20"/>
+      <c r="BC5" s="20"/>
+      <c r="BD5" s="20"/>
+      <c r="BE5" s="20"/>
+      <c r="BF5" s="20"/>
+      <c r="BG5" s="20"/>
+      <c r="BH5" s="20"/>
+      <c r="BI5" s="20"/>
+      <c r="BJ5" s="20"/>
+      <c r="BK5" s="20"/>
+      <c r="BL5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24"/>
-      <c r="B6" s="31" t="s">
+      <c r="A6" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="26"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="25"/>
+      <c r="M6" s="24" t="s">
+        <v>14</v>
+      </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="21"/>
-      <c r="X6" s="21"/>
-      <c r="Y6" s="21"/>
-      <c r="Z6" s="0"/>
-      <c r="AA6" s="0"/>
-      <c r="AB6" s="0"/>
-      <c r="AC6" s="0"/>
-      <c r="AD6" s="21"/>
-      <c r="AE6" s="21"/>
-      <c r="AF6" s="21"/>
-      <c r="AG6" s="21"/>
-      <c r="AH6" s="21"/>
-      <c r="AI6" s="0"/>
-      <c r="AJ6" s="21"/>
-      <c r="AK6" s="22"/>
-      <c r="AL6" s="22"/>
-      <c r="AM6" s="23"/>
-      <c r="AN6" s="23"/>
-      <c r="AO6" s="23"/>
-      <c r="AP6" s="0"/>
-      <c r="AQ6" s="0"/>
-      <c r="AR6" s="0"/>
-      <c r="AS6" s="0"/>
-      <c r="AT6" s="0"/>
-      <c r="AU6" s="0"/>
-      <c r="AV6" s="0"/>
-      <c r="AW6" s="0"/>
-      <c r="AX6" s="0"/>
-      <c r="AY6" s="0"/>
-      <c r="AZ6" s="0"/>
-      <c r="BA6" s="0"/>
-      <c r="BB6" s="0"/>
-      <c r="BC6" s="0"/>
-      <c r="BD6" s="0"/>
-      <c r="BE6" s="0"/>
-      <c r="BF6" s="0"/>
-      <c r="BG6" s="0"/>
-      <c r="BH6" s="0"/>
-      <c r="BI6" s="0"/>
-      <c r="BJ6" s="0"/>
-      <c r="BK6" s="0"/>
-      <c r="BL6" s="0"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="19"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="21"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="19"/>
+      <c r="AF6" s="19"/>
+      <c r="AG6" s="19"/>
+      <c r="AH6" s="19"/>
+      <c r="AI6" s="19"/>
+      <c r="AJ6" s="19"/>
+      <c r="AK6" s="19"/>
+      <c r="AL6" s="19"/>
+      <c r="AM6" s="20"/>
+      <c r="AN6" s="20"/>
+      <c r="AO6" s="20"/>
+      <c r="AP6" s="20"/>
+      <c r="AQ6" s="20"/>
+      <c r="AR6" s="20"/>
+      <c r="AS6" s="20"/>
+      <c r="AT6" s="20"/>
+      <c r="AU6" s="20"/>
+      <c r="AV6" s="20"/>
+      <c r="AW6" s="20"/>
+      <c r="AX6" s="20"/>
+      <c r="AY6" s="20"/>
+      <c r="AZ6" s="20"/>
+      <c r="BA6" s="20"/>
+      <c r="BB6" s="20"/>
+      <c r="BC6" s="20"/>
+      <c r="BD6" s="20"/>
+      <c r="BE6" s="20"/>
+      <c r="BF6" s="20"/>
+      <c r="BG6" s="20"/>
+      <c r="BH6" s="20"/>
+      <c r="BI6" s="20"/>
+      <c r="BJ6" s="20"/>
+      <c r="BK6" s="20"/>
+      <c r="BL6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="27"/>
-      <c r="M7" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="27" t="n">
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="21"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
-      <c r="W7" s="21"/>
-      <c r="X7" s="21"/>
-      <c r="Y7" s="21"/>
-      <c r="Z7" s="21"/>
-      <c r="AA7" s="21"/>
-      <c r="AB7" s="21"/>
-      <c r="AC7" s="21"/>
-      <c r="AD7" s="21"/>
-      <c r="AE7" s="21"/>
-      <c r="AF7" s="21"/>
-      <c r="AG7" s="21"/>
-      <c r="AH7" s="21"/>
-      <c r="AI7" s="0"/>
-      <c r="AJ7" s="20"/>
-      <c r="AK7" s="22"/>
-      <c r="AL7" s="22"/>
-      <c r="AM7" s="23"/>
-      <c r="AN7" s="23"/>
-      <c r="AO7" s="23"/>
-      <c r="AP7" s="0"/>
-      <c r="AQ7" s="0"/>
-      <c r="AR7" s="0"/>
-      <c r="AS7" s="0"/>
-      <c r="AT7" s="0"/>
-      <c r="AU7" s="0"/>
-      <c r="AV7" s="0"/>
-      <c r="AW7" s="0"/>
-      <c r="AX7" s="0"/>
-      <c r="AY7" s="0"/>
-      <c r="AZ7" s="0"/>
-      <c r="BA7" s="0"/>
-      <c r="BB7" s="0"/>
-      <c r="BC7" s="0"/>
-      <c r="BD7" s="0"/>
-      <c r="BE7" s="0"/>
-      <c r="BF7" s="0"/>
-      <c r="BG7" s="0"/>
-      <c r="BH7" s="0"/>
-      <c r="BI7" s="0"/>
-      <c r="BJ7" s="0"/>
-      <c r="BK7" s="0"/>
-      <c r="BL7" s="0"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="39"/>
-      <c r="Q8" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="40"/>
-      <c r="S8" s="41"/>
-      <c r="T8" s="42"/>
-      <c r="U8" s="42"/>
-      <c r="V8" s="42"/>
-      <c r="W8" s="40"/>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="40"/>
-      <c r="Z8" s="40"/>
-      <c r="AA8" s="40"/>
-      <c r="AB8" s="40"/>
-      <c r="AC8" s="40"/>
-      <c r="AD8" s="40"/>
-      <c r="AE8" s="40"/>
-      <c r="AF8" s="40"/>
-      <c r="AG8" s="40"/>
-      <c r="AH8" s="40"/>
-      <c r="AI8" s="40"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="34"/>
+      <c r="X7" s="34"/>
+      <c r="Y7" s="34"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="34"/>
+      <c r="AB7" s="34"/>
+      <c r="AC7" s="34"/>
+      <c r="AD7" s="34"/>
+      <c r="AE7" s="34"/>
+      <c r="AF7" s="34"/>
+      <c r="AG7" s="34"/>
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="34"/>
+      <c r="AJ7" s="34"/>
+      <c r="AK7" s="34"/>
+      <c r="AL7" s="34"/>
+      <c r="AM7" s="35"/>
+      <c r="AN7" s="35"/>
+      <c r="AO7" s="35"/>
+      <c r="AP7" s="35"/>
+      <c r="AQ7" s="35"/>
+      <c r="AR7" s="35"/>
+      <c r="AS7" s="35"/>
+      <c r="AT7" s="35"/>
+      <c r="AU7" s="35"/>
+      <c r="AV7" s="35"/>
+      <c r="AW7" s="35"/>
+      <c r="AX7" s="35"/>
+      <c r="AY7" s="35"/>
+      <c r="AZ7" s="35"/>
+      <c r="BA7" s="35"/>
+      <c r="BB7" s="35"/>
+      <c r="BC7" s="35"/>
+      <c r="BD7" s="35"/>
+      <c r="BE7" s="35"/>
+      <c r="BF7" s="35"/>
+      <c r="BG7" s="35"/>
+      <c r="BH7" s="35"/>
+      <c r="BI7" s="35"/>
+      <c r="BJ7" s="35"/>
+      <c r="BK7" s="35"/>
+      <c r="BL7" s="35"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="T8" s="2"/>
+      <c r="W8" s="0"/>
+      <c r="X8" s="0"/>
+      <c r="Y8" s="0"/>
+      <c r="Z8" s="0"/>
+      <c r="AA8" s="0"/>
+      <c r="AB8" s="0"/>
+      <c r="AC8" s="0"/>
+      <c r="AD8" s="0"/>
+      <c r="AE8" s="0"/>
+      <c r="AF8" s="0"/>
+      <c r="AG8" s="0"/>
+      <c r="AH8" s="0"/>
+      <c r="AI8" s="0"/>
       <c r="AJ8" s="0"/>
-      <c r="AK8" s="43"/>
-      <c r="AL8" s="43"/>
-      <c r="AM8" s="20"/>
-      <c r="AN8" s="44"/>
-      <c r="AO8" s="44"/>
-      <c r="AP8" s="0"/>
-      <c r="AQ8" s="0"/>
-      <c r="AR8" s="0"/>
-      <c r="AS8" s="0"/>
-      <c r="AT8" s="0"/>
-      <c r="AU8" s="0"/>
-      <c r="AV8" s="0"/>
-      <c r="AW8" s="0"/>
-      <c r="AX8" s="0"/>
-      <c r="AY8" s="0"/>
-      <c r="AZ8" s="0"/>
-      <c r="BA8" s="0"/>
-      <c r="BB8" s="0"/>
-      <c r="BC8" s="0"/>
-      <c r="BD8" s="0"/>
-      <c r="BE8" s="0"/>
-      <c r="BF8" s="0"/>
-      <c r="BG8" s="0"/>
-      <c r="BH8" s="0"/>
-      <c r="BI8" s="0"/>
-      <c r="BJ8" s="0"/>
-      <c r="BK8" s="0"/>
-      <c r="BL8" s="0"/>
+      <c r="AK8" s="0"/>
+      <c r="AL8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="T9" s="2"/>
+      <c r="B9" s="37"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+      <c r="I9" s="0"/>
+      <c r="J9" s="0"/>
+      <c r="K9" s="0"/>
+      <c r="L9" s="0"/>
+      <c r="M9" s="0"/>
+      <c r="N9" s="0"/>
+      <c r="O9" s="0"/>
+      <c r="P9" s="0"/>
+      <c r="Q9" s="0"/>
+      <c r="R9" s="0"/>
+      <c r="S9" s="0"/>
+      <c r="T9" s="0"/>
+      <c r="U9" s="0"/>
+      <c r="V9" s="0"/>
       <c r="W9" s="0"/>
       <c r="X9" s="0"/>
       <c r="Y9" s="0"/>
@@ -1553,7 +1438,6 @@
       <c r="AL9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="45"/>
       <c r="D10" s="0"/>
       <c r="E10" s="0"/>
       <c r="F10" s="0"/>
@@ -1591,21 +1475,47 @@
       <c r="AL10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="41" t="n">
+        <f aca="false">A11+A13</f>
+        <v>7</v>
+      </c>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
+      <c r="F11" s="39" t="n">
+        <f aca="false">C11</f>
+        <v>7</v>
+      </c>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41" t="n">
+        <f aca="false">F11+F13</f>
+        <v>10</v>
+      </c>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
-      <c r="K11" s="0"/>
-      <c r="L11" s="0"/>
-      <c r="M11" s="0"/>
+      <c r="K11" s="39" t="n">
+        <f aca="false">MAX(H11,H17,H23)</f>
+        <v>13</v>
+      </c>
+      <c r="L11" s="40"/>
+      <c r="M11" s="41" t="n">
+        <f aca="false">K11+K13</f>
+        <v>14</v>
+      </c>
       <c r="N11" s="0"/>
       <c r="O11" s="0"/>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="0"/>
-      <c r="R11" s="0"/>
+      <c r="P11" s="39" t="n">
+        <f aca="false">M11</f>
+        <v>14</v>
+      </c>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="41" t="n">
+        <f aca="false">P11+P13</f>
+        <v>15</v>
+      </c>
       <c r="S11" s="0"/>
       <c r="T11" s="0"/>
       <c r="U11" s="0"/>
@@ -1628,47 +1538,32 @@
       <c r="AL11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="49" t="n">
-        <f aca="false">A12+A14</f>
-        <v>7</v>
-      </c>
+      <c r="A12" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="47" t="n">
-        <f aca="false">C12</f>
+      <c r="F12" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="48"/>
-      <c r="H12" s="49" t="n">
-        <f aca="false">F12+F14</f>
-        <v>10</v>
-      </c>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="47" t="n">
-        <f aca="false">MAX(H12,H18,H24)</f>
-        <v>13</v>
-      </c>
-      <c r="L12" s="48"/>
-      <c r="M12" s="49" t="n">
-        <f aca="false">K12+K14</f>
-        <v>14</v>
-      </c>
+      <c r="K12" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
-      <c r="P12" s="47" t="n">
-        <f aca="false">M12</f>
+      <c r="P12" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="Q12" s="48"/>
-      <c r="R12" s="49" t="n">
-        <f aca="false">P12+P14</f>
-        <v>15</v>
-      </c>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
       <c r="U12" s="0"/>
@@ -1690,33 +1585,48 @@
       <c r="AK12" s="0"/>
       <c r="AL12" s="0"/>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="0"/>
-      <c r="E13" s="0"/>
-      <c r="F13" s="50" t="s">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="43" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0"/>
-      <c r="K13" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="0"/>
-      <c r="O13" s="0"/>
-      <c r="P13" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
+      <c r="B13" s="44" t="n">
+        <f aca="false">C14-C11</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="43" t="n">
+        <f aca="false">Q3</f>
+        <v>3</v>
+      </c>
+      <c r="G13" s="44" t="n">
+        <f aca="false">H14-H11</f>
+        <v>3</v>
+      </c>
+      <c r="H13" s="45"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="43" t="n">
+        <f aca="false">Q6</f>
+        <v>1</v>
+      </c>
+      <c r="L13" s="44" t="n">
+        <f aca="false">M14-M11</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="45"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="43" t="n">
+        <f aca="false">Q7</f>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="44" t="n">
+        <f aca="false">R14-R11</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="45"/>
       <c r="S13" s="0"/>
       <c r="T13" s="0"/>
       <c r="U13" s="0"/>
@@ -1738,48 +1648,49 @@
       <c r="AK13" s="0"/>
       <c r="AL13" s="0"/>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="49" t="n">
+        <f aca="false">C14-A13</f>
+        <v>0</v>
+      </c>
+      <c r="B14" s="37"/>
+      <c r="C14" s="50" t="n">
+        <f aca="false">MIN(F26,F20,F14)</f>
         <v>7</v>
       </c>
-      <c r="B14" s="52" t="n">
-        <f aca="false">C15-C12</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="53"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="51" t="n">
-        <f aca="false">Q3</f>
-        <v>3</v>
-      </c>
-      <c r="G14" s="56" t="n">
-        <f aca="false">H15-H12</f>
-        <v>3</v>
-      </c>
-      <c r="H14" s="53"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="51" t="n">
-        <f aca="false">Q7</f>
-        <v>1</v>
-      </c>
-      <c r="L14" s="52" t="n">
-        <f aca="false">M15-M12</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="53"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="55"/>
-      <c r="P14" s="51" t="n">
-        <f aca="false">Q8</f>
-        <v>1</v>
-      </c>
-      <c r="Q14" s="52" t="n">
-        <f aca="false">R15-R12</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="53"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="49" t="n">
+        <f aca="false">H14-F13</f>
+        <v>10</v>
+      </c>
+      <c r="G14" s="37"/>
+      <c r="H14" s="50" t="n">
+        <f aca="false">K14</f>
+        <v>13</v>
+      </c>
+      <c r="I14" s="0"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="49" t="n">
+        <f aca="false">M14-K13</f>
+        <v>13</v>
+      </c>
+      <c r="L14" s="37"/>
+      <c r="M14" s="50" t="n">
+        <f aca="false">P14</f>
+        <v>14</v>
+      </c>
+      <c r="N14" s="0"/>
+      <c r="O14" s="0"/>
+      <c r="P14" s="49" t="n">
+        <f aca="false">R14-P13</f>
+        <v>14</v>
+      </c>
+      <c r="Q14" s="37"/>
+      <c r="R14" s="50" t="n">
+        <f aca="false">R11</f>
+        <v>15</v>
+      </c>
       <c r="S14" s="0"/>
       <c r="T14" s="0"/>
       <c r="U14" s="0"/>
@@ -1802,48 +1713,21 @@
       <c r="AL14" s="0"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58" t="n">
-        <f aca="false">C15-A14</f>
-        <v>0</v>
-      </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="59" t="n">
-        <f aca="false">MIN(F27,F21,F15)</f>
-        <v>7</v>
-      </c>
-      <c r="D15" s="60"/>
+      <c r="D15" s="51"/>
       <c r="E15" s="0"/>
-      <c r="F15" s="58" t="n">
-        <f aca="false">H15-F14</f>
-        <v>10</v>
-      </c>
-      <c r="G15" s="45"/>
-      <c r="H15" s="59" t="n">
-        <f aca="false">K15</f>
-        <v>13</v>
-      </c>
+      <c r="F15" s="0"/>
+      <c r="G15" s="0"/>
+      <c r="H15" s="0"/>
       <c r="I15" s="0"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="58" t="n">
-        <f aca="false">M15-K14</f>
-        <v>13</v>
-      </c>
-      <c r="L15" s="45"/>
-      <c r="M15" s="59" t="n">
-        <f aca="false">P15</f>
-        <v>14</v>
-      </c>
+      <c r="J15" s="52"/>
+      <c r="K15" s="0"/>
+      <c r="L15" s="0"/>
+      <c r="M15" s="0"/>
       <c r="N15" s="0"/>
       <c r="O15" s="0"/>
-      <c r="P15" s="58" t="n">
-        <f aca="false">R15-P14</f>
-        <v>14</v>
-      </c>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="59" t="n">
-        <f aca="false">R12</f>
-        <v>15</v>
-      </c>
+      <c r="P15" s="0"/>
+      <c r="Q15" s="0"/>
+      <c r="R15" s="0"/>
       <c r="S15" s="0"/>
       <c r="T15" s="0"/>
       <c r="U15" s="0"/>
@@ -1866,13 +1750,13 @@
       <c r="AL15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="60"/>
+      <c r="D16" s="51"/>
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0"/>
       <c r="H16" s="0"/>
       <c r="I16" s="0"/>
-      <c r="J16" s="61"/>
+      <c r="J16" s="52"/>
       <c r="K16" s="0"/>
       <c r="L16" s="0"/>
       <c r="M16" s="0"/>
@@ -1903,13 +1787,19 @@
       <c r="AL16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="60"/>
+      <c r="D17" s="51"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="0"/>
-      <c r="G17" s="0"/>
-      <c r="H17" s="0"/>
+      <c r="F17" s="39" t="n">
+        <f aca="false">C11</f>
+        <v>7</v>
+      </c>
+      <c r="G17" s="40"/>
+      <c r="H17" s="41" t="n">
+        <f aca="false">F17+F19</f>
+        <v>13</v>
+      </c>
       <c r="I17" s="0"/>
-      <c r="J17" s="61"/>
+      <c r="J17" s="52"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0"/>
       <c r="M17" s="0"/>
@@ -1940,19 +1830,15 @@
       <c r="AL17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="60"/>
+      <c r="D18" s="51"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="47" t="n">
-        <f aca="false">C12</f>
-        <v>7</v>
-      </c>
-      <c r="G18" s="48"/>
-      <c r="H18" s="49" t="n">
-        <f aca="false">F18+F20</f>
-        <v>13</v>
-      </c>
+      <c r="F18" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
       <c r="I18" s="0"/>
-      <c r="J18" s="61"/>
+      <c r="J18" s="52"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
       <c r="M18" s="0"/>
@@ -1962,9 +1848,6 @@
       <c r="Q18" s="0"/>
       <c r="R18" s="0"/>
       <c r="S18" s="0"/>
-      <c r="T18" s="0"/>
-      <c r="U18" s="0"/>
-      <c r="V18" s="0"/>
       <c r="W18" s="0"/>
       <c r="X18" s="0"/>
       <c r="Y18" s="0"/>
@@ -1982,16 +1865,20 @@
       <c r="AK18" s="0"/>
       <c r="AL18" s="0"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="60"/>
-      <c r="E19" s="0"/>
-      <c r="F19" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="0"/>
-      <c r="J19" s="61"/>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="51"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="43" t="n">
+        <f aca="false">Q4</f>
+        <v>6</v>
+      </c>
+      <c r="G19" s="44" t="n">
+        <f aca="false">H20-H17</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="45"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="52"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0"/>
       <c r="M19" s="0"/>
@@ -2018,20 +1905,20 @@
       <c r="AK19" s="0"/>
       <c r="AL19" s="0"/>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="60"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="51" t="n">
-        <f aca="false">Q4</f>
-        <v>6</v>
-      </c>
-      <c r="G20" s="52" t="n">
-        <f aca="false">H21-H18</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="53"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="61"/>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D20" s="51"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="49" t="n">
+        <f aca="false">H20-F19</f>
+        <v>7</v>
+      </c>
+      <c r="G20" s="37"/>
+      <c r="H20" s="50" t="n">
+        <f aca="false">K14</f>
+        <v>13</v>
+      </c>
+      <c r="I20" s="0"/>
+      <c r="J20" s="52"/>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
       <c r="M20" s="0"/>
@@ -2059,19 +1946,14 @@
       <c r="AL20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="60"/>
+      <c r="A21" s="2"/>
+      <c r="D21" s="51"/>
       <c r="E21" s="0"/>
-      <c r="F21" s="58" t="n">
-        <f aca="false">H21-F20</f>
-        <v>7</v>
-      </c>
-      <c r="G21" s="45"/>
-      <c r="H21" s="59" t="n">
-        <f aca="false">K15</f>
-        <v>13</v>
-      </c>
+      <c r="F21" s="0"/>
+      <c r="G21" s="0"/>
+      <c r="H21" s="0"/>
       <c r="I21" s="0"/>
-      <c r="J21" s="61"/>
+      <c r="J21" s="52"/>
       <c r="K21" s="0"/>
       <c r="L21" s="0"/>
       <c r="M21" s="0"/>
@@ -2100,13 +1982,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="D22" s="60"/>
+      <c r="D22" s="51"/>
       <c r="E22" s="0"/>
       <c r="F22" s="0"/>
       <c r="G22" s="0"/>
       <c r="H22" s="0"/>
       <c r="I22" s="0"/>
-      <c r="J22" s="61"/>
+      <c r="J22" s="52"/>
       <c r="K22" s="0"/>
       <c r="L22" s="0"/>
       <c r="M22" s="0"/>
@@ -2135,13 +2017,19 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="D23" s="60"/>
+      <c r="D23" s="51"/>
       <c r="E23" s="0"/>
-      <c r="F23" s="0"/>
-      <c r="G23" s="0"/>
-      <c r="H23" s="0"/>
+      <c r="F23" s="39" t="n">
+        <f aca="false">C11</f>
+        <v>7</v>
+      </c>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41" t="n">
+        <f aca="false">F23+F25</f>
+        <v>10</v>
+      </c>
       <c r="I23" s="0"/>
-      <c r="J23" s="61"/>
+      <c r="J23" s="52"/>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
       <c r="M23" s="0"/>
@@ -2151,38 +2039,20 @@
       <c r="Q23" s="0"/>
       <c r="R23" s="0"/>
       <c r="S23" s="0"/>
-      <c r="W23" s="0"/>
-      <c r="X23" s="0"/>
-      <c r="Y23" s="0"/>
-      <c r="Z23" s="0"/>
-      <c r="AA23" s="0"/>
-      <c r="AB23" s="0"/>
-      <c r="AC23" s="0"/>
-      <c r="AD23" s="0"/>
-      <c r="AE23" s="0"/>
-      <c r="AF23" s="0"/>
-      <c r="AG23" s="0"/>
-      <c r="AH23" s="0"/>
-      <c r="AI23" s="0"/>
-      <c r="AJ23" s="0"/>
-      <c r="AK23" s="0"/>
-      <c r="AL23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="D24" s="60"/>
+      <c r="A24" s="0"/>
+      <c r="B24" s="0"/>
+      <c r="C24" s="0"/>
+      <c r="D24" s="51"/>
       <c r="E24" s="0"/>
-      <c r="F24" s="47" t="n">
-        <f aca="false">C12</f>
-        <v>7</v>
-      </c>
-      <c r="G24" s="48"/>
-      <c r="H24" s="49" t="n">
-        <f aca="false">F24+F26</f>
-        <v>10</v>
-      </c>
+      <c r="F24" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
       <c r="I24" s="0"/>
-      <c r="J24" s="61"/>
+      <c r="J24" s="52"/>
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
       <c r="M24" s="0"/>
@@ -2193,19 +2063,23 @@
       <c r="R24" s="0"/>
       <c r="S24" s="0"/>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0"/>
       <c r="B25" s="0"/>
       <c r="C25" s="0"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="0"/>
-      <c r="F25" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="0"/>
-      <c r="J25" s="61"/>
+      <c r="D25" s="0"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="43" t="n">
+        <f aca="false">Q5</f>
+        <v>3</v>
+      </c>
+      <c r="G25" s="44" t="n">
+        <f aca="false">H26-H23</f>
+        <v>3</v>
+      </c>
+      <c r="H25" s="45"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="0"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
       <c r="M25" s="0"/>
@@ -2216,32 +2090,25 @@
       <c r="R25" s="0"/>
       <c r="S25" s="0"/>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0"/>
       <c r="B26" s="0"/>
       <c r="C26" s="0"/>
       <c r="D26" s="0"/>
-      <c r="E26" s="55"/>
-      <c r="F26" s="51" t="n">
-        <f aca="false">Q5</f>
-        <v>3</v>
-      </c>
-      <c r="G26" s="56" t="n">
-        <f aca="false">H27-H24</f>
-        <v>3</v>
-      </c>
-      <c r="H26" s="53"/>
-      <c r="I26" s="55"/>
+      <c r="E26" s="0"/>
+      <c r="F26" s="49" t="n">
+        <f aca="false">H26-F25</f>
+        <v>10</v>
+      </c>
+      <c r="G26" s="37"/>
+      <c r="H26" s="50" t="n">
+        <f aca="false">K14</f>
+        <v>13</v>
+      </c>
+      <c r="I26" s="0"/>
       <c r="J26" s="0"/>
       <c r="K26" s="0"/>
       <c r="L26" s="0"/>
-      <c r="M26" s="0"/>
-      <c r="N26" s="0"/>
-      <c r="O26" s="0"/>
-      <c r="P26" s="0"/>
-      <c r="Q26" s="0"/>
-      <c r="R26" s="0"/>
-      <c r="S26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0"/>
@@ -2249,15 +2116,9 @@
       <c r="C27" s="0"/>
       <c r="D27" s="0"/>
       <c r="E27" s="0"/>
-      <c r="F27" s="58" t="n">
-        <f aca="false">H27-F26</f>
-        <v>10</v>
-      </c>
-      <c r="G27" s="45"/>
-      <c r="H27" s="59" t="n">
-        <f aca="false">K15</f>
-        <v>13</v>
-      </c>
+      <c r="F27" s="0"/>
+      <c r="G27" s="0"/>
+      <c r="H27" s="0"/>
       <c r="I27" s="0"/>
       <c r="J27" s="0"/>
       <c r="K27" s="0"/>
@@ -2404,228 +2265,214 @@
       <c r="L37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0"/>
-      <c r="B38" s="0"/>
-      <c r="C38" s="0"/>
-      <c r="D38" s="0"/>
-      <c r="E38" s="0"/>
-      <c r="F38" s="0"/>
-      <c r="G38" s="0"/>
-      <c r="H38" s="0"/>
-      <c r="I38" s="0"/>
-      <c r="J38" s="0"/>
-      <c r="K38" s="0"/>
-      <c r="L38" s="0"/>
+      <c r="A38" s="53"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="54"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="62"/>
-      <c r="B39" s="63"/>
-      <c r="C39" s="63"/>
-      <c r="D39" s="63"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="63"/>
-      <c r="I39" s="63"/>
-      <c r="J39" s="63"/>
-      <c r="K39" s="63"/>
-      <c r="L39" s="63"/>
+      <c r="A39" s="53"/>
+      <c r="B39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L39" s="54"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="62"/>
-      <c r="B40" s="2" t="s">
+      <c r="A40" s="53"/>
+      <c r="B40" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="F40" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="L40" s="54"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="53"/>
+      <c r="B41" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="L41" s="54"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="53"/>
+      <c r="B42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L42" s="54"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="53"/>
+      <c r="L43" s="54"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="53"/>
+      <c r="B44" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="37"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="54"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="53"/>
+      <c r="B45" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="37"/>
+      <c r="K45" s="37"/>
+      <c r="L45" s="54"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="53"/>
+      <c r="B46" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L40" s="63"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="62"/>
-      <c r="B41" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="C41" s="64"/>
-      <c r="D41" s="64"/>
-      <c r="F41" s="65" t="s">
+      <c r="C46" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="37"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="37"/>
+      <c r="I46" s="37"/>
+      <c r="J46" s="37"/>
+      <c r="K46" s="37"/>
+      <c r="L46" s="54"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="53"/>
+      <c r="B47" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37"/>
+      <c r="I47" s="37"/>
+      <c r="J47" s="37"/>
+      <c r="K47" s="37"/>
+      <c r="L47" s="54"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="53"/>
+      <c r="B48" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="37"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="37"/>
+      <c r="K48" s="37"/>
+      <c r="L48" s="54"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="53"/>
+      <c r="B49" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
-      <c r="I41" s="65"/>
-      <c r="J41" s="65"/>
-      <c r="L41" s="63"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="62"/>
-      <c r="B42" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C42" s="67" t="s">
+      <c r="C49" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="37"/>
+      <c r="I49" s="37"/>
+      <c r="J49" s="37"/>
+      <c r="K49" s="37"/>
+      <c r="L49" s="54"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="53"/>
+      <c r="B50" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="L42" s="63"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="62"/>
-      <c r="B43" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L43" s="63"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="62"/>
-      <c r="L44" s="63"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="62"/>
-      <c r="B45" s="68" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="45"/>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="45"/>
-      <c r="K45" s="45"/>
-      <c r="L45" s="63"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="62"/>
-      <c r="B46" s="68" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="45"/>
-      <c r="L46" s="63"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="62"/>
-      <c r="B47" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="D47" s="45"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="45"/>
-      <c r="K47" s="45"/>
-      <c r="L47" s="63"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="62"/>
-      <c r="B48" s="68" t="s">
-        <v>23</v>
-      </c>
-      <c r="C48" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="D48" s="45"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="63"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="62"/>
-      <c r="B49" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="C49" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" s="45"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="45"/>
-      <c r="K49" s="45"/>
-      <c r="L49" s="63"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="62"/>
-      <c r="B50" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="45" t="s">
+      <c r="C50" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="45"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="63"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="62"/>
-      <c r="B51" s="69" t="s">
-        <v>21</v>
-      </c>
-      <c r="C51" s="63" t="s">
-        <v>30</v>
-      </c>
-      <c r="D51" s="63"/>
-      <c r="E51" s="63"/>
-      <c r="F51" s="63"/>
-      <c r="G51" s="63"/>
-      <c r="H51" s="63"/>
-      <c r="I51" s="63"/>
-      <c r="J51" s="63"/>
-      <c r="K51" s="63"/>
-      <c r="L51" s="63"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="62"/>
-      <c r="B52" s="63"/>
-      <c r="C52" s="63"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="63"/>
-      <c r="F52" s="63"/>
-      <c r="G52" s="63"/>
-      <c r="H52" s="63"/>
-      <c r="I52" s="63"/>
-      <c r="J52" s="63"/>
-      <c r="K52" s="63"/>
-      <c r="L52" s="63"/>
+      <c r="A51" s="53"/>
+      <c r="B51" s="54"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="54"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="54"/>
+      <c r="H51" s="54"/>
+      <c r="I51" s="54"/>
+      <c r="J51" s="54"/>
+      <c r="K51" s="54"/>
+      <c r="L51" s="54"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="23">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:P1"/>
@@ -2635,23 +2482,22 @@
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="P13:R13"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="F41:J41"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:J40"/>
+    <mergeCell ref="C44:K44"/>
     <mergeCell ref="C45:K45"/>
     <mergeCell ref="C46:K46"/>
     <mergeCell ref="C47:K47"/>
     <mergeCell ref="C48:K48"/>
     <mergeCell ref="C49:K49"/>
-    <mergeCell ref="C50:K50"/>
   </mergeCells>
-  <conditionalFormatting sqref="AD1:AO3 AK4:AL4 AN4:AO4 AD5:AO5 R6:Y6 AK6:AO8 AD7:AH7 AD6:AH6 AJ6:AJ7 AD8:AI8 AD4:AH4 R2:AC5 R7:AC8 R1:AA5 AB1:AC1">
+  <conditionalFormatting sqref="R1:BL7">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>IF(WEEKDAY(R$1,2)=6,1,IF(WEEKDAY(R$1,2)=7,1,0))</formula>
     </cfRule>
@@ -2663,6 +2509,5 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Übungen/02_Netzplan_Firmennetzwerk.xlsx
+++ b/Übungen/02_Netzplan_Firmennetzwerk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Netzplan" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Netzplan!$A$1:$X$30</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Netzplan!$A$1:$X$32</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="32">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -40,6 +40,9 @@
     <t xml:space="preserve">D</t>
   </si>
   <si>
+    <t xml:space="preserve">Projektstart</t>
+  </si>
+  <si>
     <t xml:space="preserve">A</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
   </si>
   <si>
     <t xml:space="preserve">Domaincontroller einrichten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netzwerkinfrastruktur</t>
   </si>
   <si>
     <t xml:space="preserve">Clients in Domain einbinden</t>
@@ -124,7 +130,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -169,6 +175,14 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC9211E"/>
+      <name val="Alegreya Sans"/>
+      <family val="3"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="9"/>
       <name val="Alegreya Sans"/>
       <family val="3"/>
@@ -188,7 +202,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,6 +225,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF999999"/>
         <bgColor rgb="FFB2B2B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFC9211E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8000"/>
+        <bgColor rgb="FFFF6600"/>
       </patternFill>
     </fill>
     <fill>
@@ -388,7 +414,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="74">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -433,6 +459,26 @@
       <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="75" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -465,6 +511,18 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -474,10 +532,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -493,6 +547,22 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -513,15 +583,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -537,6 +607,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -545,31 +619,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -581,6 +655,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -601,35 +679,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -703,7 +781,7 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF8000"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF999999"/>
@@ -720,13 +798,219 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>18360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>505440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>123120</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>139320</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="0" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4617000" y="505440"/>
+          <a:ext cx="104760" cy="144720"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>54000</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>8280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>158760</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>153000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9531720" y="1362600"/>
+          <a:ext cx="104760" cy="144720"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>35280</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>169560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>140040</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>144360</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10324800" y="1694160"/>
+          <a:ext cx="104760" cy="144720"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="21600" h="21600">
+              <a:moveTo>
+                <a:pt x="10800" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="21600" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="21600"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="0" y="10800"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="10800" y="0"/>
+              </a:lnTo>
+              <a:close/>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="729fcf"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="3465a4"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BN51"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BN53"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="2" width="3.83"/>
@@ -909,554 +1193,617 @@
       <c r="BM1" s="9"/>
       <c r="BN1" s="10"/>
     </row>
-    <row r="2" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
+      <c r="AD2" s="12"/>
+      <c r="AE2" s="12"/>
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="12"/>
+      <c r="AH2" s="12"/>
+      <c r="AI2" s="12"/>
+      <c r="AJ2" s="12"/>
+      <c r="AK2" s="12"/>
+      <c r="AL2" s="12"/>
+      <c r="AM2" s="12"/>
+      <c r="AN2" s="12"/>
+      <c r="AO2" s="12"/>
+      <c r="AP2" s="12"/>
+      <c r="AQ2" s="12"/>
+      <c r="AR2" s="12"/>
+      <c r="AS2" s="12"/>
+      <c r="AT2" s="12"/>
+      <c r="AU2" s="12"/>
+      <c r="AV2" s="12"/>
+      <c r="AW2" s="12"/>
+      <c r="AX2" s="12"/>
+      <c r="AY2" s="12"/>
+      <c r="AZ2" s="12"/>
+      <c r="BA2" s="12"/>
+      <c r="BB2" s="12"/>
+      <c r="BC2" s="12"/>
+      <c r="BD2" s="12"/>
+      <c r="BE2" s="12"/>
+      <c r="BF2" s="12"/>
+      <c r="BG2" s="12"/>
+      <c r="BH2" s="12"/>
+      <c r="BI2" s="12"/>
+      <c r="BJ2" s="12"/>
+      <c r="BK2" s="12"/>
+      <c r="BL2" s="12"/>
+      <c r="BM2" s="13"/>
+      <c r="BN2" s="14"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="N3" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="18" t="n">
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="R2" s="19"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="19"/>
-      <c r="X2" s="19"/>
-      <c r="Y2" s="19"/>
-      <c r="Z2" s="19"/>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19"/>
-      <c r="AE2" s="19"/>
-      <c r="AF2" s="19"/>
-      <c r="AG2" s="19"/>
-      <c r="AH2" s="19"/>
-      <c r="AI2" s="19"/>
-      <c r="AJ2" s="19"/>
-      <c r="AK2" s="19"/>
-      <c r="AL2" s="19"/>
-      <c r="AM2" s="20"/>
-      <c r="AN2" s="20"/>
-      <c r="AO2" s="20"/>
-      <c r="AP2" s="20"/>
-      <c r="AQ2" s="20"/>
-      <c r="AR2" s="20"/>
-      <c r="AS2" s="20"/>
-      <c r="AT2" s="20"/>
-      <c r="AU2" s="20"/>
-      <c r="AV2" s="20"/>
-      <c r="AW2" s="20"/>
-      <c r="AX2" s="20"/>
-      <c r="AY2" s="20"/>
-      <c r="AZ2" s="20"/>
-      <c r="BA2" s="20"/>
-      <c r="BB2" s="20"/>
-      <c r="BC2" s="20"/>
-      <c r="BD2" s="20"/>
-      <c r="BE2" s="20"/>
-      <c r="BF2" s="20"/>
-      <c r="BG2" s="20"/>
-      <c r="BH2" s="20"/>
-      <c r="BI2" s="20"/>
-      <c r="BJ2" s="20"/>
-      <c r="BK2" s="20"/>
-      <c r="BL2" s="20"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="24" t="s">
+      <c r="R3" s="24"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="26"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+      <c r="AE3" s="27"/>
+      <c r="AF3" s="27"/>
+      <c r="AG3" s="27"/>
+      <c r="AH3" s="27"/>
+      <c r="AI3" s="27"/>
+      <c r="AJ3" s="27"/>
+      <c r="AK3" s="27"/>
+      <c r="AL3" s="27"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" s="19"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="19"/>
-      <c r="X3" s="19"/>
-      <c r="Y3" s="19"/>
-      <c r="Z3" s="19"/>
-      <c r="AA3" s="19"/>
-      <c r="AB3" s="19"/>
-      <c r="AC3" s="19"/>
-      <c r="AD3" s="19"/>
-      <c r="AE3" s="19"/>
-      <c r="AF3" s="19"/>
-      <c r="AG3" s="19"/>
-      <c r="AH3" s="19"/>
-      <c r="AI3" s="19"/>
-      <c r="AJ3" s="19"/>
-      <c r="AK3" s="19"/>
-      <c r="AL3" s="19"/>
-      <c r="AM3" s="20"/>
-      <c r="AN3" s="20"/>
-      <c r="AO3" s="20"/>
-      <c r="AP3" s="20"/>
-      <c r="AQ3" s="20"/>
-      <c r="AR3" s="20"/>
-      <c r="AS3" s="20"/>
-      <c r="AT3" s="20"/>
-      <c r="AU3" s="20"/>
-      <c r="AV3" s="20"/>
-      <c r="AW3" s="20"/>
-      <c r="AX3" s="20"/>
-      <c r="AY3" s="20"/>
-      <c r="AZ3" s="20"/>
-      <c r="BA3" s="20"/>
-      <c r="BB3" s="20"/>
-      <c r="BC3" s="20"/>
-      <c r="BD3" s="20"/>
-      <c r="BE3" s="20"/>
-      <c r="BF3" s="20"/>
-      <c r="BG3" s="20"/>
-      <c r="BH3" s="20"/>
-      <c r="BI3" s="20"/>
-      <c r="BJ3" s="20"/>
-      <c r="BK3" s="20"/>
-      <c r="BL3" s="20"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="24" t="s">
-        <v>5</v>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="31" t="s">
+        <v>6</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="24" t="s">
-        <v>10</v>
+      <c r="L4" s="32"/>
+      <c r="M4" s="31" t="s">
+        <v>11</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25" t="n">
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" s="27"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="34"/>
+      <c r="AB4" s="34"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
+      <c r="AI4" s="27"/>
+      <c r="AJ4" s="27"/>
+      <c r="AK4" s="27"/>
+      <c r="AL4" s="27"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
+      <c r="BJ4" s="28"/>
+      <c r="BK4" s="28"/>
+      <c r="BL4" s="28"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="31" t="s">
         <v>6</v>
-      </c>
-      <c r="R4" s="19"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="19"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="19"/>
-      <c r="AB4" s="19"/>
-      <c r="AC4" s="19"/>
-      <c r="AD4" s="19"/>
-      <c r="AE4" s="19"/>
-      <c r="AF4" s="19"/>
-      <c r="AG4" s="19"/>
-      <c r="AH4" s="19"/>
-      <c r="AI4" s="19"/>
-      <c r="AJ4" s="19"/>
-      <c r="AK4" s="19"/>
-      <c r="AL4" s="19"/>
-      <c r="AM4" s="20"/>
-      <c r="AN4" s="20"/>
-      <c r="AO4" s="20"/>
-      <c r="AP4" s="20"/>
-      <c r="AQ4" s="20"/>
-      <c r="AR4" s="20"/>
-      <c r="AS4" s="20"/>
-      <c r="AT4" s="20"/>
-      <c r="AU4" s="20"/>
-      <c r="AV4" s="20"/>
-      <c r="AW4" s="20"/>
-      <c r="AX4" s="20"/>
-      <c r="AY4" s="20"/>
-      <c r="AZ4" s="20"/>
-      <c r="BA4" s="20"/>
-      <c r="BB4" s="20"/>
-      <c r="BC4" s="20"/>
-      <c r="BD4" s="20"/>
-      <c r="BE4" s="20"/>
-      <c r="BF4" s="20"/>
-      <c r="BG4" s="20"/>
-      <c r="BH4" s="20"/>
-      <c r="BI4" s="20"/>
-      <c r="BJ4" s="20"/>
-      <c r="BK4" s="20"/>
-      <c r="BL4" s="20"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="24" t="s">
-        <v>5</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="24" t="s">
-        <v>10</v>
+      <c r="L5" s="32"/>
+      <c r="M5" s="31" t="s">
+        <v>11</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" s="19"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="19"/>
-      <c r="Y5" s="19"/>
-      <c r="Z5" s="19"/>
-      <c r="AA5" s="19"/>
-      <c r="AB5" s="19"/>
-      <c r="AC5" s="19"/>
-      <c r="AD5" s="19"/>
-      <c r="AE5" s="19"/>
-      <c r="AF5" s="19"/>
-      <c r="AG5" s="19"/>
-      <c r="AH5" s="19"/>
-      <c r="AI5" s="19"/>
-      <c r="AJ5" s="19"/>
-      <c r="AK5" s="19"/>
-      <c r="AL5" s="19"/>
-      <c r="AM5" s="20"/>
-      <c r="AN5" s="20"/>
-      <c r="AO5" s="20"/>
-      <c r="AP5" s="20"/>
-      <c r="AQ5" s="20"/>
-      <c r="AR5" s="20"/>
-      <c r="AS5" s="20"/>
-      <c r="AT5" s="20"/>
-      <c r="AU5" s="20"/>
-      <c r="AV5" s="20"/>
-      <c r="AW5" s="20"/>
-      <c r="AX5" s="20"/>
-      <c r="AY5" s="20"/>
-      <c r="AZ5" s="20"/>
-      <c r="BA5" s="20"/>
-      <c r="BB5" s="20"/>
-      <c r="BC5" s="20"/>
-      <c r="BD5" s="20"/>
-      <c r="BE5" s="20"/>
-      <c r="BF5" s="20"/>
-      <c r="BG5" s="20"/>
-      <c r="BH5" s="20"/>
-      <c r="BI5" s="20"/>
-      <c r="BJ5" s="20"/>
-      <c r="BK5" s="20"/>
-      <c r="BL5" s="20"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="R5" s="27"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="26"/>
+      <c r="AB5" s="26"/>
+      <c r="AC5" s="26"/>
+      <c r="AD5" s="27"/>
+      <c r="AE5" s="27"/>
+      <c r="AF5" s="26"/>
+      <c r="AG5" s="26"/>
+      <c r="AH5" s="26"/>
+      <c r="AI5" s="27"/>
+      <c r="AJ5" s="27"/>
+      <c r="AK5" s="27"/>
+      <c r="AL5" s="27"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="28"/>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28"/>
     </row>
     <row r="6" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="23" t="s">
+      <c r="A6" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="25"/>
-      <c r="M6" s="24" t="s">
-        <v>14</v>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="31" t="s">
+        <v>11</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="19"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="21"/>
-      <c r="V6" s="21"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="19"/>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="19"/>
-      <c r="AE6" s="19"/>
-      <c r="AF6" s="19"/>
-      <c r="AG6" s="19"/>
-      <c r="AH6" s="19"/>
-      <c r="AI6" s="19"/>
-      <c r="AJ6" s="19"/>
-      <c r="AK6" s="19"/>
-      <c r="AL6" s="19"/>
-      <c r="AM6" s="20"/>
-      <c r="AN6" s="20"/>
-      <c r="AO6" s="20"/>
-      <c r="AP6" s="20"/>
-      <c r="AQ6" s="20"/>
-      <c r="AR6" s="20"/>
-      <c r="AS6" s="20"/>
-      <c r="AT6" s="20"/>
-      <c r="AU6" s="20"/>
-      <c r="AV6" s="20"/>
-      <c r="AW6" s="20"/>
-      <c r="AX6" s="20"/>
-      <c r="AY6" s="20"/>
-      <c r="AZ6" s="20"/>
-      <c r="BA6" s="20"/>
-      <c r="BB6" s="20"/>
-      <c r="BC6" s="20"/>
-      <c r="BD6" s="20"/>
-      <c r="BE6" s="20"/>
-      <c r="BF6" s="20"/>
-      <c r="BG6" s="20"/>
-      <c r="BH6" s="20"/>
-      <c r="BI6" s="20"/>
-      <c r="BJ6" s="20"/>
-      <c r="BK6" s="20"/>
-      <c r="BL6" s="20"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" s="27"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="33"/>
+      <c r="V6" s="33"/>
+      <c r="W6" s="27"/>
+      <c r="X6" s="27"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="34"/>
+      <c r="AB6" s="34"/>
+      <c r="AC6" s="34"/>
+      <c r="AD6" s="27"/>
+      <c r="AE6" s="27"/>
+      <c r="AF6" s="27"/>
+      <c r="AG6" s="27"/>
+      <c r="AH6" s="27"/>
+      <c r="AI6" s="27"/>
+      <c r="AJ6" s="27"/>
+      <c r="AK6" s="27"/>
+      <c r="AL6" s="27"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="28"/>
+      <c r="AR6" s="28"/>
+      <c r="AS6" s="28"/>
+      <c r="AT6" s="28"/>
+      <c r="AU6" s="28"/>
+      <c r="AV6" s="28"/>
+      <c r="AW6" s="28"/>
+      <c r="AX6" s="28"/>
+      <c r="AY6" s="28"/>
+      <c r="AZ6" s="28"/>
+      <c r="BA6" s="28"/>
+      <c r="BB6" s="28"/>
+      <c r="BC6" s="28"/>
+      <c r="BD6" s="28"/>
+      <c r="BE6" s="28"/>
+      <c r="BF6" s="28"/>
+      <c r="BG6" s="28"/>
+      <c r="BH6" s="28"/>
+      <c r="BI6" s="28"/>
+      <c r="BJ6" s="28"/>
+      <c r="BK6" s="28"/>
+      <c r="BL6" s="28"/>
     </row>
     <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="28" t="s">
-        <v>10</v>
-      </c>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
       <c r="J7" s="29"/>
       <c r="K7" s="29"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="30" t="n">
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="33"/>
+      <c r="U7" s="33"/>
+      <c r="V7" s="33"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="27"/>
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="35"/>
+      <c r="AA7" s="36"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="27"/>
+      <c r="AE7" s="27"/>
+      <c r="AF7" s="27"/>
+      <c r="AG7" s="27"/>
+      <c r="AH7" s="27"/>
+      <c r="AI7" s="27"/>
+      <c r="AJ7" s="27"/>
+      <c r="AK7" s="27"/>
+      <c r="AL7" s="27"/>
+      <c r="AM7" s="28"/>
+      <c r="AN7" s="28"/>
+      <c r="AO7" s="28"/>
+      <c r="AP7" s="28"/>
+      <c r="AQ7" s="28"/>
+      <c r="AR7" s="28"/>
+      <c r="AS7" s="28"/>
+      <c r="AT7" s="28"/>
+      <c r="AU7" s="28"/>
+      <c r="AV7" s="28"/>
+      <c r="AW7" s="28"/>
+      <c r="AX7" s="28"/>
+      <c r="AY7" s="28"/>
+      <c r="AZ7" s="28"/>
+      <c r="BA7" s="28"/>
+      <c r="BB7" s="28"/>
+      <c r="BC7" s="28"/>
+      <c r="BD7" s="28"/>
+      <c r="BE7" s="28"/>
+      <c r="BF7" s="28"/>
+      <c r="BG7" s="28"/>
+      <c r="BH7" s="28"/>
+      <c r="BI7" s="28"/>
+      <c r="BJ7" s="28"/>
+      <c r="BK7" s="28"/>
+      <c r="BL7" s="28"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="32"/>
+      <c r="M8" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="34"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="36"/>
-      <c r="V7" s="36"/>
-      <c r="W7" s="34"/>
-      <c r="X7" s="34"/>
-      <c r="Y7" s="34"/>
-      <c r="Z7" s="34"/>
-      <c r="AA7" s="34"/>
-      <c r="AB7" s="34"/>
-      <c r="AC7" s="34"/>
-      <c r="AD7" s="34"/>
-      <c r="AE7" s="34"/>
-      <c r="AF7" s="34"/>
-      <c r="AG7" s="34"/>
-      <c r="AH7" s="34"/>
-      <c r="AI7" s="34"/>
-      <c r="AJ7" s="34"/>
-      <c r="AK7" s="34"/>
-      <c r="AL7" s="34"/>
-      <c r="AM7" s="35"/>
-      <c r="AN7" s="35"/>
-      <c r="AO7" s="35"/>
-      <c r="AP7" s="35"/>
-      <c r="AQ7" s="35"/>
-      <c r="AR7" s="35"/>
-      <c r="AS7" s="35"/>
-      <c r="AT7" s="35"/>
-      <c r="AU7" s="35"/>
-      <c r="AV7" s="35"/>
-      <c r="AW7" s="35"/>
-      <c r="AX7" s="35"/>
-      <c r="AY7" s="35"/>
-      <c r="AZ7" s="35"/>
-      <c r="BA7" s="35"/>
-      <c r="BB7" s="35"/>
-      <c r="BC7" s="35"/>
-      <c r="BD7" s="35"/>
-      <c r="BE7" s="35"/>
-      <c r="BF7" s="35"/>
-      <c r="BG7" s="35"/>
-      <c r="BH7" s="35"/>
-      <c r="BI7" s="35"/>
-      <c r="BJ7" s="35"/>
-      <c r="BK7" s="35"/>
-      <c r="BL7" s="35"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="T8" s="2"/>
-      <c r="W8" s="0"/>
-      <c r="X8" s="0"/>
-      <c r="Y8" s="0"/>
-      <c r="Z8" s="0"/>
-      <c r="AA8" s="0"/>
-      <c r="AB8" s="0"/>
-      <c r="AC8" s="0"/>
-      <c r="AD8" s="0"/>
-      <c r="AE8" s="0"/>
-      <c r="AF8" s="0"/>
-      <c r="AG8" s="0"/>
-      <c r="AH8" s="0"/>
+      <c r="R8" s="27"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="27"/>
+      <c r="X8" s="27"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27"/>
+      <c r="AA8" s="27"/>
+      <c r="AB8" s="27"/>
+      <c r="AC8" s="27"/>
+      <c r="AD8" s="27"/>
+      <c r="AE8" s="27"/>
+      <c r="AF8" s="27"/>
+      <c r="AG8" s="27"/>
+      <c r="AH8" s="27"/>
       <c r="AI8" s="0"/>
-      <c r="AJ8" s="0"/>
-      <c r="AK8" s="0"/>
-      <c r="AL8" s="0"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="37"/>
-      <c r="D9" s="0"/>
-      <c r="E9" s="0"/>
-      <c r="F9" s="0"/>
-      <c r="G9" s="0"/>
-      <c r="H9" s="0"/>
-      <c r="I9" s="0"/>
-      <c r="J9" s="0"/>
-      <c r="K9" s="0"/>
-      <c r="L9" s="0"/>
-      <c r="M9" s="0"/>
-      <c r="N9" s="0"/>
-      <c r="O9" s="0"/>
-      <c r="P9" s="0"/>
-      <c r="Q9" s="0"/>
-      <c r="R9" s="0"/>
-      <c r="S9" s="0"/>
-      <c r="T9" s="0"/>
-      <c r="U9" s="0"/>
-      <c r="V9" s="0"/>
-      <c r="W9" s="0"/>
-      <c r="X9" s="0"/>
-      <c r="Y9" s="0"/>
-      <c r="Z9" s="0"/>
-      <c r="AA9" s="0"/>
-      <c r="AB9" s="0"/>
-      <c r="AC9" s="0"/>
-      <c r="AD9" s="0"/>
-      <c r="AE9" s="0"/>
-      <c r="AF9" s="0"/>
-      <c r="AG9" s="0"/>
-      <c r="AH9" s="0"/>
-      <c r="AI9" s="0"/>
+      <c r="AJ8" s="24"/>
+      <c r="AK8" s="27"/>
+      <c r="AL8" s="27"/>
+      <c r="AM8" s="28"/>
+      <c r="AN8" s="28"/>
+      <c r="AO8" s="28"/>
+      <c r="AP8" s="28"/>
+      <c r="AQ8" s="28"/>
+      <c r="AR8" s="28"/>
+      <c r="AS8" s="28"/>
+      <c r="AT8" s="28"/>
+      <c r="AU8" s="28"/>
+      <c r="AV8" s="28"/>
+      <c r="AW8" s="28"/>
+      <c r="AX8" s="28"/>
+      <c r="AY8" s="28"/>
+      <c r="AZ8" s="28"/>
+      <c r="BA8" s="28"/>
+      <c r="BB8" s="28"/>
+      <c r="BC8" s="28"/>
+      <c r="BD8" s="28"/>
+      <c r="BE8" s="28"/>
+      <c r="BF8" s="28"/>
+      <c r="BG8" s="28"/>
+      <c r="BH8" s="28"/>
+      <c r="BI8" s="28"/>
+      <c r="BJ8" s="28"/>
+      <c r="BK8" s="28"/>
+      <c r="BL8" s="28"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" s="45"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="47"/>
+      <c r="U9" s="47"/>
+      <c r="V9" s="47"/>
+      <c r="W9" s="45"/>
+      <c r="X9" s="45"/>
+      <c r="Y9" s="45"/>
+      <c r="Z9" s="45"/>
+      <c r="AA9" s="45"/>
+      <c r="AB9" s="45"/>
+      <c r="AC9" s="45"/>
+      <c r="AD9" s="45"/>
+      <c r="AE9" s="45"/>
+      <c r="AF9" s="45"/>
+      <c r="AG9" s="45"/>
+      <c r="AH9" s="45"/>
+      <c r="AI9" s="45"/>
       <c r="AJ9" s="0"/>
-      <c r="AK9" s="0"/>
-      <c r="AL9" s="0"/>
+      <c r="AK9" s="45"/>
+      <c r="AL9" s="45"/>
+      <c r="AM9" s="48"/>
+      <c r="AN9" s="46"/>
+      <c r="AO9" s="46"/>
+      <c r="AP9" s="46"/>
+      <c r="AQ9" s="46"/>
+      <c r="AR9" s="46"/>
+      <c r="AS9" s="46"/>
+      <c r="AT9" s="46"/>
+      <c r="AU9" s="46"/>
+      <c r="AV9" s="46"/>
+      <c r="AW9" s="46"/>
+      <c r="AX9" s="46"/>
+      <c r="AY9" s="46"/>
+      <c r="AZ9" s="46"/>
+      <c r="BA9" s="46"/>
+      <c r="BB9" s="46"/>
+      <c r="BC9" s="46"/>
+      <c r="BD9" s="46"/>
+      <c r="BE9" s="46"/>
+      <c r="BF9" s="46"/>
+      <c r="BG9" s="46"/>
+      <c r="BH9" s="46"/>
+      <c r="BI9" s="46"/>
+      <c r="BJ9" s="46"/>
+      <c r="BK9" s="46"/>
+      <c r="BL9" s="46"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="0"/>
-      <c r="E10" s="0"/>
-      <c r="F10" s="0"/>
-      <c r="G10" s="0"/>
-      <c r="H10" s="0"/>
-      <c r="I10" s="0"/>
-      <c r="J10" s="0"/>
-      <c r="K10" s="0"/>
-      <c r="L10" s="0"/>
-      <c r="M10" s="0"/>
-      <c r="N10" s="0"/>
-      <c r="O10" s="0"/>
-      <c r="P10" s="0"/>
-      <c r="Q10" s="0"/>
-      <c r="R10" s="0"/>
-      <c r="S10" s="0"/>
-      <c r="T10" s="0"/>
-      <c r="U10" s="0"/>
-      <c r="V10" s="0"/>
+      <c r="B10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="50"/>
+      <c r="T10" s="2"/>
       <c r="W10" s="0"/>
       <c r="X10" s="0"/>
       <c r="Y10" s="0"/>
@@ -1475,47 +1822,22 @@
       <c r="AL10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="41" t="n">
-        <f aca="false">A11+A13</f>
-        <v>7</v>
-      </c>
+      <c r="B11" s="49"/>
       <c r="D11" s="0"/>
       <c r="E11" s="0"/>
-      <c r="F11" s="39" t="n">
-        <f aca="false">C11</f>
-        <v>7</v>
-      </c>
-      <c r="G11" s="40"/>
-      <c r="H11" s="41" t="n">
-        <f aca="false">F11+F13</f>
-        <v>10</v>
-      </c>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
       <c r="I11" s="0"/>
       <c r="J11" s="0"/>
-      <c r="K11" s="39" t="n">
-        <f aca="false">MAX(H11,H17,H23)</f>
-        <v>13</v>
-      </c>
-      <c r="L11" s="40"/>
-      <c r="M11" s="41" t="n">
-        <f aca="false">K11+K13</f>
-        <v>14</v>
-      </c>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
       <c r="N11" s="0"/>
       <c r="O11" s="0"/>
-      <c r="P11" s="39" t="n">
-        <f aca="false">M11</f>
-        <v>14</v>
-      </c>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="41" t="n">
-        <f aca="false">P11+P13</f>
-        <v>15</v>
-      </c>
+      <c r="P11" s="0"/>
+      <c r="Q11" s="0"/>
+      <c r="R11" s="0"/>
       <c r="S11" s="0"/>
       <c r="T11" s="0"/>
       <c r="U11" s="0"/>
@@ -1538,32 +1860,21 @@
       <c r="AL11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
       <c r="D12" s="0"/>
       <c r="E12" s="0"/>
-      <c r="F12" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
+      <c r="F12" s="0"/>
+      <c r="G12" s="0"/>
+      <c r="H12" s="0"/>
       <c r="I12" s="0"/>
       <c r="J12" s="0"/>
-      <c r="K12" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
+      <c r="K12" s="0"/>
+      <c r="L12" s="0"/>
+      <c r="M12" s="0"/>
       <c r="N12" s="0"/>
       <c r="O12" s="0"/>
-      <c r="P12" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
+      <c r="P12" s="0"/>
+      <c r="Q12" s="0"/>
+      <c r="R12" s="0"/>
       <c r="S12" s="0"/>
       <c r="T12" s="0"/>
       <c r="U12" s="0"/>
@@ -1585,48 +1896,48 @@
       <c r="AK12" s="0"/>
       <c r="AL12" s="0"/>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="43" t="n">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" s="52"/>
+      <c r="C13" s="53" t="n">
+        <f aca="false">A13+A15</f>
         <v>7</v>
       </c>
-      <c r="B13" s="44" t="n">
-        <f aca="false">C14-C11</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="43" t="n">
-        <f aca="false">Q3</f>
-        <v>3</v>
-      </c>
-      <c r="G13" s="44" t="n">
-        <f aca="false">H14-H11</f>
-        <v>3</v>
-      </c>
-      <c r="H13" s="45"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="43" t="n">
-        <f aca="false">Q6</f>
-        <v>1</v>
-      </c>
-      <c r="L13" s="44" t="n">
-        <f aca="false">M14-M11</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="45"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="43" t="n">
-        <f aca="false">Q7</f>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="44" t="n">
-        <f aca="false">R14-R11</f>
-        <v>0</v>
-      </c>
-      <c r="R13" s="45"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="51" t="n">
+        <f aca="false">C13</f>
+        <v>7</v>
+      </c>
+      <c r="G13" s="52"/>
+      <c r="H13" s="53" t="n">
+        <f aca="false">F13+F15</f>
+        <v>10</v>
+      </c>
+      <c r="I13" s="0"/>
+      <c r="J13" s="0"/>
+      <c r="K13" s="51" t="n">
+        <f aca="false">MAX(H13,H19,H25)</f>
+        <v>13</v>
+      </c>
+      <c r="L13" s="52"/>
+      <c r="M13" s="53" t="n">
+        <f aca="false">K13+K15</f>
+        <v>14</v>
+      </c>
+      <c r="N13" s="0"/>
+      <c r="O13" s="0"/>
+      <c r="P13" s="51" t="n">
+        <f aca="false">M13</f>
+        <v>14</v>
+      </c>
+      <c r="Q13" s="52"/>
+      <c r="R13" s="53" t="n">
+        <f aca="false">P13+P15</f>
+        <v>15</v>
+      </c>
       <c r="S13" s="0"/>
       <c r="T13" s="0"/>
       <c r="U13" s="0"/>
@@ -1649,48 +1960,32 @@
       <c r="AL13" s="0"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49" t="n">
-        <f aca="false">C14-A13</f>
-        <v>0</v>
-      </c>
-      <c r="B14" s="37"/>
-      <c r="C14" s="50" t="n">
-        <f aca="false">MIN(F26,F20,F14)</f>
-        <v>7</v>
-      </c>
-      <c r="D14" s="51"/>
+      <c r="A14" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="0"/>
       <c r="E14" s="0"/>
-      <c r="F14" s="49" t="n">
-        <f aca="false">H14-F13</f>
-        <v>10</v>
-      </c>
-      <c r="G14" s="37"/>
-      <c r="H14" s="50" t="n">
-        <f aca="false">K14</f>
-        <v>13</v>
-      </c>
+      <c r="F14" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="54"/>
+      <c r="H14" s="54"/>
       <c r="I14" s="0"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="49" t="n">
-        <f aca="false">M14-K13</f>
-        <v>13</v>
-      </c>
-      <c r="L14" s="37"/>
-      <c r="M14" s="50" t="n">
-        <f aca="false">P14</f>
-        <v>14</v>
-      </c>
+      <c r="J14" s="0"/>
+      <c r="K14" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" s="54"/>
+      <c r="M14" s="54"/>
       <c r="N14" s="0"/>
       <c r="O14" s="0"/>
-      <c r="P14" s="49" t="n">
-        <f aca="false">R14-P13</f>
-        <v>14</v>
-      </c>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="50" t="n">
-        <f aca="false">R11</f>
-        <v>15</v>
-      </c>
+      <c r="P14" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="54"/>
       <c r="S14" s="0"/>
       <c r="T14" s="0"/>
       <c r="U14" s="0"/>
@@ -1712,22 +2007,48 @@
       <c r="AK14" s="0"/>
       <c r="AL14" s="0"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="51"/>
-      <c r="E15" s="0"/>
-      <c r="F15" s="0"/>
-      <c r="G15" s="0"/>
-      <c r="H15" s="0"/>
-      <c r="I15" s="0"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="0"/>
-      <c r="L15" s="0"/>
-      <c r="M15" s="0"/>
-      <c r="N15" s="0"/>
-      <c r="O15" s="0"/>
-      <c r="P15" s="0"/>
-      <c r="Q15" s="0"/>
-      <c r="R15" s="0"/>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="56" t="n">
+        <f aca="false">C16-C13</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="57"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="55" t="n">
+        <f aca="false">Q4</f>
+        <v>3</v>
+      </c>
+      <c r="G15" s="60" t="n">
+        <f aca="false">H16-H13</f>
+        <v>3</v>
+      </c>
+      <c r="H15" s="57"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="55" t="n">
+        <f aca="false">Q8</f>
+        <v>1</v>
+      </c>
+      <c r="L15" s="56" t="n">
+        <f aca="false">M16-M13</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="57"/>
+      <c r="N15" s="59"/>
+      <c r="O15" s="59"/>
+      <c r="P15" s="55" t="n">
+        <f aca="false">Q9</f>
+        <v>1</v>
+      </c>
+      <c r="Q15" s="56" t="n">
+        <f aca="false">R16-R13</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="57"/>
       <c r="S15" s="0"/>
       <c r="T15" s="0"/>
       <c r="U15" s="0"/>
@@ -1750,21 +2071,48 @@
       <c r="AL15" s="0"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="51"/>
+      <c r="A16" s="62" t="n">
+        <f aca="false">C16-A15</f>
+        <v>0</v>
+      </c>
+      <c r="B16" s="49"/>
+      <c r="C16" s="63" t="n">
+        <f aca="false">MIN(F28,F22,F16)</f>
+        <v>7</v>
+      </c>
+      <c r="D16" s="64"/>
       <c r="E16" s="0"/>
-      <c r="F16" s="0"/>
-      <c r="G16" s="0"/>
-      <c r="H16" s="0"/>
+      <c r="F16" s="62" t="n">
+        <f aca="false">H16-F15</f>
+        <v>10</v>
+      </c>
+      <c r="G16" s="49"/>
+      <c r="H16" s="63" t="n">
+        <f aca="false">K16</f>
+        <v>13</v>
+      </c>
       <c r="I16" s="0"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="0"/>
-      <c r="L16" s="0"/>
-      <c r="M16" s="0"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="62" t="n">
+        <f aca="false">M16-K15</f>
+        <v>13</v>
+      </c>
+      <c r="L16" s="49"/>
+      <c r="M16" s="63" t="n">
+        <f aca="false">P16</f>
+        <v>14</v>
+      </c>
       <c r="N16" s="0"/>
       <c r="O16" s="0"/>
-      <c r="P16" s="0"/>
-      <c r="Q16" s="0"/>
-      <c r="R16" s="0"/>
+      <c r="P16" s="62" t="n">
+        <f aca="false">R16-P15</f>
+        <v>14</v>
+      </c>
+      <c r="Q16" s="49"/>
+      <c r="R16" s="63" t="n">
+        <f aca="false">R13</f>
+        <v>15</v>
+      </c>
       <c r="S16" s="0"/>
       <c r="T16" s="0"/>
       <c r="U16" s="0"/>
@@ -1787,19 +2135,13 @@
       <c r="AL16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="51"/>
+      <c r="D17" s="64"/>
       <c r="E17" s="0"/>
-      <c r="F17" s="39" t="n">
-        <f aca="false">C11</f>
-        <v>7</v>
-      </c>
-      <c r="G17" s="40"/>
-      <c r="H17" s="41" t="n">
-        <f aca="false">F17+F19</f>
-        <v>13</v>
-      </c>
+      <c r="F17" s="0"/>
+      <c r="G17" s="0"/>
+      <c r="H17" s="0"/>
       <c r="I17" s="0"/>
-      <c r="J17" s="52"/>
+      <c r="J17" s="65"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0"/>
       <c r="M17" s="0"/>
@@ -1830,15 +2172,13 @@
       <c r="AL17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="51"/>
+      <c r="D18" s="64"/>
       <c r="E18" s="0"/>
-      <c r="F18" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
+      <c r="F18" s="0"/>
+      <c r="G18" s="0"/>
+      <c r="H18" s="0"/>
       <c r="I18" s="0"/>
-      <c r="J18" s="52"/>
+      <c r="J18" s="65"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0"/>
       <c r="M18" s="0"/>
@@ -1848,6 +2188,9 @@
       <c r="Q18" s="0"/>
       <c r="R18" s="0"/>
       <c r="S18" s="0"/>
+      <c r="T18" s="0"/>
+      <c r="U18" s="0"/>
+      <c r="V18" s="0"/>
       <c r="W18" s="0"/>
       <c r="X18" s="0"/>
       <c r="Y18" s="0"/>
@@ -1865,20 +2208,20 @@
       <c r="AK18" s="0"/>
       <c r="AL18" s="0"/>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="51"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="43" t="n">
-        <f aca="false">Q4</f>
-        <v>6</v>
-      </c>
-      <c r="G19" s="44" t="n">
-        <f aca="false">H20-H17</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="45"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="52"/>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D19" s="64"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="51" t="n">
+        <f aca="false">C13</f>
+        <v>7</v>
+      </c>
+      <c r="G19" s="52"/>
+      <c r="H19" s="53" t="n">
+        <f aca="false">F19+F21</f>
+        <v>13</v>
+      </c>
+      <c r="I19" s="0"/>
+      <c r="J19" s="65"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0"/>
       <c r="M19" s="0"/>
@@ -1888,6 +2231,9 @@
       <c r="Q19" s="0"/>
       <c r="R19" s="0"/>
       <c r="S19" s="0"/>
+      <c r="T19" s="0"/>
+      <c r="U19" s="0"/>
+      <c r="V19" s="0"/>
       <c r="W19" s="0"/>
       <c r="X19" s="0"/>
       <c r="Y19" s="0"/>
@@ -1906,19 +2252,15 @@
       <c r="AL19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="51"/>
+      <c r="D20" s="64"/>
       <c r="E20" s="0"/>
-      <c r="F20" s="49" t="n">
-        <f aca="false">H20-F19</f>
-        <v>7</v>
-      </c>
-      <c r="G20" s="37"/>
-      <c r="H20" s="50" t="n">
-        <f aca="false">K14</f>
-        <v>13</v>
-      </c>
+      <c r="F20" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
       <c r="I20" s="0"/>
-      <c r="J20" s="52"/>
+      <c r="J20" s="65"/>
       <c r="K20" s="0"/>
       <c r="L20" s="0"/>
       <c r="M20" s="0"/>
@@ -1945,15 +2287,20 @@
       <c r="AK20" s="0"/>
       <c r="AL20" s="0"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="0"/>
-      <c r="F21" s="0"/>
-      <c r="G21" s="0"/>
-      <c r="H21" s="0"/>
-      <c r="I21" s="0"/>
-      <c r="J21" s="52"/>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D21" s="64"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="55" t="n">
+        <f aca="false">Q5</f>
+        <v>6</v>
+      </c>
+      <c r="G21" s="56" t="n">
+        <f aca="false">H22-H19</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="57"/>
+      <c r="I21" s="59"/>
+      <c r="J21" s="65"/>
       <c r="K21" s="0"/>
       <c r="L21" s="0"/>
       <c r="M21" s="0"/>
@@ -1981,14 +2328,19 @@
       <c r="AL21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="D22" s="51"/>
+      <c r="D22" s="64"/>
       <c r="E22" s="0"/>
-      <c r="F22" s="0"/>
-      <c r="G22" s="0"/>
-      <c r="H22" s="0"/>
+      <c r="F22" s="62" t="n">
+        <f aca="false">H22-F21</f>
+        <v>7</v>
+      </c>
+      <c r="G22" s="49"/>
+      <c r="H22" s="63" t="n">
+        <f aca="false">K16</f>
+        <v>13</v>
+      </c>
       <c r="I22" s="0"/>
-      <c r="J22" s="52"/>
+      <c r="J22" s="65"/>
       <c r="K22" s="0"/>
       <c r="L22" s="0"/>
       <c r="M22" s="0"/>
@@ -2017,19 +2369,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="D23" s="51"/>
+      <c r="D23" s="64"/>
       <c r="E23" s="0"/>
-      <c r="F23" s="39" t="n">
-        <f aca="false">C11</f>
-        <v>7</v>
-      </c>
-      <c r="G23" s="40"/>
-      <c r="H23" s="41" t="n">
-        <f aca="false">F23+F25</f>
-        <v>10</v>
-      </c>
+      <c r="F23" s="0"/>
+      <c r="G23" s="0"/>
+      <c r="H23" s="0"/>
       <c r="I23" s="0"/>
-      <c r="J23" s="52"/>
+      <c r="J23" s="65"/>
       <c r="K23" s="0"/>
       <c r="L23" s="0"/>
       <c r="M23" s="0"/>
@@ -2039,20 +2385,32 @@
       <c r="Q23" s="0"/>
       <c r="R23" s="0"/>
       <c r="S23" s="0"/>
+      <c r="W23" s="0"/>
+      <c r="X23" s="0"/>
+      <c r="Y23" s="0"/>
+      <c r="Z23" s="0"/>
+      <c r="AA23" s="0"/>
+      <c r="AB23" s="0"/>
+      <c r="AC23" s="0"/>
+      <c r="AD23" s="0"/>
+      <c r="AE23" s="0"/>
+      <c r="AF23" s="0"/>
+      <c r="AG23" s="0"/>
+      <c r="AH23" s="0"/>
+      <c r="AI23" s="0"/>
+      <c r="AJ23" s="0"/>
+      <c r="AK23" s="0"/>
+      <c r="AL23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0"/>
-      <c r="B24" s="0"/>
-      <c r="C24" s="0"/>
-      <c r="D24" s="51"/>
+      <c r="A24" s="2"/>
+      <c r="D24" s="64"/>
       <c r="E24" s="0"/>
-      <c r="F24" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
+      <c r="F24" s="0"/>
+      <c r="G24" s="0"/>
+      <c r="H24" s="0"/>
       <c r="I24" s="0"/>
-      <c r="J24" s="52"/>
+      <c r="J24" s="65"/>
       <c r="K24" s="0"/>
       <c r="L24" s="0"/>
       <c r="M24" s="0"/>
@@ -2062,24 +2420,38 @@
       <c r="Q24" s="0"/>
       <c r="R24" s="0"/>
       <c r="S24" s="0"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0"/>
-      <c r="B25" s="0"/>
-      <c r="C25" s="0"/>
-      <c r="D25" s="0"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="43" t="n">
-        <f aca="false">Q5</f>
-        <v>3</v>
-      </c>
-      <c r="G25" s="44" t="n">
-        <f aca="false">H26-H23</f>
-        <v>3</v>
-      </c>
-      <c r="H25" s="45"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="0"/>
+      <c r="W24" s="0"/>
+      <c r="X24" s="0"/>
+      <c r="Y24" s="0"/>
+      <c r="Z24" s="0"/>
+      <c r="AA24" s="0"/>
+      <c r="AB24" s="0"/>
+      <c r="AC24" s="0"/>
+      <c r="AD24" s="0"/>
+      <c r="AE24" s="0"/>
+      <c r="AF24" s="0"/>
+      <c r="AG24" s="0"/>
+      <c r="AH24" s="0"/>
+      <c r="AI24" s="0"/>
+      <c r="AJ24" s="0"/>
+      <c r="AK24" s="0"/>
+      <c r="AL24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="0"/>
+      <c r="F25" s="51" t="n">
+        <f aca="false">C13</f>
+        <v>7</v>
+      </c>
+      <c r="G25" s="52"/>
+      <c r="H25" s="53" t="n">
+        <f aca="false">F25+F27</f>
+        <v>10</v>
+      </c>
+      <c r="I25" s="0"/>
+      <c r="J25" s="65"/>
       <c r="K25" s="0"/>
       <c r="L25" s="0"/>
       <c r="M25" s="0"/>
@@ -2094,35 +2466,51 @@
       <c r="A26" s="0"/>
       <c r="B26" s="0"/>
       <c r="C26" s="0"/>
-      <c r="D26" s="0"/>
+      <c r="D26" s="64"/>
       <c r="E26" s="0"/>
-      <c r="F26" s="49" t="n">
-        <f aca="false">H26-F25</f>
-        <v>10</v>
-      </c>
-      <c r="G26" s="37"/>
-      <c r="H26" s="50" t="n">
-        <f aca="false">K14</f>
-        <v>13</v>
-      </c>
+      <c r="F26" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
       <c r="I26" s="0"/>
-      <c r="J26" s="0"/>
+      <c r="J26" s="65"/>
       <c r="K26" s="0"/>
       <c r="L26" s="0"/>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M26" s="0"/>
+      <c r="N26" s="0"/>
+      <c r="O26" s="0"/>
+      <c r="P26" s="0"/>
+      <c r="Q26" s="0"/>
+      <c r="R26" s="0"/>
+      <c r="S26" s="0"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0"/>
       <c r="B27" s="0"/>
       <c r="C27" s="0"/>
       <c r="D27" s="0"/>
-      <c r="E27" s="0"/>
-      <c r="F27" s="0"/>
-      <c r="G27" s="0"/>
-      <c r="H27" s="0"/>
-      <c r="I27" s="0"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="55" t="n">
+        <f aca="false">Q6</f>
+        <v>3</v>
+      </c>
+      <c r="G27" s="60" t="n">
+        <f aca="false">H28-H25</f>
+        <v>3</v>
+      </c>
+      <c r="H27" s="57"/>
+      <c r="I27" s="59"/>
       <c r="J27" s="0"/>
       <c r="K27" s="0"/>
       <c r="L27" s="0"/>
+      <c r="M27" s="0"/>
+      <c r="N27" s="0"/>
+      <c r="O27" s="0"/>
+      <c r="P27" s="0"/>
+      <c r="Q27" s="0"/>
+      <c r="R27" s="0"/>
+      <c r="S27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0"/>
@@ -2130,9 +2518,15 @@
       <c r="C28" s="0"/>
       <c r="D28" s="0"/>
       <c r="E28" s="0"/>
-      <c r="F28" s="0"/>
-      <c r="G28" s="0"/>
-      <c r="H28" s="0"/>
+      <c r="F28" s="62" t="n">
+        <f aca="false">H28-F27</f>
+        <v>10</v>
+      </c>
+      <c r="G28" s="49"/>
+      <c r="H28" s="63" t="n">
+        <f aca="false">K16</f>
+        <v>13</v>
+      </c>
       <c r="I28" s="0"/>
       <c r="J28" s="0"/>
       <c r="K28" s="0"/>
@@ -2265,239 +2659,269 @@
       <c r="L37" s="0"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="53"/>
-      <c r="B38" s="54"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="54"/>
-      <c r="I38" s="54"/>
-      <c r="J38" s="54"/>
-      <c r="K38" s="54"/>
-      <c r="L38" s="54"/>
+      <c r="A38" s="0"/>
+      <c r="B38" s="0"/>
+      <c r="C38" s="0"/>
+      <c r="D38" s="0"/>
+      <c r="E38" s="0"/>
+      <c r="F38" s="0"/>
+      <c r="G38" s="0"/>
+      <c r="H38" s="0"/>
+      <c r="I38" s="0"/>
+      <c r="J38" s="0"/>
+      <c r="K38" s="0"/>
+      <c r="L38" s="0"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="53"/>
-      <c r="B39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L39" s="54"/>
+      <c r="A39" s="0"/>
+      <c r="B39" s="0"/>
+      <c r="C39" s="0"/>
+      <c r="D39" s="0"/>
+      <c r="E39" s="0"/>
+      <c r="F39" s="0"/>
+      <c r="G39" s="0"/>
+      <c r="H39" s="0"/>
+      <c r="I39" s="0"/>
+      <c r="J39" s="0"/>
+      <c r="K39" s="0"/>
+      <c r="L39" s="0"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="53"/>
-      <c r="B40" s="55" t="s">
+      <c r="A40" s="66"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="67"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="67"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="66"/>
+      <c r="B41" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L41" s="67"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="66"/>
+      <c r="B42" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="F40" s="56" t="s">
+      <c r="C42" s="68"/>
+      <c r="D42" s="68"/>
+      <c r="F42" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" s="69"/>
+      <c r="H42" s="69"/>
+      <c r="I42" s="69"/>
+      <c r="J42" s="69"/>
+      <c r="L42" s="67"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="66"/>
+      <c r="B43" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="L43" s="67"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="66"/>
+      <c r="B44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="67"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="66"/>
+      <c r="L45" s="67"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="66"/>
+      <c r="B46" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="56"/>
-      <c r="L40" s="54"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="53"/>
-      <c r="B41" s="57" t="s">
+      <c r="C46" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D46" s="49"/>
+      <c r="E46" s="49"/>
+      <c r="F46" s="49"/>
+      <c r="G46" s="49"/>
+      <c r="H46" s="49"/>
+      <c r="I46" s="49"/>
+      <c r="J46" s="49"/>
+      <c r="K46" s="49"/>
+      <c r="L46" s="67"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="66"/>
+      <c r="B47" s="72" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="49"/>
+      <c r="H47" s="49"/>
+      <c r="I47" s="49"/>
+      <c r="J47" s="49"/>
+      <c r="K47" s="49"/>
+      <c r="L47" s="67"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="66"/>
+      <c r="B48" s="72" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="49"/>
+      <c r="J48" s="49"/>
+      <c r="K48" s="49"/>
+      <c r="L48" s="67"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="66"/>
+      <c r="B49" s="72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="49"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="49"/>
+      <c r="J49" s="49"/>
+      <c r="K49" s="49"/>
+      <c r="L49" s="67"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="66"/>
+      <c r="B50" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="C41" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="L41" s="54"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="53"/>
-      <c r="B42" s="2" t="s">
+      <c r="C50" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="49"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="49"/>
+      <c r="H50" s="49"/>
+      <c r="I50" s="49"/>
+      <c r="J50" s="49"/>
+      <c r="K50" s="49"/>
+      <c r="L50" s="67"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="66"/>
+      <c r="B51" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="C51" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D51" s="49"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="49"/>
+      <c r="H51" s="49"/>
+      <c r="I51" s="49"/>
+      <c r="J51" s="49"/>
+      <c r="K51" s="49"/>
+      <c r="L51" s="67"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="66"/>
+      <c r="B52" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="L42" s="54"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="53"/>
-      <c r="L43" s="54"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="53"/>
-      <c r="B44" s="59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
-      <c r="J44" s="37"/>
-      <c r="K44" s="37"/>
-      <c r="L44" s="54"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="53"/>
-      <c r="B45" s="59" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="37"/>
-      <c r="J45" s="37"/>
-      <c r="K45" s="37"/>
-      <c r="L45" s="54"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="53"/>
-      <c r="B46" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="37"/>
-      <c r="I46" s="37"/>
-      <c r="J46" s="37"/>
-      <c r="K46" s="37"/>
-      <c r="L46" s="54"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="53"/>
-      <c r="B47" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="37"/>
-      <c r="I47" s="37"/>
-      <c r="J47" s="37"/>
-      <c r="K47" s="37"/>
-      <c r="L47" s="54"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="53"/>
-      <c r="B48" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="37"/>
-      <c r="K48" s="37"/>
-      <c r="L48" s="54"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="53"/>
-      <c r="B49" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="C49" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37"/>
-      <c r="H49" s="37"/>
-      <c r="I49" s="37"/>
-      <c r="J49" s="37"/>
-      <c r="K49" s="37"/>
-      <c r="L49" s="54"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="53"/>
-      <c r="B50" s="60" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
-      <c r="F50" s="54"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="54"/>
-      <c r="I50" s="54"/>
-      <c r="J50" s="54"/>
-      <c r="K50" s="54"/>
-      <c r="L50" s="54"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="53"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="54"/>
-      <c r="D51" s="54"/>
-      <c r="E51" s="54"/>
-      <c r="F51" s="54"/>
-      <c r="G51" s="54"/>
-      <c r="H51" s="54"/>
-      <c r="I51" s="54"/>
-      <c r="J51" s="54"/>
-      <c r="K51" s="54"/>
-      <c r="L51" s="54"/>
+      <c r="C52" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
+      <c r="H52" s="67"/>
+      <c r="I52" s="67"/>
+      <c r="J52" s="67"/>
+      <c r="K52" s="67"/>
+      <c r="L52" s="67"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="66"/>
+      <c r="B53" s="67"/>
+      <c r="C53" s="67"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="67"/>
+      <c r="H53" s="67"/>
+      <c r="I53" s="67"/>
+      <c r="J53" s="67"/>
+      <c r="K53" s="67"/>
+      <c r="L53" s="67"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="25">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:P1"/>
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="A2:Q2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="K12:M12"/>
-    <mergeCell ref="P12:R12"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:J40"/>
-    <mergeCell ref="C44:K44"/>
-    <mergeCell ref="C45:K45"/>
+    <mergeCell ref="A7:Q7"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="P14:R14"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="F42:J42"/>
     <mergeCell ref="C46:K46"/>
     <mergeCell ref="C47:K47"/>
     <mergeCell ref="C48:K48"/>
     <mergeCell ref="C49:K49"/>
+    <mergeCell ref="C50:K50"/>
+    <mergeCell ref="C51:K51"/>
   </mergeCells>
-  <conditionalFormatting sqref="R1:BL7">
+  <conditionalFormatting sqref="R1:BL7 R8:AH8 AJ8:BL8 R9:AI9 AK9:BL9">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>IF(WEEKDAY(R$1,2)=6,1,IF(WEEKDAY(R$1,2)=7,1,0))</formula>
     </cfRule>
@@ -2509,5 +2933,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Standard"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Standard"&amp;12Seite &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>